--- a/pair_strategies_analysis.xlsx
+++ b/pair_strategies_analysis.xlsx
@@ -502,10 +502,10 @@
         <v>10000</v>
       </c>
       <c r="H2" t="n">
-        <v>46526.36</v>
+        <v>47239.1</v>
       </c>
       <c r="I2" t="n">
-        <v>365.26</v>
+        <v>372.39</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>27150.11</v>
+        <v>27265.15</v>
       </c>
       <c r="I3" t="n">
-        <v>171.5</v>
+        <v>172.65</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>10000</v>
       </c>
       <c r="H4" t="n">
-        <v>23030.48</v>
+        <v>22837.73</v>
       </c>
       <c r="I4" t="n">
-        <v>130.3</v>
+        <v>128.38</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -622,10 +622,10 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>17881.86</v>
+        <v>18155.79</v>
       </c>
       <c r="I5" t="n">
-        <v>78.81999999999999</v>
+        <v>81.56</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -662,10 +662,10 @@
         <v>10000</v>
       </c>
       <c r="H6" t="n">
-        <v>17548.1</v>
+        <v>17401.23</v>
       </c>
       <c r="I6" t="n">
-        <v>75.48</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -702,10 +702,10 @@
         <v>10000</v>
       </c>
       <c r="H7" t="n">
-        <v>16960.63</v>
+        <v>17115.59</v>
       </c>
       <c r="I7" t="n">
-        <v>69.61</v>
+        <v>71.16</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         <v>10000</v>
       </c>
       <c r="H8" t="n">
-        <v>14196.08</v>
+        <v>14325.78</v>
       </c>
       <c r="I8" t="n">
-        <v>41.96</v>
+        <v>43.26</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
         <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>12859.11</v>
+        <v>12751.49</v>
       </c>
       <c r="I9" t="n">
-        <v>28.59</v>
+        <v>27.51</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>11587.62</v>
+        <v>11776.96</v>
       </c>
       <c r="I10" t="n">
-        <v>15.88</v>
+        <v>17.77</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -862,10 +862,10 @@
         <v>10000</v>
       </c>
       <c r="H11" t="n">
-        <v>10884.05</v>
+        <v>11154.09</v>
       </c>
       <c r="I11" t="n">
-        <v>8.84</v>
+        <v>11.54</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
         <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>10103.2</v>
+        <v>10268.28</v>
       </c>
       <c r="I12" t="n">
-        <v>1.03</v>
+        <v>2.68</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -942,10 +942,10 @@
         <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>9122.65</v>
+        <v>9046.299999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.77</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -982,10 +982,10 @@
         <v>10000</v>
       </c>
       <c r="H14" t="n">
-        <v>8612.49</v>
+        <v>8807.1</v>
       </c>
       <c r="I14" t="n">
-        <v>-13.88</v>
+        <v>-11.93</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1022,10 +1022,10 @@
         <v>10000</v>
       </c>
       <c r="H15" t="n">
-        <v>8462.75</v>
+        <v>8653.98</v>
       </c>
       <c r="I15" t="n">
-        <v>-15.37</v>
+        <v>-13.46</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1062,10 +1062,10 @@
         <v>10000</v>
       </c>
       <c r="H16" t="n">
-        <v>8436.4</v>
+        <v>8574.25</v>
       </c>
       <c r="I16" t="n">
-        <v>-15.64</v>
+        <v>-14.26</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1102,10 +1102,10 @@
         <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>7883.67</v>
+        <v>8004.44</v>
       </c>
       <c r="I17" t="n">
-        <v>-21.16</v>
+        <v>-19.96</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         <v>10000</v>
       </c>
       <c r="H18" t="n">
-        <v>6484.91</v>
+        <v>6631.44</v>
       </c>
       <c r="I18" t="n">
-        <v>-35.15</v>
+        <v>-33.69</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         <v>10000</v>
       </c>
       <c r="H19" t="n">
-        <v>5714.77</v>
+        <v>5843.91</v>
       </c>
       <c r="I19" t="n">
-        <v>-42.85</v>
+        <v>-41.56</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1222,10 +1222,10 @@
         <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>5555.72</v>
+        <v>5640.83</v>
       </c>
       <c r="I20" t="n">
-        <v>-44.44</v>
+        <v>-43.59</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NEAR/TRX</t>
+          <t>NEAR/HBAR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>1757</v>
+        <v>1518</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1262,14 +1262,14 @@
         <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>5396.02</v>
+        <v>5403.42</v>
       </c>
       <c r="I21" t="n">
-        <v>-46.04</v>
+        <v>-45.97</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1452.103586 NEAR + cash 0.00</t>
+          <t>67815.763416 HBAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NEAR/HBAR</t>
+          <t>NEAR/TRX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>1518</v>
+        <v>1757</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1302,14 +1302,14 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>5380.3</v>
+        <v>5350.86</v>
       </c>
       <c r="I22" t="n">
-        <v>-46.2</v>
+        <v>-46.49</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>67815.763416 HBAR + cash 0.00</t>
+          <t>1452.103586 NEAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>10000</v>
       </c>
       <c r="H23" t="n">
-        <v>5185.49</v>
+        <v>5142.09</v>
       </c>
       <c r="I23" t="n">
-        <v>-48.15</v>
+        <v>-48.58</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1382,10 +1382,10 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>4848.3</v>
+        <v>4869.14</v>
       </c>
       <c r="I24" t="n">
-        <v>-51.52</v>
+        <v>-51.31</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
         <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>4728.15</v>
+        <v>4748.47</v>
       </c>
       <c r="I25" t="n">
-        <v>-52.72</v>
+        <v>-52.52</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1462,10 +1462,10 @@
         <v>10000</v>
       </c>
       <c r="H26" t="n">
-        <v>4533.14</v>
+        <v>4602.58</v>
       </c>
       <c r="I26" t="n">
-        <v>-54.67</v>
+        <v>-53.97</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1502,10 +1502,10 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>3857.87</v>
+        <v>3912.59</v>
       </c>
       <c r="I27" t="n">
-        <v>-61.42</v>
+        <v>-60.87</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1542,10 +1542,10 @@
         <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>3767.84</v>
+        <v>3784.04</v>
       </c>
       <c r="I28" t="n">
-        <v>-62.32</v>
+        <v>-62.16</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         <v>10000</v>
       </c>
       <c r="H29" t="n">
-        <v>3643.63</v>
+        <v>3695.32</v>
       </c>
       <c r="I29" t="n">
-        <v>-63.56</v>
+        <v>-63.05</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>2931.27</v>
+        <v>2943.87</v>
       </c>
       <c r="I30" t="n">
-        <v>-70.69</v>
+        <v>-70.56</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1662,10 +1662,10 @@
         <v>10000</v>
       </c>
       <c r="H31" t="n">
-        <v>2801.77</v>
+        <v>2813.81</v>
       </c>
       <c r="I31" t="n">
-        <v>-71.98</v>
+        <v>-71.86</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1702,10 +1702,10 @@
         <v>10000</v>
       </c>
       <c r="H32" t="n">
-        <v>2751.2</v>
+        <v>2763.02</v>
       </c>
       <c r="I32" t="n">
-        <v>-72.48999999999999</v>
+        <v>-72.37</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
         <v>10000</v>
       </c>
       <c r="H33" t="n">
-        <v>2415.11</v>
+        <v>2475.03</v>
       </c>
       <c r="I33" t="n">
-        <v>-75.84999999999999</v>
+        <v>-75.25</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1782,10 +1782,10 @@
         <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>2042.81</v>
+        <v>2100.64</v>
       </c>
       <c r="I34" t="n">
-        <v>-79.56999999999999</v>
+        <v>-78.98999999999999</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
         <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>1881.23</v>
+        <v>1934.49</v>
       </c>
       <c r="I35" t="n">
-        <v>-81.19</v>
+        <v>-80.66</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DOT/ATOM</t>
+          <t>ADA/NEAR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>548</v>
+        <v>1322</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1862,14 +1862,14 @@
         <v>10000</v>
       </c>
       <c r="H36" t="n">
-        <v>1756.54</v>
+        <v>1788.82</v>
       </c>
       <c r="I36" t="n">
-        <v>-82.43000000000001</v>
+        <v>-82.11</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1552.538505 DOT + cash 0.00</t>
+          <t>8005.048211 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ADA/NEAR</t>
+          <t>DOT/ATOM</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E37" t="n">
-        <v>1322</v>
+        <v>548</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1902,14 +1902,14 @@
         <v>10000</v>
       </c>
       <c r="H37" t="n">
-        <v>1745.51</v>
+        <v>1764.93</v>
       </c>
       <c r="I37" t="n">
-        <v>-82.54000000000001</v>
+        <v>-82.34999999999999</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8005.048211 ADA + cash 0.00</t>
+          <t>1552.538505 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -1942,10 +1942,10 @@
         <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>1720.1</v>
+        <v>1762.78</v>
       </c>
       <c r="I38" t="n">
-        <v>-82.8</v>
+        <v>-82.37</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
         <v>10000</v>
       </c>
       <c r="H39" t="n">
-        <v>1456.07</v>
+        <v>1463.02</v>
       </c>
       <c r="I39" t="n">
-        <v>-85.44</v>
+        <v>-85.37</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2022,10 +2022,10 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>1264.86</v>
+        <v>1270.89</v>
       </c>
       <c r="I40" t="n">
-        <v>-87.34999999999999</v>
+        <v>-87.29000000000001</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2062,10 +2062,10 @@
         <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>1223.33</v>
+        <v>1257.96</v>
       </c>
       <c r="I41" t="n">
-        <v>-87.77</v>
+        <v>-87.42</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2102,10 +2102,10 @@
         <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>1197.64</v>
+        <v>1231.54</v>
       </c>
       <c r="I42" t="n">
-        <v>-88.02</v>
+        <v>-87.68000000000001</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>1178.14</v>
+        <v>1207.37</v>
       </c>
       <c r="I43" t="n">
-        <v>-88.22</v>
+        <v>-87.93000000000001</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ICP/BNB</t>
+          <t>ADA/ETH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2173,7 +2173,7 @@
         <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>1682</v>
+        <v>1807</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2182,14 +2182,14 @@
         <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>1170.38</v>
+        <v>1197.12</v>
       </c>
       <c r="I44" t="n">
-        <v>-88.3</v>
+        <v>-88.03</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>415.028914 ICP + cash 0.00</t>
+          <t>5357.161790 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ADA/ETH</t>
+          <t>ICP/BNB</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2213,7 +2213,7 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1807</v>
+        <v>1682</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2222,14 +2222,14 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>1168.13</v>
+        <v>1186.98</v>
       </c>
       <c r="I45" t="n">
-        <v>-88.31999999999999</v>
+        <v>-88.13</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>5357.161790 ADA + cash 0.00</t>
+          <t>415.028914 ICP + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -2262,10 +2262,10 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>1151.56</v>
+        <v>1180.13</v>
       </c>
       <c r="I46" t="n">
-        <v>-88.48</v>
+        <v>-88.2</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2302,10 +2302,10 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>1142.03</v>
+        <v>1170.36</v>
       </c>
       <c r="I47" t="n">
-        <v>-88.58</v>
+        <v>-88.3</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2342,10 +2342,10 @@
         <v>10000</v>
       </c>
       <c r="H48" t="n">
-        <v>1093.2</v>
+        <v>1108.7</v>
       </c>
       <c r="I48" t="n">
-        <v>-89.06999999999999</v>
+        <v>-88.91</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2382,10 +2382,10 @@
         <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>893.64</v>
+        <v>918.9400000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>-91.06</v>
+        <v>-90.81</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2422,10 +2422,10 @@
         <v>10000</v>
       </c>
       <c r="H50" t="n">
-        <v>790.05</v>
+        <v>801.25</v>
       </c>
       <c r="I50" t="n">
-        <v>-92.09999999999999</v>
+        <v>-91.98999999999999</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2462,10 +2462,10 @@
         <v>10000</v>
       </c>
       <c r="H51" t="n">
-        <v>752.49</v>
+        <v>756.08</v>
       </c>
       <c r="I51" t="n">
-        <v>-92.48</v>
+        <v>-92.44</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2502,10 +2502,10 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>729.74</v>
+        <v>750.4</v>
       </c>
       <c r="I52" t="n">
-        <v>-92.7</v>
+        <v>-92.5</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         <v>10000</v>
       </c>
       <c r="H53" t="n">
-        <v>723.23</v>
+        <v>743.71</v>
       </c>
       <c r="I53" t="n">
-        <v>-92.77</v>
+        <v>-92.56</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2582,10 +2582,10 @@
         <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>672.59</v>
+        <v>691.63</v>
       </c>
       <c r="I54" t="n">
-        <v>-93.27</v>
+        <v>-93.08</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2622,10 +2622,10 @@
         <v>10000</v>
       </c>
       <c r="H55" t="n">
-        <v>660.42</v>
+        <v>669.79</v>
       </c>
       <c r="I55" t="n">
-        <v>-93.40000000000001</v>
+        <v>-93.3</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2662,10 +2662,10 @@
         <v>10000</v>
       </c>
       <c r="H56" t="n">
-        <v>654.79</v>
+        <v>664.0700000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-93.45</v>
+        <v>-93.36</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2702,10 +2702,10 @@
         <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>618.42</v>
+        <v>621.37</v>
       </c>
       <c r="I57" t="n">
-        <v>-93.81999999999999</v>
+        <v>-93.79000000000001</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DOT/LINK</t>
+          <t>ETH/ATOM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1538</v>
+        <v>1751</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -2742,14 +2742,14 @@
         <v>10000</v>
       </c>
       <c r="H58" t="n">
-        <v>603.89</v>
+        <v>614.84</v>
       </c>
       <c r="I58" t="n">
-        <v>-93.95999999999999</v>
+        <v>-93.84999999999999</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>533.758881 DOT + cash 0.00</t>
+          <t>360.907629 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DOT/AAVE</t>
+          <t>DOT/LINK</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2773,7 +2773,7 @@
         <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>1244</v>
+        <v>1538</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -2782,14 +2782,14 @@
         <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>602.02</v>
+        <v>606.78</v>
       </c>
       <c r="I59" t="n">
-        <v>-93.98</v>
+        <v>-93.93000000000001</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>532.101615 DOT + cash 0.00</t>
+          <t>533.758881 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ETH/ATOM</t>
+          <t>DOT/AAVE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2810,10 +2810,10 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>1751</v>
+        <v>1244</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -2822,14 +2822,14 @@
         <v>10000</v>
       </c>
       <c r="H60" t="n">
-        <v>597.92</v>
+        <v>604.89</v>
       </c>
       <c r="I60" t="n">
-        <v>-94.02</v>
+        <v>-93.95</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>360.907629 ATOM + cash 0.00</t>
+          <t>532.101615 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -2862,10 +2862,10 @@
         <v>10000</v>
       </c>
       <c r="H61" t="n">
-        <v>567.29</v>
+        <v>575.34</v>
       </c>
       <c r="I61" t="n">
-        <v>-94.33</v>
+        <v>-94.25</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2902,10 +2902,10 @@
         <v>10000</v>
       </c>
       <c r="H62" t="n">
-        <v>567.29</v>
+        <v>575.34</v>
       </c>
       <c r="I62" t="n">
-        <v>-94.33</v>
+        <v>-94.25</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2942,10 +2942,10 @@
         <v>10000</v>
       </c>
       <c r="H63" t="n">
-        <v>567.29</v>
+        <v>575.34</v>
       </c>
       <c r="I63" t="n">
-        <v>-94.33</v>
+        <v>-94.25</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2982,10 +2982,10 @@
         <v>10000</v>
       </c>
       <c r="H64" t="n">
-        <v>540.37</v>
+        <v>542.95</v>
       </c>
       <c r="I64" t="n">
-        <v>-94.59999999999999</v>
+        <v>-94.56999999999999</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
         <v>10000</v>
       </c>
       <c r="H65" t="n">
-        <v>494.01</v>
+        <v>496.37</v>
       </c>
       <c r="I65" t="n">
-        <v>-95.06</v>
+        <v>-95.04000000000001</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3062,10 +3062,10 @@
         <v>10000</v>
       </c>
       <c r="H66" t="n">
-        <v>491.48</v>
+        <v>493.82</v>
       </c>
       <c r="I66" t="n">
-        <v>-95.09</v>
+        <v>-95.06</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3102,10 +3102,10 @@
         <v>10000</v>
       </c>
       <c r="H67" t="n">
-        <v>430.35</v>
+        <v>432.4</v>
       </c>
       <c r="I67" t="n">
-        <v>-95.7</v>
+        <v>-95.68000000000001</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3142,10 +3142,10 @@
         <v>10000</v>
       </c>
       <c r="H68" t="n">
-        <v>260.64</v>
+        <v>259.21</v>
       </c>
       <c r="I68" t="n">
-        <v>-97.39</v>
+        <v>-97.41</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3182,10 +3182,10 @@
         <v>10000</v>
       </c>
       <c r="H69" t="n">
-        <v>208.84</v>
+        <v>207.7</v>
       </c>
       <c r="I69" t="n">
-        <v>-97.91</v>
+        <v>-97.92</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3222,10 +3222,10 @@
         <v>10000</v>
       </c>
       <c r="H70" t="n">
-        <v>193.31</v>
+        <v>192.25</v>
       </c>
       <c r="I70" t="n">
-        <v>-98.06999999999999</v>
+        <v>-98.08</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3262,10 +3262,10 @@
         <v>10000</v>
       </c>
       <c r="H71" t="n">
-        <v>154.85</v>
+        <v>154</v>
       </c>
       <c r="I71" t="n">
-        <v>-98.45</v>
+        <v>-98.45999999999999</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>10000</v>
       </c>
       <c r="H72" t="n">
-        <v>132.48</v>
+        <v>131.76</v>
       </c>
       <c r="I72" t="n">
         <v>-98.68000000000001</v>
@@ -3342,10 +3342,10 @@
         <v>10000</v>
       </c>
       <c r="H73" t="n">
-        <v>110.75</v>
+        <v>110.14</v>
       </c>
       <c r="I73" t="n">
-        <v>-98.89</v>
+        <v>-98.90000000000001</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>10000</v>
       </c>
       <c r="H74" t="n">
-        <v>108.24</v>
+        <v>107.65</v>
       </c>
       <c r="I74" t="n">
         <v>-98.92</v>
@@ -3422,7 +3422,7 @@
         <v>10000</v>
       </c>
       <c r="H75" t="n">
-        <v>107.41</v>
+        <v>106.82</v>
       </c>
       <c r="I75" t="n">
         <v>-98.93000000000001</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>XCH/TRX</t>
+          <t>LINK/XCH</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>1808</v>
+        <v>1757</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -3462,14 +3462,14 @@
         <v>10000</v>
       </c>
       <c r="H76" t="n">
-        <v>93.51000000000001</v>
+        <v>93.83</v>
       </c>
       <c r="I76" t="n">
         <v>-99.06</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>62.430263 XCH + cash 0.00</t>
+          <t>62.983169 XCH + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LINK/XCH</t>
+          <t>XCH/TRX</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>1757</v>
+        <v>1808</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -3502,14 +3502,14 @@
         <v>10000</v>
       </c>
       <c r="H77" t="n">
-        <v>94.34</v>
+        <v>93</v>
       </c>
       <c r="I77" t="n">
-        <v>-99.06</v>
+        <v>-99.06999999999999</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>62.983169 XCH + cash 0.00</t>
+          <t>62.430263 XCH + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -3542,10 +3542,10 @@
         <v>10000</v>
       </c>
       <c r="H78" t="n">
-        <v>90.94</v>
+        <v>90.44</v>
       </c>
       <c r="I78" t="n">
-        <v>-99.09</v>
+        <v>-99.09999999999999</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3582,10 +3582,10 @@
         <v>10000</v>
       </c>
       <c r="H79" t="n">
-        <v>90.90000000000001</v>
+        <v>90.41</v>
       </c>
       <c r="I79" t="n">
-        <v>-99.09</v>
+        <v>-99.09999999999999</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3688,10 +3688,10 @@
         <v>10000</v>
       </c>
       <c r="H2" t="n">
-        <v>50757.25</v>
+        <v>50972.33</v>
       </c>
       <c r="I2" t="n">
-        <v>407.57</v>
+        <v>409.72</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -3728,10 +3728,10 @@
         <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>30905.72</v>
+        <v>30647.06</v>
       </c>
       <c r="I3" t="n">
-        <v>209.06</v>
+        <v>206.47</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -3768,10 +3768,10 @@
         <v>10000</v>
       </c>
       <c r="H4" t="n">
-        <v>20406.15</v>
+        <v>20493.85</v>
       </c>
       <c r="I4" t="n">
-        <v>104.06</v>
+        <v>104.94</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -3808,10 +3808,10 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>20056.37</v>
+        <v>20363.61</v>
       </c>
       <c r="I5" t="n">
-        <v>100.56</v>
+        <v>103.64</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BTC/NEAR</t>
+          <t>ETH/TRX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1388</v>
+        <v>1499</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -3848,14 +3848,14 @@
         <v>10000</v>
       </c>
       <c r="H6" t="n">
-        <v>15433.56</v>
+        <v>15516.21</v>
       </c>
       <c r="I6" t="n">
-        <v>54.34</v>
+        <v>55.16</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4153.272897 NEAR + cash 0.00</t>
+          <t>5.891635 ETH + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ETH/TRX</t>
+          <t>BTC/NEAR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>1499</v>
+        <v>1388</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3888,14 +3888,14 @@
         <v>10000</v>
       </c>
       <c r="H7" t="n">
-        <v>15266.76</v>
+        <v>15304.4</v>
       </c>
       <c r="I7" t="n">
-        <v>52.67</v>
+        <v>53.04</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.891635 ETH + cash 0.00</t>
+          <t>4153.272897 NEAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -3928,10 +3928,10 @@
         <v>10000</v>
       </c>
       <c r="H8" t="n">
-        <v>13754.26</v>
+        <v>13879.92</v>
       </c>
       <c r="I8" t="n">
-        <v>37.54</v>
+        <v>38.8</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -3968,10 +3968,10 @@
         <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>13514.05</v>
+        <v>13819.42</v>
       </c>
       <c r="I9" t="n">
-        <v>35.14</v>
+        <v>38.19</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>12813.58</v>
+        <v>12930.65</v>
       </c>
       <c r="I10" t="n">
-        <v>28.14</v>
+        <v>29.31</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -4048,10 +4048,10 @@
         <v>10000</v>
       </c>
       <c r="H11" t="n">
-        <v>12756.57</v>
+        <v>12649.81</v>
       </c>
       <c r="I11" t="n">
-        <v>27.57</v>
+        <v>26.5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -4088,10 +4088,10 @@
         <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>11201.54</v>
+        <v>11384.56</v>
       </c>
       <c r="I12" t="n">
-        <v>12.02</v>
+        <v>13.85</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>7464.59</v>
+        <v>7402.11</v>
       </c>
       <c r="I13" t="n">
-        <v>-25.35</v>
+        <v>-25.98</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -4168,10 +4168,10 @@
         <v>10000</v>
       </c>
       <c r="H14" t="n">
-        <v>6525.15</v>
+        <v>6672.6</v>
       </c>
       <c r="I14" t="n">
-        <v>-34.75</v>
+        <v>-33.27</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -4208,10 +4208,10 @@
         <v>10000</v>
       </c>
       <c r="H15" t="n">
-        <v>5999.66</v>
+        <v>6135.23</v>
       </c>
       <c r="I15" t="n">
-        <v>-40</v>
+        <v>-38.65</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -4248,10 +4248,10 @@
         <v>10000</v>
       </c>
       <c r="H16" t="n">
-        <v>5997.76</v>
+        <v>6089.64</v>
       </c>
       <c r="I16" t="n">
-        <v>-40.02</v>
+        <v>-39.1</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -4288,10 +4288,10 @@
         <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>5885.23</v>
+        <v>5981.39</v>
       </c>
       <c r="I17" t="n">
-        <v>-41.15</v>
+        <v>-40.19</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
         <v>10000</v>
       </c>
       <c r="H18" t="n">
-        <v>5714.77</v>
+        <v>5843.91</v>
       </c>
       <c r="I18" t="n">
-        <v>-42.85</v>
+        <v>-41.56</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>10000</v>
       </c>
       <c r="H19" t="n">
-        <v>5627.14</v>
+        <v>5754.3</v>
       </c>
       <c r="I19" t="n">
-        <v>-43.73</v>
+        <v>-42.46</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -4408,10 +4408,10 @@
         <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>5555.72</v>
+        <v>5640.83</v>
       </c>
       <c r="I20" t="n">
-        <v>-44.44</v>
+        <v>-43.59</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NEAR/BNB</t>
+          <t>ETH/LINK</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4436,10 +4436,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>1619</v>
+        <v>1662</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -4448,14 +4448,14 @@
         <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>5262.03</v>
+        <v>5364.86</v>
       </c>
       <c r="I21" t="n">
-        <v>-47.38</v>
+        <v>-46.35</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1416.045622 NEAR + cash 0.00</t>
+          <t>432.813809 LINK + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ETH/LINK</t>
+          <t>NEAR/BNB</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4476,10 +4476,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>1662</v>
+        <v>1619</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -4488,14 +4488,14 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>5246.31</v>
+        <v>5217.99</v>
       </c>
       <c r="I22" t="n">
-        <v>-47.54</v>
+        <v>-47.82</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>432.813809 LINK + cash 0.00</t>
+          <t>1416.045622 NEAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -4528,10 +4528,10 @@
         <v>10000</v>
       </c>
       <c r="H23" t="n">
-        <v>4533.14</v>
+        <v>4602.58</v>
       </c>
       <c r="I23" t="n">
-        <v>-54.67</v>
+        <v>-53.97</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -4568,10 +4568,10 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>4030.65</v>
+        <v>4047.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-59.69</v>
+        <v>-59.52</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -4608,10 +4608,10 @@
         <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>3171.89</v>
+        <v>3250.59</v>
       </c>
       <c r="I25" t="n">
-        <v>-68.28</v>
+        <v>-67.48999999999999</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BTC/HBAR</t>
+          <t>LINK/ATOM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>1801</v>
+        <v>1316</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -4648,14 +4648,14 @@
         <v>10000</v>
       </c>
       <c r="H26" t="n">
-        <v>2898.61</v>
+        <v>2915.05</v>
       </c>
       <c r="I26" t="n">
-        <v>-71.01000000000001</v>
+        <v>-70.84999999999999</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>36535.460650 HBAR + cash 0.00</t>
+          <t>1711.109090 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LINK/HBAR</t>
+          <t>BTC/HBAR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4679,7 +4679,7 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>1462</v>
+        <v>1801</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -4688,14 +4688,14 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>2882.51</v>
+        <v>2911.07</v>
       </c>
       <c r="I27" t="n">
-        <v>-71.17</v>
+        <v>-70.89</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>36332.460352 HBAR + cash 0.00</t>
+          <t>36535.460650 HBAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LINK/ATOM</t>
+          <t>LINK/HBAR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1316</v>
+        <v>1462</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -4728,14 +4728,14 @@
         <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>2834.79</v>
+        <v>2894.9</v>
       </c>
       <c r="I28" t="n">
-        <v>-71.65000000000001</v>
+        <v>-71.05</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1711.109090 ATOM + cash 0.00</t>
+          <t>36332.460352 HBAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -4768,10 +4768,10 @@
         <v>10000</v>
       </c>
       <c r="H29" t="n">
-        <v>2800.55</v>
+        <v>2813.92</v>
       </c>
       <c r="I29" t="n">
-        <v>-71.98999999999999</v>
+        <v>-71.86</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -4808,10 +4808,10 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>2792.22</v>
+        <v>2804.22</v>
       </c>
       <c r="I30" t="n">
-        <v>-72.08</v>
+        <v>-71.95999999999999</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         <v>10000</v>
       </c>
       <c r="H31" t="n">
-        <v>2751.2</v>
+        <v>2763.02</v>
       </c>
       <c r="I31" t="n">
-        <v>-72.48999999999999</v>
+        <v>-72.37</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -4888,10 +4888,10 @@
         <v>10000</v>
       </c>
       <c r="H32" t="n">
-        <v>2462.48</v>
+        <v>2474.23</v>
       </c>
       <c r="I32" t="n">
-        <v>-75.38</v>
+        <v>-75.26000000000001</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -4928,10 +4928,10 @@
         <v>10000</v>
       </c>
       <c r="H33" t="n">
-        <v>2406.44</v>
+        <v>2416.79</v>
       </c>
       <c r="I33" t="n">
-        <v>-75.94</v>
+        <v>-75.83</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -4968,10 +4968,10 @@
         <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>2384.14</v>
+        <v>2394.39</v>
       </c>
       <c r="I34" t="n">
-        <v>-76.16</v>
+        <v>-76.06</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ICP/BNB</t>
+          <t>ATOM/HBAR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>1682</v>
+        <v>1461</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -5008,14 +5008,14 @@
         <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>2174.67</v>
+        <v>2217.47</v>
       </c>
       <c r="I35" t="n">
-        <v>-78.25</v>
+        <v>-77.83</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>771.157939 ICP + cash 0.00</t>
+          <t>1301.638641 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ATOM/HBAR</t>
+          <t>ICP/BNB</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1461</v>
+        <v>1682</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -5048,14 +5048,14 @@
         <v>10000</v>
       </c>
       <c r="H36" t="n">
-        <v>2156.42</v>
+        <v>2205.51</v>
       </c>
       <c r="I36" t="n">
-        <v>-78.44</v>
+        <v>-77.94</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1301.638641 ATOM + cash 0.00</t>
+          <t>771.157939 ICP + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -5088,10 +5088,10 @@
         <v>10000</v>
       </c>
       <c r="H37" t="n">
-        <v>1816.96</v>
+        <v>1868.4</v>
       </c>
       <c r="I37" t="n">
-        <v>-81.83</v>
+        <v>-81.31999999999999</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DOT/AAVE</t>
+          <t>ADA/ICP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>1678</v>
+        <v>1382</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -5128,14 +5128,14 @@
         <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>1576.59</v>
+        <v>1611.38</v>
       </c>
       <c r="I38" t="n">
-        <v>-84.23</v>
+        <v>-83.89</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1393.486357 DOT + cash 0.00</t>
+          <t>7211.025611 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ADA/ICP</t>
+          <t>DOT/AAVE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1382</v>
+        <v>1678</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -5168,14 +5168,14 @@
         <v>10000</v>
       </c>
       <c r="H39" t="n">
-        <v>1572.37</v>
+        <v>1584.12</v>
       </c>
       <c r="I39" t="n">
-        <v>-84.28</v>
+        <v>-84.16</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>7211.025611 ADA + cash 0.00</t>
+          <t>1393.486357 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -5208,10 +5208,10 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>1378.76</v>
+        <v>1417.79</v>
       </c>
       <c r="I40" t="n">
-        <v>-86.20999999999999</v>
+        <v>-85.81999999999999</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -5248,10 +5248,10 @@
         <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>1268.91</v>
+        <v>1300.39</v>
       </c>
       <c r="I41" t="n">
-        <v>-87.31</v>
+        <v>-87</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -5288,10 +5288,10 @@
         <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>1268.54</v>
+        <v>1300.01</v>
       </c>
       <c r="I42" t="n">
-        <v>-87.31</v>
+        <v>-87</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>1244.67</v>
+        <v>1275.55</v>
       </c>
       <c r="I43" t="n">
-        <v>-87.55</v>
+        <v>-87.23999999999999</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DOT/BNB</t>
+          <t>ADA/ATOM</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5359,7 +5359,7 @@
         <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>1659</v>
+        <v>1487</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -5368,14 +5368,14 @@
         <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>1184.49</v>
+        <v>1212.35</v>
       </c>
       <c r="I44" t="n">
-        <v>-88.16</v>
+        <v>-87.88</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>1046.926411 DOT + cash 0.00</t>
+          <t>5425.315793 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ADA/ATOM</t>
+          <t>ADA/LINK</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5399,7 +5399,7 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1487</v>
+        <v>1791</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -5408,14 +5408,14 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>1183</v>
+        <v>1207.37</v>
       </c>
       <c r="I45" t="n">
-        <v>-88.17</v>
+        <v>-87.93000000000001</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>5425.315793 ADA + cash 0.00</t>
+          <t>5403.040011 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ADA/LINK</t>
+          <t>ADA/ETH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5439,7 +5439,7 @@
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>1791</v>
+        <v>1807</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -5448,14 +5448,14 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>1178.14</v>
+        <v>1197.12</v>
       </c>
       <c r="I46" t="n">
-        <v>-88.22</v>
+        <v>-88.03</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>5403.040011 ADA + cash 0.00</t>
+          <t>5357.161790 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ADA/ETH</t>
+          <t>DOT/BNB</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5479,7 +5479,7 @@
         <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>1807</v>
+        <v>1659</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -5488,14 +5488,14 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>1168.13</v>
+        <v>1190.15</v>
       </c>
       <c r="I47" t="n">
-        <v>-88.31999999999999</v>
+        <v>-88.09999999999999</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>5357.161790 ADA + cash 0.00</t>
+          <t>1046.926411 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -5528,10 +5528,10 @@
         <v>10000</v>
       </c>
       <c r="H48" t="n">
-        <v>1160.68</v>
+        <v>1189.47</v>
       </c>
       <c r="I48" t="n">
-        <v>-88.39</v>
+        <v>-88.11</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -5568,10 +5568,10 @@
         <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>1154.3</v>
+        <v>1182.94</v>
       </c>
       <c r="I49" t="n">
-        <v>-88.45999999999999</v>
+        <v>-88.17</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -5608,10 +5608,10 @@
         <v>10000</v>
       </c>
       <c r="H50" t="n">
-        <v>1151.56</v>
+        <v>1180.13</v>
       </c>
       <c r="I50" t="n">
-        <v>-88.48</v>
+        <v>-88.2</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -5648,10 +5648,10 @@
         <v>10000</v>
       </c>
       <c r="H51" t="n">
-        <v>1142.03</v>
+        <v>1170.36</v>
       </c>
       <c r="I51" t="n">
-        <v>-88.58</v>
+        <v>-88.3</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -5688,10 +5688,10 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>1093.86</v>
+        <v>1124.83</v>
       </c>
       <c r="I52" t="n">
-        <v>-89.06</v>
+        <v>-88.75</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -5728,10 +5728,10 @@
         <v>10000</v>
       </c>
       <c r="H53" t="n">
-        <v>728.3200000000001</v>
+        <v>738.65</v>
       </c>
       <c r="I53" t="n">
-        <v>-92.72</v>
+        <v>-92.61</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -5768,10 +5768,10 @@
         <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>698.13</v>
+        <v>708.04</v>
       </c>
       <c r="I54" t="n">
-        <v>-93.02</v>
+        <v>-92.92</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>10000</v>
       </c>
       <c r="H55" t="n">
-        <v>692.6</v>
+        <v>702.4299999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>-93.06999999999999</v>
+        <v>-92.98</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -5848,10 +5848,10 @@
         <v>10000</v>
       </c>
       <c r="H56" t="n">
-        <v>670.53</v>
+        <v>680.04</v>
       </c>
       <c r="I56" t="n">
-        <v>-93.29000000000001</v>
+        <v>-93.2</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ICP/TRX</t>
+          <t>BTC/ATOM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>1790</v>
+        <v>1757</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -5888,14 +5888,14 @@
         <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>660.42</v>
+        <v>673.8099999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>-93.40000000000001</v>
+        <v>-93.26000000000001</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>234.191349 ICP + cash 0.00</t>
+          <t>395.521717 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BTC/ATOM</t>
+          <t>ICP/TRX</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>1757</v>
+        <v>1790</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -5928,14 +5928,14 @@
         <v>10000</v>
       </c>
       <c r="H58" t="n">
-        <v>655.26</v>
+        <v>669.79</v>
       </c>
       <c r="I58" t="n">
-        <v>-93.45</v>
+        <v>-93.3</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>395.521717 ATOM + cash 0.00</t>
+          <t>234.191349 ICP + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -5968,10 +5968,10 @@
         <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>642.71</v>
+        <v>660.9</v>
       </c>
       <c r="I59" t="n">
-        <v>-93.56999999999999</v>
+        <v>-93.39</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -6008,10 +6008,10 @@
         <v>10000</v>
       </c>
       <c r="H60" t="n">
-        <v>622.36</v>
+        <v>625.33</v>
       </c>
       <c r="I60" t="n">
-        <v>-93.78</v>
+        <v>-93.75</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -6048,10 +6048,10 @@
         <v>10000</v>
       </c>
       <c r="H61" t="n">
-        <v>567.29</v>
+        <v>575.34</v>
       </c>
       <c r="I61" t="n">
-        <v>-94.33</v>
+        <v>-94.25</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -6088,10 +6088,10 @@
         <v>10000</v>
       </c>
       <c r="H62" t="n">
-        <v>567.29</v>
+        <v>575.34</v>
       </c>
       <c r="I62" t="n">
-        <v>-94.33</v>
+        <v>-94.25</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -6128,10 +6128,10 @@
         <v>10000</v>
       </c>
       <c r="H63" t="n">
-        <v>567.29</v>
+        <v>575.34</v>
       </c>
       <c r="I63" t="n">
-        <v>-94.33</v>
+        <v>-94.25</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -6168,10 +6168,10 @@
         <v>10000</v>
       </c>
       <c r="H64" t="n">
-        <v>567.29</v>
+        <v>575.34</v>
       </c>
       <c r="I64" t="n">
-        <v>-94.33</v>
+        <v>-94.25</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -6208,10 +6208,10 @@
         <v>10000</v>
       </c>
       <c r="H65" t="n">
-        <v>567.29</v>
+        <v>575.34</v>
       </c>
       <c r="I65" t="n">
-        <v>-94.33</v>
+        <v>-94.25</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -6248,10 +6248,10 @@
         <v>10000</v>
       </c>
       <c r="H66" t="n">
-        <v>523.24</v>
+        <v>525.74</v>
       </c>
       <c r="I66" t="n">
-        <v>-94.77</v>
+        <v>-94.73999999999999</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>10000</v>
       </c>
       <c r="H67" t="n">
-        <v>505.09</v>
+        <v>519.38</v>
       </c>
       <c r="I67" t="n">
-        <v>-94.95</v>
+        <v>-94.81</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -6328,10 +6328,10 @@
         <v>10000</v>
       </c>
       <c r="H68" t="n">
-        <v>491.48</v>
+        <v>493.82</v>
       </c>
       <c r="I68" t="n">
-        <v>-95.09</v>
+        <v>-95.06</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
         <v>10000</v>
       </c>
       <c r="H69" t="n">
-        <v>440.2</v>
+        <v>442.3</v>
       </c>
       <c r="I69" t="n">
-        <v>-95.59999999999999</v>
+        <v>-95.58</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -6408,10 +6408,10 @@
         <v>10000</v>
       </c>
       <c r="H70" t="n">
-        <v>140.77</v>
+        <v>140</v>
       </c>
       <c r="I70" t="n">
-        <v>-98.59</v>
+        <v>-98.59999999999999</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -6448,10 +6448,10 @@
         <v>10000</v>
       </c>
       <c r="H71" t="n">
-        <v>102.63</v>
+        <v>102.07</v>
       </c>
       <c r="I71" t="n">
-        <v>-98.97</v>
+        <v>-98.98</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>10000</v>
       </c>
       <c r="H72" t="n">
-        <v>100.31</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="I72" t="n">
         <v>-99</v>
@@ -6528,10 +6528,10 @@
         <v>10000</v>
       </c>
       <c r="H73" t="n">
-        <v>99.59</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>-99</v>
+        <v>-99.01000000000001</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -6568,10 +6568,10 @@
         <v>10000</v>
       </c>
       <c r="H74" t="n">
-        <v>97.86</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>-99.02</v>
+        <v>-99.03</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>10000</v>
       </c>
       <c r="H75" t="n">
-        <v>94.34</v>
+        <v>93.83</v>
       </c>
       <c r="I75" t="n">
         <v>-99.06</v>
@@ -6648,10 +6648,10 @@
         <v>10000</v>
       </c>
       <c r="H76" t="n">
-        <v>93.81999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="I76" t="n">
-        <v>-99.06</v>
+        <v>-99.06999999999999</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -6688,10 +6688,10 @@
         <v>10000</v>
       </c>
       <c r="H77" t="n">
-        <v>91.72</v>
+        <v>91.22</v>
       </c>
       <c r="I77" t="n">
-        <v>-99.08</v>
+        <v>-99.09</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -6728,10 +6728,10 @@
         <v>10000</v>
       </c>
       <c r="H78" t="n">
-        <v>83.53</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>-99.16</v>
+        <v>-99.17</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>10000</v>
       </c>
       <c r="H79" t="n">
-        <v>81.3</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="I79" t="n">
         <v>-99.19</v>
@@ -6874,10 +6874,10 @@
         <v>10000</v>
       </c>
       <c r="H2" t="n">
-        <v>104238.11</v>
+        <v>105834.93</v>
       </c>
       <c r="I2" t="n">
-        <v>942.38</v>
+        <v>958.35</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -6914,10 +6914,10 @@
         <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>97889.72</v>
+        <v>98784.08</v>
       </c>
       <c r="I3" t="n">
-        <v>878.9</v>
+        <v>887.84</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -6954,10 +6954,10 @@
         <v>10000</v>
       </c>
       <c r="H4" t="n">
-        <v>92803.19</v>
+        <v>94224.85000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>828.03</v>
+        <v>842.25</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -6994,10 +6994,10 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>63207.16</v>
+        <v>64239.94</v>
       </c>
       <c r="I5" t="n">
-        <v>532.0700000000001</v>
+        <v>542.4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -7034,10 +7034,10 @@
         <v>10000</v>
       </c>
       <c r="H6" t="n">
-        <v>62799.38</v>
+        <v>64218.42</v>
       </c>
       <c r="I6" t="n">
-        <v>527.99</v>
+        <v>542.1799999999999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -7074,10 +7074,10 @@
         <v>10000</v>
       </c>
       <c r="H7" t="n">
-        <v>57616.82</v>
+        <v>58499.45</v>
       </c>
       <c r="I7" t="n">
-        <v>476.17</v>
+        <v>484.99</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -7114,10 +7114,10 @@
         <v>10000</v>
       </c>
       <c r="H8" t="n">
-        <v>55890.9</v>
+        <v>56127.73</v>
       </c>
       <c r="I8" t="n">
-        <v>458.91</v>
+        <v>461.28</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -7154,10 +7154,10 @@
         <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>54417.4</v>
+        <v>54651.29</v>
       </c>
       <c r="I9" t="n">
-        <v>444.17</v>
+        <v>446.51</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -7194,10 +7194,10 @@
         <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>53334.36</v>
+        <v>54151.39</v>
       </c>
       <c r="I10" t="n">
-        <v>433.34</v>
+        <v>441.51</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -7234,10 +7234,10 @@
         <v>10000</v>
       </c>
       <c r="H11" t="n">
-        <v>51979.99</v>
+        <v>52203.41</v>
       </c>
       <c r="I11" t="n">
-        <v>419.8</v>
+        <v>422.03</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -7274,10 +7274,10 @@
         <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>47067.7</v>
+        <v>46673.78</v>
       </c>
       <c r="I12" t="n">
-        <v>370.68</v>
+        <v>366.74</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>45327.35</v>
+        <v>45522.17</v>
       </c>
       <c r="I13" t="n">
-        <v>353.27</v>
+        <v>355.22</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -7354,10 +7354,10 @@
         <v>10000</v>
       </c>
       <c r="H14" t="n">
-        <v>43659.58</v>
+        <v>43844.58</v>
       </c>
       <c r="I14" t="n">
-        <v>336.6</v>
+        <v>338.45</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -7394,10 +7394,10 @@
         <v>10000</v>
       </c>
       <c r="H15" t="n">
-        <v>42272.66</v>
+        <v>43321.47</v>
       </c>
       <c r="I15" t="n">
-        <v>322.73</v>
+        <v>333.21</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -7434,10 +7434,10 @@
         <v>10000</v>
       </c>
       <c r="H16" t="n">
-        <v>42074.73</v>
+        <v>41722.59</v>
       </c>
       <c r="I16" t="n">
-        <v>320.75</v>
+        <v>317.23</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -7474,10 +7474,10 @@
         <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>40309.91</v>
+        <v>41220.76</v>
       </c>
       <c r="I17" t="n">
-        <v>303.1</v>
+        <v>312.21</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -7514,10 +7514,10 @@
         <v>10000</v>
       </c>
       <c r="H18" t="n">
-        <v>38976.6</v>
+        <v>38650.4</v>
       </c>
       <c r="I18" t="n">
-        <v>289.77</v>
+        <v>286.5</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -7554,10 +7554,10 @@
         <v>10000</v>
       </c>
       <c r="H19" t="n">
-        <v>36512.26</v>
+        <v>36669.19</v>
       </c>
       <c r="I19" t="n">
-        <v>265.12</v>
+        <v>266.69</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -7594,10 +7594,10 @@
         <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>33132.69</v>
+        <v>33674.07</v>
       </c>
       <c r="I20" t="n">
-        <v>231.33</v>
+        <v>236.74</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -7634,10 +7634,10 @@
         <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>33097.45</v>
+        <v>33566.92</v>
       </c>
       <c r="I21" t="n">
-        <v>230.97</v>
+        <v>235.67</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -7674,10 +7674,10 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>32751.3</v>
+        <v>33491.37</v>
       </c>
       <c r="I22" t="n">
-        <v>227.51</v>
+        <v>234.91</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         <v>10000</v>
       </c>
       <c r="H23" t="n">
-        <v>30479.33</v>
+        <v>31168.05</v>
       </c>
       <c r="I23" t="n">
-        <v>204.79</v>
+        <v>211.68</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -7754,10 +7754,10 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>29917.16</v>
+        <v>30341.52</v>
       </c>
       <c r="I24" t="n">
-        <v>199.17</v>
+        <v>203.42</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -7794,10 +7794,10 @@
         <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>27156.66</v>
+        <v>27770.3</v>
       </c>
       <c r="I25" t="n">
-        <v>171.57</v>
+        <v>177.7</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -7834,10 +7834,10 @@
         <v>10000</v>
       </c>
       <c r="H26" t="n">
-        <v>25908.68</v>
+        <v>26494.12</v>
       </c>
       <c r="I26" t="n">
-        <v>159.09</v>
+        <v>164.94</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -7874,10 +7874,10 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>23030.96</v>
+        <v>23407.27</v>
       </c>
       <c r="I27" t="n">
-        <v>130.31</v>
+        <v>134.07</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NEAR/HBAR</t>
+          <t>ICP/BTC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>957</v>
+        <v>824</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -7914,14 +7914,14 @@
         <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>21417.21</v>
+        <v>21548.24</v>
       </c>
       <c r="I28" t="n">
-        <v>114.17</v>
+        <v>115.48</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>269952.347078 HBAR + cash 0.00</t>
+          <t>7534.348009 ICP + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ICP/BTC</t>
+          <t>NEAR/HBAR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>824</v>
+        <v>957</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -7954,14 +7954,14 @@
         <v>10000</v>
       </c>
       <c r="H29" t="n">
-        <v>21246.86</v>
+        <v>21509.26</v>
       </c>
       <c r="I29" t="n">
-        <v>112.47</v>
+        <v>115.09</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>7534.348009 ICP + cash 0.00</t>
+          <t>269952.347078 HBAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -7994,10 +7994,10 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>20906.42</v>
+        <v>21425.12</v>
       </c>
       <c r="I30" t="n">
-        <v>109.06</v>
+        <v>114.25</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -8034,10 +8034,10 @@
         <v>10000</v>
       </c>
       <c r="H31" t="n">
-        <v>20361.74</v>
+        <v>20866.93</v>
       </c>
       <c r="I31" t="n">
-        <v>103.62</v>
+        <v>108.67</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -8074,10 +8074,10 @@
         <v>10000</v>
       </c>
       <c r="H32" t="n">
-        <v>19891.61</v>
+        <v>20385.14</v>
       </c>
       <c r="I32" t="n">
-        <v>98.92</v>
+        <v>103.85</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -8114,10 +8114,10 @@
         <v>10000</v>
       </c>
       <c r="H33" t="n">
-        <v>18831.97</v>
+        <v>19139.68</v>
       </c>
       <c r="I33" t="n">
-        <v>88.31999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -8154,10 +8154,10 @@
         <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>18172.19</v>
+        <v>18469.11</v>
       </c>
       <c r="I34" t="n">
-        <v>81.72</v>
+        <v>84.69</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -8194,10 +8194,10 @@
         <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>17839.51</v>
+        <v>18131</v>
       </c>
       <c r="I35" t="n">
-        <v>78.40000000000001</v>
+        <v>81.31</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -8234,10 +8234,10 @@
         <v>10000</v>
       </c>
       <c r="H36" t="n">
-        <v>15907.55</v>
+        <v>16167.47</v>
       </c>
       <c r="I36" t="n">
-        <v>59.08</v>
+        <v>61.67</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -8274,10 +8274,10 @@
         <v>10000</v>
       </c>
       <c r="H37" t="n">
-        <v>15481.03</v>
+        <v>15700.62</v>
       </c>
       <c r="I37" t="n">
-        <v>54.81</v>
+        <v>57.01</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -8314,10 +8314,10 @@
         <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>15117.16</v>
+        <v>15331.59</v>
       </c>
       <c r="I38" t="n">
-        <v>51.17</v>
+        <v>53.32</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -8354,10 +8354,10 @@
         <v>10000</v>
       </c>
       <c r="H39" t="n">
-        <v>14680.04</v>
+        <v>14888.26</v>
       </c>
       <c r="I39" t="n">
-        <v>46.8</v>
+        <v>48.88</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -8394,10 +8394,10 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>13832.45</v>
+        <v>14175.64</v>
       </c>
       <c r="I40" t="n">
-        <v>38.32</v>
+        <v>41.76</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -8434,10 +8434,10 @@
         <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>13562.49</v>
+        <v>13898.98</v>
       </c>
       <c r="I41" t="n">
-        <v>35.62</v>
+        <v>38.99</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -8474,10 +8474,10 @@
         <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>13032.12</v>
+        <v>13216.98</v>
       </c>
       <c r="I42" t="n">
-        <v>30.32</v>
+        <v>32.17</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -8514,10 +8514,10 @@
         <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>12849.55</v>
+        <v>13031.81</v>
       </c>
       <c r="I43" t="n">
-        <v>28.5</v>
+        <v>30.32</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -8554,10 +8554,10 @@
         <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>12698.34</v>
+        <v>13013.39</v>
       </c>
       <c r="I44" t="n">
-        <v>26.98</v>
+        <v>30.13</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -8594,10 +8594,10 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>12383.62</v>
+        <v>12690.87</v>
       </c>
       <c r="I45" t="n">
-        <v>23.84</v>
+        <v>26.91</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -8634,10 +8634,10 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>11024</v>
+        <v>11180.36</v>
       </c>
       <c r="I46" t="n">
-        <v>10.24</v>
+        <v>11.8</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -8674,10 +8674,10 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>4440.87</v>
+        <v>4462.07</v>
       </c>
       <c r="I47" t="n">
-        <v>-55.59</v>
+        <v>-55.38</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -8714,10 +8714,10 @@
         <v>10000</v>
       </c>
       <c r="H48" t="n">
-        <v>3700.75</v>
+        <v>3718.41</v>
       </c>
       <c r="I48" t="n">
-        <v>-62.99</v>
+        <v>-62.82</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -8754,10 +8754,10 @@
         <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>3559.61</v>
+        <v>3660.38</v>
       </c>
       <c r="I49" t="n">
-        <v>-64.40000000000001</v>
+        <v>-63.4</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -8794,10 +8794,10 @@
         <v>10000</v>
       </c>
       <c r="H50" t="n">
-        <v>3213.92</v>
+        <v>3229.26</v>
       </c>
       <c r="I50" t="n">
-        <v>-67.86</v>
+        <v>-67.70999999999999</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -8834,10 +8834,10 @@
         <v>10000</v>
       </c>
       <c r="H51" t="n">
-        <v>3168.17</v>
+        <v>3183.29</v>
       </c>
       <c r="I51" t="n">
-        <v>-68.31999999999999</v>
+        <v>-68.17</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DOT/BNB</t>
+          <t>DOT/ATOM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1030</v>
+        <v>864</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -8874,14 +8874,14 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>3126.26</v>
+        <v>3164.35</v>
       </c>
       <c r="I52" t="n">
-        <v>-68.73999999999999</v>
+        <v>-68.36</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2763.181063 DOT + cash 0.00</t>
+          <t>1857.450413 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -8893,7 +8893,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DOT/ATOM</t>
+          <t>DOT/BNB</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>864</v>
+        <v>1030</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -8914,14 +8914,14 @@
         <v>10000</v>
       </c>
       <c r="H53" t="n">
-        <v>3077.24</v>
+        <v>3141.18</v>
       </c>
       <c r="I53" t="n">
-        <v>-69.23</v>
+        <v>-68.59</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>1857.450413 ATOM + cash 0.00</t>
+          <t>2763.181063 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -8954,10 +8954,10 @@
         <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>3054.99</v>
+        <v>3069.57</v>
       </c>
       <c r="I54" t="n">
-        <v>-69.45</v>
+        <v>-69.3</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -8994,10 +8994,10 @@
         <v>10000</v>
       </c>
       <c r="H55" t="n">
-        <v>2957.86</v>
+        <v>3041.6</v>
       </c>
       <c r="I55" t="n">
-        <v>-70.42</v>
+        <v>-69.58</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ADA/DOT</t>
+          <t>ETH/ATOM</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -9022,10 +9022,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>923</v>
+        <v>967</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -9034,14 +9034,14 @@
         <v>10000</v>
       </c>
       <c r="H56" t="n">
-        <v>2916.28</v>
+        <v>2932.38</v>
       </c>
       <c r="I56" t="n">
-        <v>-70.84</v>
+        <v>-70.68000000000001</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2577.583471 DOT + cash 0.00</t>
+          <t>1721.284500 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ICP/DOT</t>
+          <t>ADA/DOT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -9065,7 +9065,7 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>1059</v>
+        <v>923</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -9074,14 +9074,14 @@
         <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>2898.11</v>
+        <v>2930.2</v>
       </c>
       <c r="I57" t="n">
-        <v>-71.02</v>
+        <v>-70.7</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2561.522641 DOT + cash 0.00</t>
+          <t>2577.583471 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ETH/ATOM</t>
+          <t>ICP/DOT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -9102,10 +9102,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>967</v>
+        <v>1059</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -9114,14 +9114,14 @@
         <v>10000</v>
       </c>
       <c r="H58" t="n">
-        <v>2851.65</v>
+        <v>2911.94</v>
       </c>
       <c r="I58" t="n">
-        <v>-71.48</v>
+        <v>-70.88</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>1721.284500 ATOM + cash 0.00</t>
+          <t>2561.522641 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -9154,10 +9154,10 @@
         <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>2754.07</v>
+        <v>2767.22</v>
       </c>
       <c r="I59" t="n">
-        <v>-72.45999999999999</v>
+        <v>-72.33</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -9194,10 +9194,10 @@
         <v>10000</v>
       </c>
       <c r="H60" t="n">
-        <v>2754.07</v>
+        <v>2767.22</v>
       </c>
       <c r="I60" t="n">
-        <v>-72.45999999999999</v>
+        <v>-72.33</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -9234,10 +9234,10 @@
         <v>10000</v>
       </c>
       <c r="H61" t="n">
-        <v>2575.06</v>
+        <v>2647.96</v>
       </c>
       <c r="I61" t="n">
-        <v>-74.25</v>
+        <v>-73.52</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -9274,10 +9274,10 @@
         <v>10000</v>
       </c>
       <c r="H62" t="n">
-        <v>2529.98</v>
+        <v>2601.6</v>
       </c>
       <c r="I62" t="n">
-        <v>-74.7</v>
+        <v>-73.98</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -9314,10 +9314,10 @@
         <v>10000</v>
       </c>
       <c r="H63" t="n">
-        <v>2456.44</v>
+        <v>2525.98</v>
       </c>
       <c r="I63" t="n">
-        <v>-75.44</v>
+        <v>-74.73999999999999</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -9354,10 +9354,10 @@
         <v>10000</v>
       </c>
       <c r="H64" t="n">
-        <v>2429.11</v>
+        <v>2497.88</v>
       </c>
       <c r="I64" t="n">
-        <v>-75.70999999999999</v>
+        <v>-75.02</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -9394,10 +9394,10 @@
         <v>10000</v>
       </c>
       <c r="H65" t="n">
-        <v>2396.27</v>
+        <v>2464.1</v>
       </c>
       <c r="I65" t="n">
-        <v>-76.04000000000001</v>
+        <v>-75.36</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -9434,10 +9434,10 @@
         <v>10000</v>
       </c>
       <c r="H66" t="n">
-        <v>2390.39</v>
+        <v>2458.06</v>
       </c>
       <c r="I66" t="n">
-        <v>-76.09999999999999</v>
+        <v>-75.42</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -9474,10 +9474,10 @@
         <v>10000</v>
       </c>
       <c r="H67" t="n">
-        <v>2277</v>
+        <v>2341.46</v>
       </c>
       <c r="I67" t="n">
-        <v>-77.23</v>
+        <v>-76.59</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -9514,10 +9514,10 @@
         <v>10000</v>
       </c>
       <c r="H68" t="n">
-        <v>894.08</v>
+        <v>889.1900000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>-91.06</v>
+        <v>-91.11</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -9554,10 +9554,10 @@
         <v>10000</v>
       </c>
       <c r="H69" t="n">
-        <v>889.1900000000001</v>
+        <v>884.33</v>
       </c>
       <c r="I69" t="n">
-        <v>-91.11</v>
+        <v>-91.16</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -9594,10 +9594,10 @@
         <v>10000</v>
       </c>
       <c r="H70" t="n">
-        <v>686.39</v>
+        <v>682.63</v>
       </c>
       <c r="I70" t="n">
-        <v>-93.14</v>
+        <v>-93.17</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -9634,10 +9634,10 @@
         <v>10000</v>
       </c>
       <c r="H71" t="n">
-        <v>684.14</v>
+        <v>680.39</v>
       </c>
       <c r="I71" t="n">
-        <v>-93.16</v>
+        <v>-93.2</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -9674,10 +9674,10 @@
         <v>10000</v>
       </c>
       <c r="H72" t="n">
-        <v>591.45</v>
+        <v>588.22</v>
       </c>
       <c r="I72" t="n">
-        <v>-94.09</v>
+        <v>-94.12</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -9714,10 +9714,10 @@
         <v>10000</v>
       </c>
       <c r="H73" t="n">
-        <v>589.48</v>
+        <v>586.25</v>
       </c>
       <c r="I73" t="n">
-        <v>-94.11</v>
+        <v>-94.14</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -9754,10 +9754,10 @@
         <v>10000</v>
       </c>
       <c r="H74" t="n">
-        <v>586.28</v>
+        <v>583.0700000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>-94.14</v>
+        <v>-94.17</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -9794,10 +9794,10 @@
         <v>10000</v>
       </c>
       <c r="H75" t="n">
-        <v>579.58</v>
+        <v>576.4</v>
       </c>
       <c r="I75" t="n">
-        <v>-94.2</v>
+        <v>-94.23999999999999</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -9834,10 +9834,10 @@
         <v>10000</v>
       </c>
       <c r="H76" t="n">
-        <v>571.42</v>
+        <v>568.3</v>
       </c>
       <c r="I76" t="n">
-        <v>-94.29000000000001</v>
+        <v>-94.31999999999999</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -9874,10 +9874,10 @@
         <v>10000</v>
       </c>
       <c r="H77" t="n">
-        <v>569.34</v>
+        <v>566.22</v>
       </c>
       <c r="I77" t="n">
-        <v>-94.31</v>
+        <v>-94.34</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -9914,10 +9914,10 @@
         <v>10000</v>
       </c>
       <c r="H78" t="n">
-        <v>566.59</v>
+        <v>563.49</v>
       </c>
       <c r="I78" t="n">
-        <v>-94.33</v>
+        <v>-94.37</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -9954,10 +9954,10 @@
         <v>10000</v>
       </c>
       <c r="H79" t="n">
-        <v>541.08</v>
+        <v>538.12</v>
       </c>
       <c r="I79" t="n">
-        <v>-94.59</v>
+        <v>-94.62</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -10060,10 +10060,10 @@
         <v>10000</v>
       </c>
       <c r="H2" t="n">
-        <v>106213.07</v>
+        <v>107183.48</v>
       </c>
       <c r="I2" t="n">
-        <v>962.13</v>
+        <v>971.83</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -10100,10 +10100,10 @@
         <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>97683.25</v>
+        <v>99179.66</v>
       </c>
       <c r="I3" t="n">
-        <v>876.83</v>
+        <v>891.8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -10140,10 +10140,10 @@
         <v>10000</v>
       </c>
       <c r="H4" t="n">
-        <v>96270.69</v>
+        <v>98659.23</v>
       </c>
       <c r="I4" t="n">
-        <v>862.71</v>
+        <v>886.59</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -10180,10 +10180,10 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>90776.22</v>
+        <v>92827.42999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>807.76</v>
+        <v>828.27</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -10220,10 +10220,10 @@
         <v>10000</v>
       </c>
       <c r="H6" t="n">
-        <v>63248.86</v>
+        <v>64282.32</v>
       </c>
       <c r="I6" t="n">
-        <v>532.49</v>
+        <v>542.8200000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -10260,10 +10260,10 @@
         <v>10000</v>
       </c>
       <c r="H7" t="n">
-        <v>62401.79</v>
+        <v>61879.54</v>
       </c>
       <c r="I7" t="n">
-        <v>524.02</v>
+        <v>518.8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -10300,10 +10300,10 @@
         <v>10000</v>
       </c>
       <c r="H8" t="n">
-        <v>55532.28</v>
+        <v>55767.59</v>
       </c>
       <c r="I8" t="n">
-        <v>455.32</v>
+        <v>457.68</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -10340,10 +10340,10 @@
         <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>54417.4</v>
+        <v>54651.29</v>
       </c>
       <c r="I9" t="n">
-        <v>444.17</v>
+        <v>446.51</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -10380,10 +10380,10 @@
         <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>53105.81</v>
+        <v>53334.07</v>
       </c>
       <c r="I10" t="n">
-        <v>431.06</v>
+        <v>433.34</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -10420,10 +10420,10 @@
         <v>10000</v>
       </c>
       <c r="H11" t="n">
-        <v>51340.15</v>
+        <v>52500.25</v>
       </c>
       <c r="I11" t="n">
-        <v>413.4</v>
+        <v>425</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BTC/NEAR</t>
+          <t>AAVE/BTC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -10448,10 +10448,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>966</v>
+        <v>533</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -10460,14 +10460,14 @@
         <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>51234.47</v>
+        <v>51367.67</v>
       </c>
       <c r="I12" t="n">
-        <v>412.34</v>
+        <v>413.68</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13787.531741 NEAR + cash 0.00</t>
+          <t>366.912175 AAVE + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AAVE/BTC</t>
+          <t>BTC/NEAR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>533</v>
+        <v>966</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -10500,14 +10500,14 @@
         <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>50592.64</v>
+        <v>50805.68</v>
       </c>
       <c r="I13" t="n">
-        <v>405.93</v>
+        <v>408.06</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>366.912175 AAVE + cash 0.00</t>
+          <t>13787.531741 NEAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -10540,10 +10540,10 @@
         <v>10000</v>
       </c>
       <c r="H14" t="n">
-        <v>44166.31</v>
+        <v>44353.46</v>
       </c>
       <c r="I14" t="n">
-        <v>341.66</v>
+        <v>343.53</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -10580,10 +10580,10 @@
         <v>10000</v>
       </c>
       <c r="H15" t="n">
-        <v>43381.37</v>
+        <v>44090.2</v>
       </c>
       <c r="I15" t="n">
-        <v>333.81</v>
+        <v>340.9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -10620,10 +10620,10 @@
         <v>10000</v>
       </c>
       <c r="H16" t="n">
-        <v>42074.73</v>
+        <v>41722.59</v>
       </c>
       <c r="I16" t="n">
-        <v>320.75</v>
+        <v>317.23</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -10660,10 +10660,10 @@
         <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>40360.37</v>
+        <v>41272.37</v>
       </c>
       <c r="I17" t="n">
-        <v>303.6</v>
+        <v>312.72</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -10700,10 +10700,10 @@
         <v>10000</v>
       </c>
       <c r="H18" t="n">
-        <v>39062.88</v>
+        <v>38735.95</v>
       </c>
       <c r="I18" t="n">
-        <v>290.63</v>
+        <v>287.36</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -10740,10 +10740,10 @@
         <v>10000</v>
       </c>
       <c r="H19" t="n">
-        <v>38976.6</v>
+        <v>38650.4</v>
       </c>
       <c r="I19" t="n">
-        <v>289.77</v>
+        <v>286.5</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -10780,10 +10780,10 @@
         <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>37706.28</v>
+        <v>38641.8</v>
       </c>
       <c r="I20" t="n">
-        <v>277.06</v>
+        <v>286.42</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -10820,10 +10820,10 @@
         <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>34937.46</v>
+        <v>35472.67</v>
       </c>
       <c r="I21" t="n">
-        <v>249.37</v>
+        <v>254.73</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -10860,10 +10860,10 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>32751.3</v>
+        <v>33491.37</v>
       </c>
       <c r="I22" t="n">
-        <v>227.51</v>
+        <v>234.91</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -10900,10 +10900,10 @@
         <v>10000</v>
       </c>
       <c r="H23" t="n">
-        <v>29917.16</v>
+        <v>30341.52</v>
       </c>
       <c r="I23" t="n">
-        <v>199.17</v>
+        <v>203.42</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -10940,10 +10940,10 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>29725.13</v>
+        <v>29852.9</v>
       </c>
       <c r="I24" t="n">
-        <v>197.25</v>
+        <v>198.53</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -10980,10 +10980,10 @@
         <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>25908.68</v>
+        <v>26494.12</v>
       </c>
       <c r="I25" t="n">
-        <v>159.09</v>
+        <v>164.94</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -11020,10 +11020,10 @@
         <v>10000</v>
       </c>
       <c r="H26" t="n">
-        <v>23030.96</v>
+        <v>23407.27</v>
       </c>
       <c r="I26" t="n">
-        <v>130.31</v>
+        <v>134.07</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -11060,10 +11060,10 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>22870.74</v>
+        <v>22969.04</v>
       </c>
       <c r="I27" t="n">
-        <v>128.71</v>
+        <v>129.69</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -11100,10 +11100,10 @@
         <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>21246.86</v>
+        <v>21548.24</v>
       </c>
       <c r="I28" t="n">
-        <v>112.47</v>
+        <v>115.48</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -11140,10 +11140,10 @@
         <v>10000</v>
       </c>
       <c r="H29" t="n">
-        <v>20906.42</v>
+        <v>21425.12</v>
       </c>
       <c r="I29" t="n">
-        <v>109.06</v>
+        <v>114.25</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -11180,10 +11180,10 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>19496.1</v>
+        <v>19936.65</v>
       </c>
       <c r="I30" t="n">
-        <v>94.95999999999999</v>
+        <v>99.37</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -11220,10 +11220,10 @@
         <v>10000</v>
       </c>
       <c r="H31" t="n">
-        <v>19091.93</v>
+        <v>19362.74</v>
       </c>
       <c r="I31" t="n">
-        <v>90.92</v>
+        <v>93.63</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -11260,10 +11260,10 @@
         <v>10000</v>
       </c>
       <c r="H32" t="n">
-        <v>18831.97</v>
+        <v>19139.68</v>
       </c>
       <c r="I32" t="n">
-        <v>88.31999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         <v>10000</v>
       </c>
       <c r="H33" t="n">
-        <v>18172.19</v>
+        <v>18469.11</v>
       </c>
       <c r="I33" t="n">
-        <v>81.72</v>
+        <v>84.69</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -11340,10 +11340,10 @@
         <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>18085.89</v>
+        <v>18381.4</v>
       </c>
       <c r="I34" t="n">
-        <v>80.86</v>
+        <v>83.81</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -11380,10 +11380,10 @@
         <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>17630.99</v>
+        <v>17881.08</v>
       </c>
       <c r="I35" t="n">
-        <v>76.31</v>
+        <v>78.81</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -11420,10 +11420,10 @@
         <v>10000</v>
       </c>
       <c r="H36" t="n">
-        <v>15907.55</v>
+        <v>16167.47</v>
       </c>
       <c r="I36" t="n">
-        <v>59.08</v>
+        <v>61.67</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -11460,10 +11460,10 @@
         <v>10000</v>
       </c>
       <c r="H37" t="n">
-        <v>15481.03</v>
+        <v>15700.62</v>
       </c>
       <c r="I37" t="n">
-        <v>54.81</v>
+        <v>57.01</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -11500,10 +11500,10 @@
         <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>14766.62</v>
+        <v>15132.99</v>
       </c>
       <c r="I38" t="n">
-        <v>47.67</v>
+        <v>51.33</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -11540,10 +11540,10 @@
         <v>10000</v>
       </c>
       <c r="H39" t="n">
-        <v>13562.49</v>
+        <v>13898.98</v>
       </c>
       <c r="I39" t="n">
-        <v>35.62</v>
+        <v>38.99</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -11580,10 +11580,10 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>13176.6</v>
+        <v>13503.52</v>
       </c>
       <c r="I40" t="n">
-        <v>31.77</v>
+        <v>35.04</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -11620,10 +11620,10 @@
         <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>13032.12</v>
+        <v>13216.98</v>
       </c>
       <c r="I41" t="n">
-        <v>30.32</v>
+        <v>32.17</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -11660,10 +11660,10 @@
         <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>12849.55</v>
+        <v>13031.81</v>
       </c>
       <c r="I42" t="n">
-        <v>28.5</v>
+        <v>30.32</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -11700,10 +11700,10 @@
         <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>12583.76</v>
+        <v>12895.97</v>
       </c>
       <c r="I43" t="n">
-        <v>25.84</v>
+        <v>28.96</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -11740,10 +11740,10 @@
         <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>12115.87</v>
+        <v>12416.48</v>
       </c>
       <c r="I44" t="n">
-        <v>21.16</v>
+        <v>24.16</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -11780,10 +11780,10 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>11161.97</v>
+        <v>11320.29</v>
       </c>
       <c r="I45" t="n">
-        <v>11.62</v>
+        <v>13.2</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -11820,10 +11820,10 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>11024</v>
+        <v>11180.36</v>
       </c>
       <c r="I46" t="n">
-        <v>10.24</v>
+        <v>11.8</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -11860,10 +11860,10 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>5924.33</v>
+        <v>6092.04</v>
       </c>
       <c r="I47" t="n">
-        <v>-40.76</v>
+        <v>-39.08</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -11900,10 +11900,10 @@
         <v>10000</v>
       </c>
       <c r="H48" t="n">
-        <v>3792.58</v>
+        <v>3810.68</v>
       </c>
       <c r="I48" t="n">
-        <v>-62.07</v>
+        <v>-61.89</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -11940,10 +11940,10 @@
         <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>3235.26</v>
+        <v>3326.85</v>
       </c>
       <c r="I49" t="n">
-        <v>-67.65000000000001</v>
+        <v>-66.73</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -11980,10 +11980,10 @@
         <v>10000</v>
       </c>
       <c r="H50" t="n">
-        <v>3213.92</v>
+        <v>3229.26</v>
       </c>
       <c r="I50" t="n">
-        <v>-67.86</v>
+        <v>-67.70999999999999</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -12020,10 +12020,10 @@
         <v>10000</v>
       </c>
       <c r="H51" t="n">
-        <v>3168.17</v>
+        <v>3183.29</v>
       </c>
       <c r="I51" t="n">
-        <v>-68.31999999999999</v>
+        <v>-68.17</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -12060,10 +12060,10 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>3126.26</v>
+        <v>3141.18</v>
       </c>
       <c r="I52" t="n">
-        <v>-68.73999999999999</v>
+        <v>-68.59</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -12100,10 +12100,10 @@
         <v>10000</v>
       </c>
       <c r="H53" t="n">
-        <v>3107.43</v>
+        <v>3122.26</v>
       </c>
       <c r="I53" t="n">
-        <v>-68.93000000000001</v>
+        <v>-68.78</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -12140,10 +12140,10 @@
         <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>3054.99</v>
+        <v>3069.57</v>
       </c>
       <c r="I54" t="n">
-        <v>-69.45</v>
+        <v>-69.3</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ADA/DOT</t>
+          <t>AAVE/ATOM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -12168,10 +12168,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>910</v>
+        <v>933</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -12180,14 +12180,14 @@
         <v>10000</v>
       </c>
       <c r="H55" t="n">
-        <v>2968.53</v>
+        <v>3041.6</v>
       </c>
       <c r="I55" t="n">
-        <v>-70.31</v>
+        <v>-69.58</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2623.768625 DOT + cash 0.00</t>
+          <t>1785.393146 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -12199,7 +12199,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AAVE/ATOM</t>
+          <t>ADA/DOT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -12208,10 +12208,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>933</v>
+        <v>910</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -12220,14 +12220,14 @@
         <v>10000</v>
       </c>
       <c r="H56" t="n">
-        <v>2957.86</v>
+        <v>2982.7</v>
       </c>
       <c r="I56" t="n">
-        <v>-70.42</v>
+        <v>-70.17</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1785.393146 ATOM + cash 0.00</t>
+          <t>2623.768625 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -12260,10 +12260,10 @@
         <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>2898.11</v>
+        <v>2911.94</v>
       </c>
       <c r="I57" t="n">
-        <v>-71.02</v>
+        <v>-70.88</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -12300,10 +12300,10 @@
         <v>10000</v>
       </c>
       <c r="H58" t="n">
-        <v>2754.07</v>
+        <v>2767.22</v>
       </c>
       <c r="I58" t="n">
-        <v>-72.45999999999999</v>
+        <v>-72.33</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -12340,10 +12340,10 @@
         <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>2754.07</v>
+        <v>2767.22</v>
       </c>
       <c r="I59" t="n">
-        <v>-72.45999999999999</v>
+        <v>-72.33</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -12380,10 +12380,10 @@
         <v>10000</v>
       </c>
       <c r="H60" t="n">
-        <v>2678.8</v>
+        <v>2754.63</v>
       </c>
       <c r="I60" t="n">
-        <v>-73.20999999999999</v>
+        <v>-72.45</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -12420,10 +12420,10 @@
         <v>10000</v>
       </c>
       <c r="H61" t="n">
-        <v>2575.06</v>
+        <v>2647.96</v>
       </c>
       <c r="I61" t="n">
-        <v>-74.25</v>
+        <v>-73.52</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -12460,10 +12460,10 @@
         <v>10000</v>
       </c>
       <c r="H62" t="n">
-        <v>2529.98</v>
+        <v>2601.6</v>
       </c>
       <c r="I62" t="n">
-        <v>-74.7</v>
+        <v>-73.98</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -12500,10 +12500,10 @@
         <v>10000</v>
       </c>
       <c r="H63" t="n">
-        <v>2456.44</v>
+        <v>2525.98</v>
       </c>
       <c r="I63" t="n">
-        <v>-75.44</v>
+        <v>-74.73999999999999</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -12540,10 +12540,10 @@
         <v>10000</v>
       </c>
       <c r="H64" t="n">
-        <v>2443.88</v>
+        <v>2513.06</v>
       </c>
       <c r="I64" t="n">
-        <v>-75.56</v>
+        <v>-74.87</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -12580,10 +12580,10 @@
         <v>10000</v>
       </c>
       <c r="H65" t="n">
-        <v>2429.11</v>
+        <v>2497.88</v>
       </c>
       <c r="I65" t="n">
-        <v>-75.70999999999999</v>
+        <v>-75.02</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -12620,10 +12620,10 @@
         <v>10000</v>
       </c>
       <c r="H66" t="n">
-        <v>2428.48</v>
+        <v>2497.23</v>
       </c>
       <c r="I66" t="n">
-        <v>-75.72</v>
+        <v>-75.03</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -12660,10 +12660,10 @@
         <v>10000</v>
       </c>
       <c r="H67" t="n">
-        <v>2390.39</v>
+        <v>2458.06</v>
       </c>
       <c r="I67" t="n">
-        <v>-76.09999999999999</v>
+        <v>-75.42</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -12700,10 +12700,10 @@
         <v>10000</v>
       </c>
       <c r="H68" t="n">
-        <v>2277</v>
+        <v>2341.46</v>
       </c>
       <c r="I68" t="n">
-        <v>-77.23</v>
+        <v>-76.59</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -12740,10 +12740,10 @@
         <v>10000</v>
       </c>
       <c r="H69" t="n">
-        <v>1773.52</v>
+        <v>1763.81</v>
       </c>
       <c r="I69" t="n">
-        <v>-82.26000000000001</v>
+        <v>-82.36</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -12780,10 +12780,10 @@
         <v>10000</v>
       </c>
       <c r="H70" t="n">
-        <v>889.1900000000001</v>
+        <v>884.33</v>
       </c>
       <c r="I70" t="n">
-        <v>-91.11</v>
+        <v>-91.16</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -12820,10 +12820,10 @@
         <v>10000</v>
       </c>
       <c r="H71" t="n">
-        <v>686.39</v>
+        <v>682.63</v>
       </c>
       <c r="I71" t="n">
-        <v>-93.14</v>
+        <v>-93.17</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -12860,10 +12860,10 @@
         <v>10000</v>
       </c>
       <c r="H72" t="n">
-        <v>591.45</v>
+        <v>588.22</v>
       </c>
       <c r="I72" t="n">
-        <v>-94.09</v>
+        <v>-94.12</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -12900,10 +12900,10 @@
         <v>10000</v>
       </c>
       <c r="H73" t="n">
-        <v>589.48</v>
+        <v>586.25</v>
       </c>
       <c r="I73" t="n">
-        <v>-94.11</v>
+        <v>-94.14</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -12940,10 +12940,10 @@
         <v>10000</v>
       </c>
       <c r="H74" t="n">
-        <v>586.28</v>
+        <v>583.0700000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>-94.14</v>
+        <v>-94.17</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -12980,10 +12980,10 @@
         <v>10000</v>
       </c>
       <c r="H75" t="n">
-        <v>579.58</v>
+        <v>576.4</v>
       </c>
       <c r="I75" t="n">
-        <v>-94.2</v>
+        <v>-94.23999999999999</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -13020,10 +13020,10 @@
         <v>10000</v>
       </c>
       <c r="H76" t="n">
-        <v>571.42</v>
+        <v>568.3</v>
       </c>
       <c r="I76" t="n">
-        <v>-94.29000000000001</v>
+        <v>-94.31999999999999</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -13060,10 +13060,10 @@
         <v>10000</v>
       </c>
       <c r="H77" t="n">
-        <v>569.34</v>
+        <v>566.22</v>
       </c>
       <c r="I77" t="n">
-        <v>-94.31</v>
+        <v>-94.34</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -13100,10 +13100,10 @@
         <v>10000</v>
       </c>
       <c r="H78" t="n">
-        <v>566.59</v>
+        <v>563.49</v>
       </c>
       <c r="I78" t="n">
-        <v>-94.33</v>
+        <v>-94.37</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -13140,10 +13140,10 @@
         <v>10000</v>
       </c>
       <c r="H79" t="n">
-        <v>541.08</v>
+        <v>538.12</v>
       </c>
       <c r="I79" t="n">
-        <v>-94.59</v>
+        <v>-94.62</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -13246,10 +13246,10 @@
         <v>10000</v>
       </c>
       <c r="H2" t="n">
-        <v>14728.41</v>
+        <v>14969.06</v>
       </c>
       <c r="I2" t="n">
-        <v>47.28</v>
+        <v>49.69</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -13286,10 +13286,10 @@
         <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>14392.55</v>
+        <v>14627.72</v>
       </c>
       <c r="I3" t="n">
-        <v>43.93</v>
+        <v>46.28</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -13326,10 +13326,10 @@
         <v>10000</v>
       </c>
       <c r="H4" t="n">
-        <v>12936.75</v>
+        <v>12912.92</v>
       </c>
       <c r="I4" t="n">
-        <v>29.37</v>
+        <v>29.13</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -13345,19 +13345,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ZRO/NEAR</t>
+          <t>NEAR/BNB</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -13366,14 +13366,14 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>11302.93</v>
+        <v>11359.63</v>
       </c>
       <c r="I5" t="n">
-        <v>13.03</v>
+        <v>13.6</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9419.108519 ZRO + cash 0.00</t>
+          <t>14.840841 BNB + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -13385,19 +13385,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NEAR/BNB</t>
+          <t>ZRO/NEAR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -13406,14 +13406,14 @@
         <v>10000</v>
       </c>
       <c r="H6" t="n">
-        <v>11256.78</v>
+        <v>11302.93</v>
       </c>
       <c r="I6" t="n">
-        <v>12.57</v>
+        <v>13.03</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14.840841 BNB + cash 0.00</t>
+          <t>9419.108519 ZRO + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -13526,10 +13526,10 @@
         <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>10383.11</v>
+        <v>10530.39</v>
       </c>
       <c r="I9" t="n">
-        <v>3.83</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -13566,10 +13566,10 @@
         <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>10127.78</v>
+        <v>10271.44</v>
       </c>
       <c r="I10" t="n">
-        <v>1.28</v>
+        <v>2.71</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -13646,10 +13646,10 @@
         <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>9682.27</v>
+        <v>9723.299999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.18</v>
+        <v>-2.77</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -13686,10 +13686,10 @@
         <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>9342.48</v>
+        <v>9475</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.58</v>
+        <v>-5.25</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -13726,10 +13726,10 @@
         <v>10000</v>
       </c>
       <c r="H14" t="n">
-        <v>8942</v>
+        <v>9023.690000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-10.58</v>
+        <v>-9.76</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -13806,10 +13806,10 @@
         <v>10000</v>
       </c>
       <c r="H16" t="n">
-        <v>8250.99</v>
+        <v>8286.450000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-17.49</v>
+        <v>-17.14</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ICP/BTC</t>
+          <t>LINK/NEAR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -13834,10 +13834,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>288</v>
+        <v>129</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -13846,14 +13846,14 @@
         <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>8097.59</v>
+        <v>8271.92</v>
       </c>
       <c r="I17" t="n">
-        <v>-19.02</v>
+        <v>-17.28</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2871.486789 ICP + cash 0.00</t>
+          <t>667.343584 LINK + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LINK/NEAR</t>
+          <t>ICP/BTC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -13874,10 +13874,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>129</v>
+        <v>288</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -13886,14 +13886,14 @@
         <v>10000</v>
       </c>
       <c r="H18" t="n">
-        <v>8089.14</v>
+        <v>8212.450000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-19.11</v>
+        <v>-17.88</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>667.343584 LINK + cash 0.00</t>
+          <t>2871.486789 ICP + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -13905,7 +13905,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BTC/BNB</t>
+          <t>AAVE/ATOM</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -13914,10 +13914,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>181</v>
+        <v>104</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -13926,14 +13926,14 @@
         <v>10000</v>
       </c>
       <c r="H19" t="n">
-        <v>8043.32</v>
+        <v>8104.39</v>
       </c>
       <c r="I19" t="n">
-        <v>-19.57</v>
+        <v>-18.96</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.099576 BTC + cash 0.00</t>
+          <t>4757.212175 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -13945,7 +13945,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AAVE/ATOM</t>
+          <t>BTC/BNB</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -13954,10 +13954,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>104</v>
+        <v>181</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -13966,14 +13966,14 @@
         <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>7881.27</v>
+        <v>8077.4</v>
       </c>
       <c r="I20" t="n">
-        <v>-21.19</v>
+        <v>-19.23</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4757.212175 ATOM + cash 0.00</t>
+          <t>0.099576 BTC + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -14006,10 +14006,10 @@
         <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>7718.6</v>
+        <v>7751.31</v>
       </c>
       <c r="I21" t="n">
-        <v>-22.81</v>
+        <v>-22.49</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -14046,10 +14046,10 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>7505.96</v>
+        <v>7620.94</v>
       </c>
       <c r="I22" t="n">
-        <v>-24.94</v>
+        <v>-23.79</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -14086,10 +14086,10 @@
         <v>10000</v>
       </c>
       <c r="H23" t="n">
-        <v>7429.74</v>
+        <v>7535.13</v>
       </c>
       <c r="I23" t="n">
-        <v>-25.7</v>
+        <v>-24.65</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -14126,10 +14126,10 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>6909.29</v>
+        <v>7104.88</v>
       </c>
       <c r="I24" t="n">
-        <v>-30.91</v>
+        <v>-28.95</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ETH/TRX</t>
+          <t>ETH/ATOM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -14154,10 +14154,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>315</v>
+        <v>230</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -14166,14 +14166,14 @@
         <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>6789.35</v>
+        <v>6977.1</v>
       </c>
       <c r="I25" t="n">
-        <v>-32.11</v>
+        <v>-30.23</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2.620096 ETH + cash 0.00</t>
+          <t>4095.504647 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -14185,7 +14185,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ETH/ATOM</t>
+          <t>ETH/TRX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -14194,10 +14194,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>230</v>
+        <v>315</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -14206,14 +14206,14 @@
         <v>10000</v>
       </c>
       <c r="H26" t="n">
-        <v>6785.02</v>
+        <v>6900.28</v>
       </c>
       <c r="I26" t="n">
-        <v>-32.15</v>
+        <v>-31</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>4095.504647 ATOM + cash 0.00</t>
+          <t>2.620096 ETH + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -14246,10 +14246,10 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>6660.26</v>
+        <v>6688.89</v>
       </c>
       <c r="I27" t="n">
-        <v>-33.4</v>
+        <v>-33.11</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -14286,10 +14286,10 @@
         <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>5905.18</v>
+        <v>6038.62</v>
       </c>
       <c r="I28" t="n">
-        <v>-40.95</v>
+        <v>-39.61</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -14326,10 +14326,10 @@
         <v>10000</v>
       </c>
       <c r="H29" t="n">
-        <v>5791.13</v>
+        <v>5885.76</v>
       </c>
       <c r="I29" t="n">
-        <v>-42.09</v>
+        <v>-41.14</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -14366,10 +14366,10 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>5791.13</v>
+        <v>5885.76</v>
       </c>
       <c r="I30" t="n">
-        <v>-42.09</v>
+        <v>-41.14</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -14406,10 +14406,10 @@
         <v>10000</v>
       </c>
       <c r="H31" t="n">
-        <v>5762.64</v>
+        <v>5850.92</v>
       </c>
       <c r="I31" t="n">
-        <v>-42.37</v>
+        <v>-41.49</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -14446,10 +14446,10 @@
         <v>10000</v>
       </c>
       <c r="H32" t="n">
-        <v>5607.55</v>
+        <v>5766.29</v>
       </c>
       <c r="I32" t="n">
-        <v>-43.92</v>
+        <v>-42.34</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -14486,10 +14486,10 @@
         <v>10000</v>
       </c>
       <c r="H33" t="n">
-        <v>5386.2</v>
+        <v>5507.91</v>
       </c>
       <c r="I33" t="n">
-        <v>-46.14</v>
+        <v>-44.92</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -14526,10 +14526,10 @@
         <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>5332.06</v>
+        <v>5483.01</v>
       </c>
       <c r="I34" t="n">
-        <v>-46.68</v>
+        <v>-45.17</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -14545,19 +14545,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ZRO/HBAR</t>
+          <t>ICP/AAVE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -14566,14 +14566,14 @@
         <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>5245.11</v>
+        <v>5299.67</v>
       </c>
       <c r="I35" t="n">
-        <v>-47.55</v>
+        <v>-47</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>66111.832284 HBAR + cash 0.00</t>
+          <t>37.854819 AAVE + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -14585,19 +14585,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ICP/AAVE</t>
+          <t>ZRO/HBAR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -14606,14 +14606,14 @@
         <v>10000</v>
       </c>
       <c r="H36" t="n">
-        <v>5219.71</v>
+        <v>5267.66</v>
       </c>
       <c r="I36" t="n">
-        <v>-47.8</v>
+        <v>-47.32</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>37.854819 AAVE + cash 0.00</t>
+          <t>66111.832284 HBAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -14646,10 +14646,10 @@
         <v>10000</v>
       </c>
       <c r="H37" t="n">
-        <v>5135.23</v>
+        <v>5251.27</v>
       </c>
       <c r="I37" t="n">
-        <v>-48.65</v>
+        <v>-47.49</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -14686,10 +14686,10 @@
         <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>5135.23</v>
+        <v>5251.27</v>
       </c>
       <c r="I38" t="n">
-        <v>-48.65</v>
+        <v>-47.49</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -14726,10 +14726,10 @@
         <v>10000</v>
       </c>
       <c r="H39" t="n">
-        <v>5135.23</v>
+        <v>5251.27</v>
       </c>
       <c r="I39" t="n">
-        <v>-48.65</v>
+        <v>-47.49</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -14766,10 +14766,10 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>5135.23</v>
+        <v>5251.27</v>
       </c>
       <c r="I40" t="n">
-        <v>-48.65</v>
+        <v>-47.49</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -14806,10 +14806,10 @@
         <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>4842.74</v>
+        <v>4916.92</v>
       </c>
       <c r="I41" t="n">
-        <v>-51.57</v>
+        <v>-50.83</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -14846,10 +14846,10 @@
         <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>4819.38</v>
+        <v>4893.21</v>
       </c>
       <c r="I42" t="n">
-        <v>-51.81</v>
+        <v>-51.07</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>4636.89</v>
+        <v>4656.82</v>
       </c>
       <c r="I43" t="n">
-        <v>-53.63</v>
+        <v>-53.43</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -14926,10 +14926,10 @@
         <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>4570.83</v>
+        <v>4640.86</v>
       </c>
       <c r="I44" t="n">
-        <v>-54.29</v>
+        <v>-53.59</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -14966,10 +14966,10 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>4570.83</v>
+        <v>4640.86</v>
       </c>
       <c r="I45" t="n">
-        <v>-54.29</v>
+        <v>-53.59</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -15006,10 +15006,10 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>4570.83</v>
+        <v>4640.86</v>
       </c>
       <c r="I46" t="n">
-        <v>-54.29</v>
+        <v>-53.59</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -15046,10 +15046,10 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>4324.46</v>
+        <v>4343.05</v>
       </c>
       <c r="I47" t="n">
-        <v>-56.76</v>
+        <v>-56.57</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DOT/XCH</t>
+          <t>BTC/ATOM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -15074,10 +15074,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>85</v>
+        <v>348</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -15086,14 +15086,14 @@
         <v>10000</v>
       </c>
       <c r="H48" t="n">
-        <v>3943.19</v>
+        <v>4006.67</v>
       </c>
       <c r="I48" t="n">
-        <v>-60.57</v>
+        <v>-59.93</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2632.476385 XCH + cash 0.00</t>
+          <t>2351.883028 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15105,19 +15105,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BTC/ATOM</t>
+          <t>ZRO/ATOM</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -15126,14 +15126,14 @@
         <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>3896.36</v>
+        <v>3969.73</v>
       </c>
       <c r="I49" t="n">
-        <v>-61.04</v>
+        <v>-60.3</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2351.883028 ATOM + cash 0.00</t>
+          <t>2330.198886 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15145,19 +15145,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ZRO/ATOM</t>
+          <t>DOT/XCH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E50" t="n">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -15166,14 +15166,14 @@
         <v>10000</v>
       </c>
       <c r="H50" t="n">
-        <v>3860.44</v>
+        <v>3921.6</v>
       </c>
       <c r="I50" t="n">
-        <v>-61.4</v>
+        <v>-60.78</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2330.198886 ATOM + cash 0.00</t>
+          <t>2632.476385 XCH + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15206,10 +15206,10 @@
         <v>10000</v>
       </c>
       <c r="H51" t="n">
-        <v>3644.06</v>
+        <v>3747.22</v>
       </c>
       <c r="I51" t="n">
-        <v>-63.56</v>
+        <v>-62.53</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -15246,10 +15246,10 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>3644.06</v>
+        <v>3747.22</v>
       </c>
       <c r="I52" t="n">
-        <v>-63.56</v>
+        <v>-62.53</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -15286,10 +15286,10 @@
         <v>10000</v>
       </c>
       <c r="H53" t="n">
-        <v>3605.34</v>
+        <v>3620.84</v>
       </c>
       <c r="I53" t="n">
-        <v>-63.95</v>
+        <v>-63.79</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -15326,10 +15326,10 @@
         <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>3547.57</v>
+        <v>3564.51</v>
       </c>
       <c r="I54" t="n">
-        <v>-64.52</v>
+        <v>-64.34999999999999</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -15366,10 +15366,10 @@
         <v>10000</v>
       </c>
       <c r="H55" t="n">
-        <v>3548.13</v>
+        <v>3563.38</v>
       </c>
       <c r="I55" t="n">
-        <v>-64.52</v>
+        <v>-64.37</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -15406,10 +15406,10 @@
         <v>10000</v>
       </c>
       <c r="H56" t="n">
-        <v>3511.16</v>
+        <v>3526.25</v>
       </c>
       <c r="I56" t="n">
-        <v>-64.89</v>
+        <v>-64.73999999999999</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -15446,10 +15446,10 @@
         <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>3494.22</v>
+        <v>3509.24</v>
       </c>
       <c r="I57" t="n">
-        <v>-65.06</v>
+        <v>-64.91</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -15486,10 +15486,10 @@
         <v>10000</v>
       </c>
       <c r="H58" t="n">
-        <v>3328.54</v>
+        <v>3342.84</v>
       </c>
       <c r="I58" t="n">
-        <v>-66.70999999999999</v>
+        <v>-66.56999999999999</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -15526,10 +15526,10 @@
         <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>3192.65</v>
+        <v>3175.17</v>
       </c>
       <c r="I59" t="n">
-        <v>-68.06999999999999</v>
+        <v>-68.25</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -15566,10 +15566,10 @@
         <v>10000</v>
       </c>
       <c r="H60" t="n">
-        <v>3145.59</v>
+        <v>3160.6</v>
       </c>
       <c r="I60" t="n">
-        <v>-68.54000000000001</v>
+        <v>-68.39</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -15606,10 +15606,10 @@
         <v>10000</v>
       </c>
       <c r="H61" t="n">
-        <v>2973.41</v>
+        <v>2987.6</v>
       </c>
       <c r="I61" t="n">
-        <v>-70.27</v>
+        <v>-70.12</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -15646,10 +15646,10 @@
         <v>10000</v>
       </c>
       <c r="H62" t="n">
-        <v>2945.85</v>
+        <v>2959.91</v>
       </c>
       <c r="I62" t="n">
-        <v>-70.54000000000001</v>
+        <v>-70.40000000000001</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AAVE/XCH</t>
+          <t>ADA/NEAR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -15674,10 +15674,10 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>210</v>
+        <v>274</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -15686,14 +15686,14 @@
         <v>10000</v>
       </c>
       <c r="H63" t="n">
-        <v>2890.92</v>
+        <v>2915.67</v>
       </c>
       <c r="I63" t="n">
-        <v>-71.09</v>
+        <v>-70.84</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>1929.983353 XCH + cash 0.00</t>
+          <t>13047.794641 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ADA/NEAR</t>
+          <t>AAVE/XCH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -15714,10 +15714,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>274</v>
+        <v>210</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -15726,14 +15726,14 @@
         <v>10000</v>
       </c>
       <c r="H64" t="n">
-        <v>2845.08</v>
+        <v>2875.1</v>
       </c>
       <c r="I64" t="n">
-        <v>-71.55</v>
+        <v>-71.25</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>13047.794641 ADA + cash 0.00</t>
+          <t>1929.983353 XCH + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15745,7 +15745,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DOT/NEAR</t>
+          <t>ADA/ATOM</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -15757,7 +15757,7 @@
         <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -15766,14 +15766,14 @@
         <v>10000</v>
       </c>
       <c r="H65" t="n">
-        <v>2816.46</v>
+        <v>2870.25</v>
       </c>
       <c r="I65" t="n">
-        <v>-71.84</v>
+        <v>-71.3</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2489.356202 DOT + cash 0.00</t>
+          <t>12844.538258 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DOT/HBAR</t>
+          <t>DOT/NEAR</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -15797,7 +15797,7 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -15806,14 +15806,14 @@
         <v>10000</v>
       </c>
       <c r="H66" t="n">
-        <v>2813.07</v>
+        <v>2829.9</v>
       </c>
       <c r="I66" t="n">
-        <v>-71.87</v>
+        <v>-71.7</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2486.362185 DOT + cash 0.00</t>
+          <t>2489.356202 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15825,7 +15825,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ADA/ATOM</t>
+          <t>DOT/HBAR</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -15837,7 +15837,7 @@
         <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -15846,14 +15846,14 @@
         <v>10000</v>
       </c>
       <c r="H67" t="n">
-        <v>2800.76</v>
+        <v>2826.5</v>
       </c>
       <c r="I67" t="n">
-        <v>-71.98999999999999</v>
+        <v>-71.73999999999999</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>12844.538258 ADA + cash 0.00</t>
+          <t>2486.362185 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15886,10 +15886,10 @@
         <v>10000</v>
       </c>
       <c r="H68" t="n">
-        <v>2776.94</v>
+        <v>2790.2</v>
       </c>
       <c r="I68" t="n">
-        <v>-72.23</v>
+        <v>-72.09999999999999</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -15926,10 +15926,10 @@
         <v>10000</v>
       </c>
       <c r="H69" t="n">
-        <v>2710.9</v>
+        <v>2778.16</v>
       </c>
       <c r="I69" t="n">
-        <v>-72.89</v>
+        <v>-72.22</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -15966,10 +15966,10 @@
         <v>10000</v>
       </c>
       <c r="H70" t="n">
-        <v>2703.3</v>
+        <v>2716.21</v>
       </c>
       <c r="I70" t="n">
-        <v>-72.97</v>
+        <v>-72.84</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -16006,10 +16006,10 @@
         <v>10000</v>
       </c>
       <c r="H71" t="n">
-        <v>2547.22</v>
+        <v>2559.38</v>
       </c>
       <c r="I71" t="n">
-        <v>-74.53</v>
+        <v>-74.41</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -16046,10 +16046,10 @@
         <v>10000</v>
       </c>
       <c r="H72" t="n">
-        <v>2547.22</v>
+        <v>2559.38</v>
       </c>
       <c r="I72" t="n">
-        <v>-74.53</v>
+        <v>-74.41</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -16086,10 +16086,10 @@
         <v>10000</v>
       </c>
       <c r="H73" t="n">
-        <v>2547.22</v>
+        <v>2559.38</v>
       </c>
       <c r="I73" t="n">
-        <v>-74.53</v>
+        <v>-74.41</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -16126,10 +16126,10 @@
         <v>10000</v>
       </c>
       <c r="H74" t="n">
-        <v>2547.22</v>
+        <v>2559.38</v>
       </c>
       <c r="I74" t="n">
-        <v>-74.53</v>
+        <v>-74.41</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -16166,10 +16166,10 @@
         <v>10000</v>
       </c>
       <c r="H75" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I75" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -16206,10 +16206,10 @@
         <v>10000</v>
       </c>
       <c r="H76" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I76" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -16246,10 +16246,10 @@
         <v>10000</v>
       </c>
       <c r="H77" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I77" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -16286,10 +16286,10 @@
         <v>10000</v>
       </c>
       <c r="H78" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I78" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -16326,10 +16326,10 @@
         <v>10000</v>
       </c>
       <c r="H79" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I79" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -16366,10 +16366,10 @@
         <v>10000</v>
       </c>
       <c r="H80" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I80" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -16406,10 +16406,10 @@
         <v>10000</v>
       </c>
       <c r="H81" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I81" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -16446,10 +16446,10 @@
         <v>10000</v>
       </c>
       <c r="H82" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I82" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -16486,10 +16486,10 @@
         <v>10000</v>
       </c>
       <c r="H83" t="n">
-        <v>2407.23</v>
+        <v>2394.06</v>
       </c>
       <c r="I83" t="n">
-        <v>-75.93000000000001</v>
+        <v>-76.06</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -16526,10 +16526,10 @@
         <v>10000</v>
       </c>
       <c r="H84" t="n">
-        <v>2270.6</v>
+        <v>2258.17</v>
       </c>
       <c r="I84" t="n">
-        <v>-77.29000000000001</v>
+        <v>-77.42</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -16566,10 +16566,10 @@
         <v>10000</v>
       </c>
       <c r="H85" t="n">
-        <v>2114.24</v>
+        <v>2102.67</v>
       </c>
       <c r="I85" t="n">
-        <v>-78.86</v>
+        <v>-78.97</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -16606,10 +16606,10 @@
         <v>10000</v>
       </c>
       <c r="H86" t="n">
-        <v>2063.46</v>
+        <v>2052.16</v>
       </c>
       <c r="I86" t="n">
-        <v>-79.37</v>
+        <v>-79.48</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -16646,10 +16646,10 @@
         <v>10000</v>
       </c>
       <c r="H87" t="n">
-        <v>2039.73</v>
+        <v>2028.57</v>
       </c>
       <c r="I87" t="n">
-        <v>-79.59999999999999</v>
+        <v>-79.70999999999999</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -16686,10 +16686,10 @@
         <v>10000</v>
       </c>
       <c r="H88" t="n">
-        <v>1978.83</v>
+        <v>1968</v>
       </c>
       <c r="I88" t="n">
-        <v>-80.20999999999999</v>
+        <v>-80.31999999999999</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -16726,10 +16726,10 @@
         <v>10000</v>
       </c>
       <c r="H89" t="n">
-        <v>1812.51</v>
+        <v>1802.59</v>
       </c>
       <c r="I89" t="n">
-        <v>-81.87</v>
+        <v>-81.97</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -16766,10 +16766,10 @@
         <v>10000</v>
       </c>
       <c r="H90" t="n">
-        <v>1641.26</v>
+        <v>1632.27</v>
       </c>
       <c r="I90" t="n">
-        <v>-83.59</v>
+        <v>-83.68000000000001</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -16806,10 +16806,10 @@
         <v>10000</v>
       </c>
       <c r="H91" t="n">
-        <v>1637.41</v>
+        <v>1628.44</v>
       </c>
       <c r="I91" t="n">
-        <v>-83.63</v>
+        <v>-83.72</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -16846,10 +16846,10 @@
         <v>10000</v>
       </c>
       <c r="H92" t="n">
-        <v>1564.6</v>
+        <v>1556.03</v>
       </c>
       <c r="I92" t="n">
-        <v>-84.34999999999999</v>
+        <v>-84.44</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -16992,10 +16992,10 @@
         <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>13989.55</v>
+        <v>14187.98</v>
       </c>
       <c r="I3" t="n">
-        <v>39.9</v>
+        <v>41.88</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -17072,10 +17072,10 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>12760.33</v>
+        <v>12876.92</v>
       </c>
       <c r="I5" t="n">
-        <v>27.6</v>
+        <v>28.77</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -17112,10 +17112,10 @@
         <v>10000</v>
       </c>
       <c r="H6" t="n">
-        <v>12713.68</v>
+        <v>12767.55</v>
       </c>
       <c r="I6" t="n">
-        <v>27.14</v>
+        <v>27.68</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -17152,10 +17152,10 @@
         <v>10000</v>
       </c>
       <c r="H7" t="n">
-        <v>11625.02</v>
+        <v>11674.98</v>
       </c>
       <c r="I7" t="n">
-        <v>16.25</v>
+        <v>16.75</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -17171,19 +17171,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ZRO/BTC</t>
+          <t>NEAR/BNB</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>171</v>
+        <v>330</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -17192,14 +17192,14 @@
         <v>10000</v>
       </c>
       <c r="H8" t="n">
-        <v>11562.05</v>
+        <v>11658.05</v>
       </c>
       <c r="I8" t="n">
-        <v>15.62</v>
+        <v>16.58</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.143138 BTC + cash 0.00</t>
+          <t>15.230722 BNB + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -17211,19 +17211,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NEAR/BNB</t>
+          <t>ZRO/BTC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>330</v>
+        <v>171</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -17232,14 +17232,14 @@
         <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>11552.5</v>
+        <v>11611.04</v>
       </c>
       <c r="I9" t="n">
-        <v>15.53</v>
+        <v>16.11</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15.230722 BNB + cash 0.00</t>
+          <t>0.143138 BTC + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -17272,10 +17272,10 @@
         <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>11520.7</v>
+        <v>11499.48</v>
       </c>
       <c r="I10" t="n">
-        <v>15.21</v>
+        <v>14.99</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -17312,10 +17312,10 @@
         <v>10000</v>
       </c>
       <c r="H11" t="n">
-        <v>11448.01</v>
+        <v>11385.34</v>
       </c>
       <c r="I11" t="n">
-        <v>14.48</v>
+        <v>13.85</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -17352,10 +17352,10 @@
         <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>10741.29</v>
+        <v>10893.65</v>
       </c>
       <c r="I12" t="n">
-        <v>7.41</v>
+        <v>8.94</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -17392,10 +17392,10 @@
         <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>10725.46</v>
+        <v>10770.91</v>
       </c>
       <c r="I13" t="n">
-        <v>7.25</v>
+        <v>7.71</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -17472,10 +17472,10 @@
         <v>10000</v>
       </c>
       <c r="H15" t="n">
-        <v>9374.969999999999</v>
+        <v>9528.15</v>
       </c>
       <c r="I15" t="n">
-        <v>-6.25</v>
+        <v>-4.72</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -17512,10 +17512,10 @@
         <v>10000</v>
       </c>
       <c r="H16" t="n">
-        <v>9342.48</v>
+        <v>9475</v>
       </c>
       <c r="I16" t="n">
-        <v>-6.58</v>
+        <v>-5.25</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -17552,10 +17552,10 @@
         <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>9180.290000000001</v>
+        <v>9387.73</v>
       </c>
       <c r="I17" t="n">
-        <v>-8.199999999999999</v>
+        <v>-6.12</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -17592,10 +17592,10 @@
         <v>10000</v>
       </c>
       <c r="H18" t="n">
-        <v>9141.610000000001</v>
+        <v>9225.129999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-8.58</v>
+        <v>-7.75</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -17632,10 +17632,10 @@
         <v>10000</v>
       </c>
       <c r="H19" t="n">
-        <v>8958.620000000001</v>
+        <v>8996.58</v>
       </c>
       <c r="I19" t="n">
-        <v>-10.41</v>
+        <v>-10.03</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -17672,10 +17672,10 @@
         <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>8457.209999999999</v>
+        <v>8595.4</v>
       </c>
       <c r="I20" t="n">
-        <v>-15.43</v>
+        <v>-14.05</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -17712,10 +17712,10 @@
         <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>7902.21</v>
+        <v>8023.26</v>
       </c>
       <c r="I21" t="n">
-        <v>-20.98</v>
+        <v>-19.77</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -17752,10 +17752,10 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>7574.77</v>
+        <v>7698.54</v>
       </c>
       <c r="I22" t="n">
-        <v>-24.25</v>
+        <v>-23.01</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -17792,10 +17792,10 @@
         <v>10000</v>
       </c>
       <c r="H23" t="n">
-        <v>7360.44</v>
+        <v>7568.81</v>
       </c>
       <c r="I23" t="n">
-        <v>-26.4</v>
+        <v>-24.31</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -17832,10 +17832,10 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>6969.84</v>
+        <v>6999.37</v>
       </c>
       <c r="I24" t="n">
-        <v>-30.3</v>
+        <v>-30.01</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -17872,10 +17872,10 @@
         <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>5791.13</v>
+        <v>5885.76</v>
       </c>
       <c r="I25" t="n">
-        <v>-42.09</v>
+        <v>-41.14</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -17912,10 +17912,10 @@
         <v>10000</v>
       </c>
       <c r="H26" t="n">
-        <v>5791.13</v>
+        <v>5885.76</v>
       </c>
       <c r="I26" t="n">
-        <v>-42.09</v>
+        <v>-41.14</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -17952,10 +17952,10 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>5791.13</v>
+        <v>5885.76</v>
       </c>
       <c r="I27" t="n">
-        <v>-42.09</v>
+        <v>-41.14</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -17992,10 +17992,10 @@
         <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>5791.13</v>
+        <v>5885.76</v>
       </c>
       <c r="I28" t="n">
-        <v>-42.09</v>
+        <v>-41.14</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -18032,10 +18032,10 @@
         <v>10000</v>
       </c>
       <c r="H29" t="n">
-        <v>5510.59</v>
+        <v>5595</v>
       </c>
       <c r="I29" t="n">
-        <v>-44.89</v>
+        <v>-44.05</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -18072,10 +18072,10 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>5386.2</v>
+        <v>5507.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-46.14</v>
+        <v>-44.92</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -18112,10 +18112,10 @@
         <v>10000</v>
       </c>
       <c r="H31" t="n">
-        <v>5252.1</v>
+        <v>5274.67</v>
       </c>
       <c r="I31" t="n">
-        <v>-47.48</v>
+        <v>-47.25</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -18152,10 +18152,10 @@
         <v>10000</v>
       </c>
       <c r="H32" t="n">
-        <v>5135.23</v>
+        <v>5251.27</v>
       </c>
       <c r="I32" t="n">
-        <v>-48.65</v>
+        <v>-47.49</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>10000</v>
       </c>
       <c r="H33" t="n">
-        <v>5135.23</v>
+        <v>5251.27</v>
       </c>
       <c r="I33" t="n">
-        <v>-48.65</v>
+        <v>-47.49</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -18232,10 +18232,10 @@
         <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>5135.23</v>
+        <v>5251.27</v>
       </c>
       <c r="I34" t="n">
-        <v>-48.65</v>
+        <v>-47.49</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -18272,10 +18272,10 @@
         <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>5135.23</v>
+        <v>5251.27</v>
       </c>
       <c r="I35" t="n">
-        <v>-48.65</v>
+        <v>-47.49</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -18312,10 +18312,10 @@
         <v>10000</v>
       </c>
       <c r="H36" t="n">
-        <v>5135.23</v>
+        <v>5251.27</v>
       </c>
       <c r="I36" t="n">
-        <v>-48.65</v>
+        <v>-47.49</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -18352,10 +18352,10 @@
         <v>10000</v>
       </c>
       <c r="H37" t="n">
-        <v>5135.23</v>
+        <v>5251.27</v>
       </c>
       <c r="I37" t="n">
-        <v>-48.65</v>
+        <v>-47.49</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -18392,10 +18392,10 @@
         <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>5135.23</v>
+        <v>5251.27</v>
       </c>
       <c r="I38" t="n">
-        <v>-48.65</v>
+        <v>-47.49</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -18432,10 +18432,10 @@
         <v>10000</v>
       </c>
       <c r="H39" t="n">
-        <v>5135.23</v>
+        <v>5251.27</v>
       </c>
       <c r="I39" t="n">
-        <v>-48.65</v>
+        <v>-47.49</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>5135.23</v>
+        <v>5251.27</v>
       </c>
       <c r="I40" t="n">
-        <v>-48.65</v>
+        <v>-47.49</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -18512,10 +18512,10 @@
         <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>4977.16</v>
+        <v>5000.92</v>
       </c>
       <c r="I41" t="n">
-        <v>-50.23</v>
+        <v>-49.99</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -18552,10 +18552,10 @@
         <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>4791.9</v>
+        <v>4865.3</v>
       </c>
       <c r="I42" t="n">
-        <v>-52.08</v>
+        <v>-51.35</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -18592,10 +18592,10 @@
         <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>4570.83</v>
+        <v>4640.86</v>
       </c>
       <c r="I43" t="n">
-        <v>-54.29</v>
+        <v>-53.59</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -18632,10 +18632,10 @@
         <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>4570.83</v>
+        <v>4640.86</v>
       </c>
       <c r="I44" t="n">
-        <v>-54.29</v>
+        <v>-53.59</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>4570.83</v>
+        <v>4640.86</v>
       </c>
       <c r="I45" t="n">
-        <v>-54.29</v>
+        <v>-53.59</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -18712,10 +18712,10 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>4570.83</v>
+        <v>4640.86</v>
       </c>
       <c r="I46" t="n">
-        <v>-54.29</v>
+        <v>-53.59</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -18752,10 +18752,10 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>4570.83</v>
+        <v>4640.86</v>
       </c>
       <c r="I47" t="n">
-        <v>-54.29</v>
+        <v>-53.59</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -18792,10 +18792,10 @@
         <v>10000</v>
       </c>
       <c r="H48" t="n">
-        <v>4570.83</v>
+        <v>4640.86</v>
       </c>
       <c r="I48" t="n">
-        <v>-54.29</v>
+        <v>-53.59</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -18832,10 +18832,10 @@
         <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>4570.83</v>
+        <v>4640.86</v>
       </c>
       <c r="I49" t="n">
-        <v>-54.29</v>
+        <v>-53.59</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -18872,10 +18872,10 @@
         <v>10000</v>
       </c>
       <c r="H50" t="n">
-        <v>4410.06</v>
+        <v>4534.9</v>
       </c>
       <c r="I50" t="n">
-        <v>-55.9</v>
+        <v>-54.65</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -18912,10 +18912,10 @@
         <v>10000</v>
       </c>
       <c r="H51" t="n">
-        <v>3984.08</v>
+        <v>4096.87</v>
       </c>
       <c r="I51" t="n">
-        <v>-60.16</v>
+        <v>-59.03</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -18931,19 +18931,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ZRO/HBAR</t>
+          <t>ETH/ATOM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="D52" t="n">
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -18952,14 +18952,14 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>3934.88</v>
+        <v>3993.01</v>
       </c>
       <c r="I52" t="n">
-        <v>-60.65</v>
+        <v>-60.07</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>49597.066179 HBAR + cash 0.00</t>
+          <t>2343.863143 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -18971,19 +18971,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ETH/ATOM</t>
+          <t>ZRO/HBAR</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="D53" t="n">
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -18992,14 +18992,14 @@
         <v>10000</v>
       </c>
       <c r="H53" t="n">
-        <v>3883.08</v>
+        <v>3951.8</v>
       </c>
       <c r="I53" t="n">
-        <v>-61.17</v>
+        <v>-60.48</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2343.863143 ATOM + cash 0.00</t>
+          <t>49597.066179 HBAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -19032,10 +19032,10 @@
         <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>3644.06</v>
+        <v>3747.22</v>
       </c>
       <c r="I54" t="n">
-        <v>-63.56</v>
+        <v>-62.53</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -19072,10 +19072,10 @@
         <v>10000</v>
       </c>
       <c r="H55" t="n">
-        <v>3644.06</v>
+        <v>3747.22</v>
       </c>
       <c r="I55" t="n">
-        <v>-63.56</v>
+        <v>-62.53</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -19112,10 +19112,10 @@
         <v>10000</v>
       </c>
       <c r="H56" t="n">
-        <v>3644.06</v>
+        <v>3747.22</v>
       </c>
       <c r="I56" t="n">
-        <v>-63.56</v>
+        <v>-62.53</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -19152,10 +19152,10 @@
         <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>3644.06</v>
+        <v>3747.22</v>
       </c>
       <c r="I57" t="n">
-        <v>-63.56</v>
+        <v>-62.53</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -19192,10 +19192,10 @@
         <v>10000</v>
       </c>
       <c r="H58" t="n">
-        <v>3644.06</v>
+        <v>3747.22</v>
       </c>
       <c r="I58" t="n">
-        <v>-63.56</v>
+        <v>-62.53</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -19232,10 +19232,10 @@
         <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>3605.34</v>
+        <v>3620.84</v>
       </c>
       <c r="I59" t="n">
-        <v>-63.95</v>
+        <v>-63.79</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -19272,10 +19272,10 @@
         <v>10000</v>
       </c>
       <c r="H60" t="n">
-        <v>3597.1</v>
+        <v>3612.56</v>
       </c>
       <c r="I60" t="n">
-        <v>-64.03</v>
+        <v>-63.87</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -19312,10 +19312,10 @@
         <v>10000</v>
       </c>
       <c r="H61" t="n">
-        <v>3548.13</v>
+        <v>3563.38</v>
       </c>
       <c r="I61" t="n">
-        <v>-64.52</v>
+        <v>-64.37</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -19352,10 +19352,10 @@
         <v>10000</v>
       </c>
       <c r="H62" t="n">
-        <v>3328.54</v>
+        <v>3342.84</v>
       </c>
       <c r="I62" t="n">
-        <v>-66.70999999999999</v>
+        <v>-66.56999999999999</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -19392,10 +19392,10 @@
         <v>10000</v>
       </c>
       <c r="H63" t="n">
-        <v>2758.95</v>
+        <v>2743.85</v>
       </c>
       <c r="I63" t="n">
-        <v>-72.41</v>
+        <v>-72.56</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -19432,10 +19432,10 @@
         <v>10000</v>
       </c>
       <c r="H64" t="n">
-        <v>2690.03</v>
+        <v>2702.86</v>
       </c>
       <c r="I64" t="n">
-        <v>-73.09999999999999</v>
+        <v>-72.97</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -19472,10 +19472,10 @@
         <v>10000</v>
       </c>
       <c r="H65" t="n">
-        <v>2547.22</v>
+        <v>2559.38</v>
       </c>
       <c r="I65" t="n">
-        <v>-74.53</v>
+        <v>-74.41</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -19512,10 +19512,10 @@
         <v>10000</v>
       </c>
       <c r="H66" t="n">
-        <v>2547.22</v>
+        <v>2559.38</v>
       </c>
       <c r="I66" t="n">
-        <v>-74.53</v>
+        <v>-74.41</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -19552,10 +19552,10 @@
         <v>10000</v>
       </c>
       <c r="H67" t="n">
-        <v>2547.22</v>
+        <v>2559.38</v>
       </c>
       <c r="I67" t="n">
-        <v>-74.53</v>
+        <v>-74.41</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -19592,10 +19592,10 @@
         <v>10000</v>
       </c>
       <c r="H68" t="n">
-        <v>2547.22</v>
+        <v>2559.38</v>
       </c>
       <c r="I68" t="n">
-        <v>-74.53</v>
+        <v>-74.41</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -19632,10 +19632,10 @@
         <v>10000</v>
       </c>
       <c r="H69" t="n">
-        <v>2547.22</v>
+        <v>2559.38</v>
       </c>
       <c r="I69" t="n">
-        <v>-74.53</v>
+        <v>-74.41</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -19672,10 +19672,10 @@
         <v>10000</v>
       </c>
       <c r="H70" t="n">
-        <v>2547.22</v>
+        <v>2559.38</v>
       </c>
       <c r="I70" t="n">
-        <v>-74.53</v>
+        <v>-74.41</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -19712,10 +19712,10 @@
         <v>10000</v>
       </c>
       <c r="H71" t="n">
-        <v>2547.22</v>
+        <v>2559.38</v>
       </c>
       <c r="I71" t="n">
-        <v>-74.53</v>
+        <v>-74.41</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -19752,10 +19752,10 @@
         <v>10000</v>
       </c>
       <c r="H72" t="n">
-        <v>2547.22</v>
+        <v>2559.38</v>
       </c>
       <c r="I72" t="n">
-        <v>-74.53</v>
+        <v>-74.41</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -19792,10 +19792,10 @@
         <v>10000</v>
       </c>
       <c r="H73" t="n">
-        <v>2547.22</v>
+        <v>2559.38</v>
       </c>
       <c r="I73" t="n">
-        <v>-74.53</v>
+        <v>-74.41</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -19832,10 +19832,10 @@
         <v>10000</v>
       </c>
       <c r="H74" t="n">
-        <v>2547.22</v>
+        <v>2559.38</v>
       </c>
       <c r="I74" t="n">
-        <v>-74.53</v>
+        <v>-74.41</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -19872,10 +19872,10 @@
         <v>10000</v>
       </c>
       <c r="H75" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I75" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -19912,10 +19912,10 @@
         <v>10000</v>
       </c>
       <c r="H76" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I76" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -19952,10 +19952,10 @@
         <v>10000</v>
       </c>
       <c r="H77" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I77" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -19992,10 +19992,10 @@
         <v>10000</v>
       </c>
       <c r="H78" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I78" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -20032,10 +20032,10 @@
         <v>10000</v>
       </c>
       <c r="H79" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I79" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -20072,10 +20072,10 @@
         <v>10000</v>
       </c>
       <c r="H80" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I80" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -20112,10 +20112,10 @@
         <v>10000</v>
       </c>
       <c r="H81" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I81" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -20152,10 +20152,10 @@
         <v>10000</v>
       </c>
       <c r="H82" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I82" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -20192,10 +20192,10 @@
         <v>10000</v>
       </c>
       <c r="H83" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I83" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -20232,10 +20232,10 @@
         <v>10000</v>
       </c>
       <c r="H84" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I84" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -20272,10 +20272,10 @@
         <v>10000</v>
       </c>
       <c r="H85" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I85" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -20312,10 +20312,10 @@
         <v>10000</v>
       </c>
       <c r="H86" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I86" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -20352,10 +20352,10 @@
         <v>10000</v>
       </c>
       <c r="H87" t="n">
-        <v>2431.14</v>
+        <v>2491.46</v>
       </c>
       <c r="I87" t="n">
-        <v>-75.69</v>
+        <v>-75.09</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -20392,10 +20392,10 @@
         <v>10000</v>
       </c>
       <c r="H88" t="n">
-        <v>1813.78</v>
+        <v>1803.85</v>
       </c>
       <c r="I88" t="n">
-        <v>-81.86</v>
+        <v>-81.95999999999999</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -20432,10 +20432,10 @@
         <v>10000</v>
       </c>
       <c r="H89" t="n">
-        <v>1745.05</v>
+        <v>1735.5</v>
       </c>
       <c r="I89" t="n">
-        <v>-82.55</v>
+        <v>-82.65000000000001</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -20472,10 +20472,10 @@
         <v>10000</v>
       </c>
       <c r="H90" t="n">
-        <v>1564.6</v>
+        <v>1556.03</v>
       </c>
       <c r="I90" t="n">
-        <v>-84.34999999999999</v>
+        <v>-84.44</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -20512,10 +20512,10 @@
         <v>10000</v>
       </c>
       <c r="H91" t="n">
-        <v>1564.6</v>
+        <v>1556.03</v>
       </c>
       <c r="I91" t="n">
-        <v>-84.34999999999999</v>
+        <v>-84.44</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -20552,10 +20552,10 @@
         <v>10000</v>
       </c>
       <c r="H92" t="n">
-        <v>1564.6</v>
+        <v>1556.03</v>
       </c>
       <c r="I92" t="n">
-        <v>-84.34999999999999</v>
+        <v>-84.44</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>

--- a/pair_strategies_analysis.xlsx
+++ b/pair_strategies_analysis.xlsx
@@ -502,10 +502,10 @@
         <v>10000</v>
       </c>
       <c r="H2" t="n">
-        <v>47239.1</v>
+        <v>46786.18</v>
       </c>
       <c r="I2" t="n">
-        <v>372.39</v>
+        <v>367.86</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>27265.15</v>
+        <v>27255.24</v>
       </c>
       <c r="I3" t="n">
-        <v>172.65</v>
+        <v>172.55</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>10000</v>
       </c>
       <c r="H4" t="n">
-        <v>22837.73</v>
+        <v>23257.93</v>
       </c>
       <c r="I4" t="n">
-        <v>128.38</v>
+        <v>132.58</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -622,10 +622,10 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>18155.79</v>
+        <v>17981.72</v>
       </c>
       <c r="I5" t="n">
-        <v>81.56</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -662,10 +662,10 @@
         <v>10000</v>
       </c>
       <c r="H6" t="n">
-        <v>17401.23</v>
+        <v>17721.41</v>
       </c>
       <c r="I6" t="n">
-        <v>74.01000000000001</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -702,10 +702,10 @@
         <v>10000</v>
       </c>
       <c r="H7" t="n">
-        <v>17115.59</v>
+        <v>17070.86</v>
       </c>
       <c r="I7" t="n">
-        <v>71.16</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         <v>10000</v>
       </c>
       <c r="H8" t="n">
-        <v>14325.78</v>
+        <v>14288.35</v>
       </c>
       <c r="I8" t="n">
-        <v>43.26</v>
+        <v>42.88</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
         <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>12751.49</v>
+        <v>12986.11</v>
       </c>
       <c r="I9" t="n">
-        <v>27.51</v>
+        <v>29.86</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>11776.96</v>
+        <v>11695.22</v>
       </c>
       <c r="I10" t="n">
-        <v>17.77</v>
+        <v>16.95</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -862,10 +862,10 @@
         <v>10000</v>
       </c>
       <c r="H11" t="n">
-        <v>11154.09</v>
+        <v>11286.81</v>
       </c>
       <c r="I11" t="n">
-        <v>11.54</v>
+        <v>12.87</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
         <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>10268.28</v>
+        <v>10197.01</v>
       </c>
       <c r="I12" t="n">
-        <v>2.68</v>
+        <v>1.97</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -942,10 +942,10 @@
         <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>9046.299999999999</v>
+        <v>9212.74</v>
       </c>
       <c r="I13" t="n">
-        <v>-9.539999999999999</v>
+        <v>-7.87</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -982,10 +982,10 @@
         <v>10000</v>
       </c>
       <c r="H14" t="n">
-        <v>8807.1</v>
+        <v>8727.24</v>
       </c>
       <c r="I14" t="n">
-        <v>-11.93</v>
+        <v>-12.73</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1022,10 +1022,10 @@
         <v>10000</v>
       </c>
       <c r="H15" t="n">
-        <v>8653.98</v>
+        <v>8575.5</v>
       </c>
       <c r="I15" t="n">
-        <v>-13.46</v>
+        <v>-14.24</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1062,10 +1062,10 @@
         <v>10000</v>
       </c>
       <c r="H16" t="n">
-        <v>8574.25</v>
+        <v>8514.73</v>
       </c>
       <c r="I16" t="n">
-        <v>-14.26</v>
+        <v>-14.85</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1102,10 +1102,10 @@
         <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>8004.44</v>
+        <v>7927.69</v>
       </c>
       <c r="I17" t="n">
-        <v>-19.96</v>
+        <v>-20.72</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         <v>10000</v>
       </c>
       <c r="H18" t="n">
-        <v>6631.44</v>
+        <v>6571.31</v>
       </c>
       <c r="I18" t="n">
-        <v>-33.69</v>
+        <v>-34.29</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         <v>10000</v>
       </c>
       <c r="H19" t="n">
-        <v>5843.91</v>
+        <v>5790.91</v>
       </c>
       <c r="I19" t="n">
-        <v>-41.56</v>
+        <v>-42.09</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1222,10 +1222,10 @@
         <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>5640.83</v>
+        <v>5586.74</v>
       </c>
       <c r="I20" t="n">
-        <v>-43.59</v>
+        <v>-44.13</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NEAR/HBAR</t>
+          <t>NEAR/TRX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1518</v>
+        <v>1757</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1262,14 +1262,14 @@
         <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>5403.42</v>
+        <v>5449.31</v>
       </c>
       <c r="I21" t="n">
-        <v>-45.97</v>
+        <v>-45.51</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>67815.763416 HBAR + cash 0.00</t>
+          <t>1452.103586 NEAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NEAR/TRX</t>
+          <t>NEAR/HBAR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>1757</v>
+        <v>1518</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1302,14 +1302,14 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>5350.86</v>
+        <v>5389.86</v>
       </c>
       <c r="I22" t="n">
-        <v>-46.49</v>
+        <v>-46.1</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1452.103586 NEAR + cash 0.00</t>
+          <t>67815.763416 HBAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>10000</v>
       </c>
       <c r="H23" t="n">
-        <v>5142.09</v>
+        <v>5236.7</v>
       </c>
       <c r="I23" t="n">
-        <v>-48.58</v>
+        <v>-47.63</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1382,10 +1382,10 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>4869.14</v>
+        <v>4856.91</v>
       </c>
       <c r="I24" t="n">
-        <v>-51.31</v>
+        <v>-51.43</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
         <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>4748.47</v>
+        <v>4736.55</v>
       </c>
       <c r="I25" t="n">
-        <v>-52.52</v>
+        <v>-52.63</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1462,10 +1462,10 @@
         <v>10000</v>
       </c>
       <c r="H26" t="n">
-        <v>4602.58</v>
+        <v>4558.45</v>
       </c>
       <c r="I26" t="n">
-        <v>-53.97</v>
+        <v>-54.42</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1502,10 +1502,10 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>3912.59</v>
+        <v>3898.91</v>
       </c>
       <c r="I27" t="n">
-        <v>-60.87</v>
+        <v>-61.01</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1542,10 +1542,10 @@
         <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>3784.04</v>
+        <v>3774.54</v>
       </c>
       <c r="I28" t="n">
-        <v>-62.16</v>
+        <v>-62.25</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         <v>10000</v>
       </c>
       <c r="H29" t="n">
-        <v>3695.32</v>
+        <v>3682.4</v>
       </c>
       <c r="I29" t="n">
-        <v>-63.05</v>
+        <v>-63.18</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>2943.87</v>
+        <v>2936.48</v>
       </c>
       <c r="I30" t="n">
-        <v>-70.56</v>
+        <v>-70.64</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1662,10 +1662,10 @@
         <v>10000</v>
       </c>
       <c r="H31" t="n">
-        <v>2813.81</v>
+        <v>2806.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-71.86</v>
+        <v>-71.93000000000001</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1702,10 +1702,10 @@
         <v>10000</v>
       </c>
       <c r="H32" t="n">
-        <v>2763.02</v>
+        <v>2756.09</v>
       </c>
       <c r="I32" t="n">
-        <v>-72.37</v>
+        <v>-72.44</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
         <v>10000</v>
       </c>
       <c r="H33" t="n">
-        <v>2475.03</v>
+        <v>2504.49</v>
       </c>
       <c r="I33" t="n">
-        <v>-75.25</v>
+        <v>-74.95999999999999</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1782,10 +1782,10 @@
         <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>2100.64</v>
+        <v>2106.56</v>
       </c>
       <c r="I34" t="n">
-        <v>-78.98999999999999</v>
+        <v>-78.93000000000001</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
         <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>1934.49</v>
+        <v>1939.94</v>
       </c>
       <c r="I35" t="n">
-        <v>-80.66</v>
+        <v>-80.59999999999999</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1862,10 +1862,10 @@
         <v>10000</v>
       </c>
       <c r="H36" t="n">
-        <v>1788.82</v>
+        <v>1810.1</v>
       </c>
       <c r="I36" t="n">
-        <v>-82.11</v>
+        <v>-81.90000000000001</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DOT/ATOM</t>
+          <t>ADA/AAVE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>548</v>
+        <v>1541</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1902,14 +1902,14 @@
         <v>10000</v>
       </c>
       <c r="H37" t="n">
-        <v>1764.93</v>
+        <v>1783.75</v>
       </c>
       <c r="I37" t="n">
-        <v>-82.34999999999999</v>
+        <v>-82.16</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1552.538505 DOT + cash 0.00</t>
+          <t>7888.527556 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ADA/AAVE</t>
+          <t>DOT/ATOM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E38" t="n">
-        <v>1541</v>
+        <v>548</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1942,14 +1942,14 @@
         <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>1762.78</v>
+        <v>1753.9</v>
       </c>
       <c r="I38" t="n">
-        <v>-82.37</v>
+        <v>-82.45999999999999</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>7888.527556 ADA + cash 0.00</t>
+          <t>1552.538505 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -1982,10 +1982,10 @@
         <v>10000</v>
       </c>
       <c r="H39" t="n">
-        <v>1463.02</v>
+        <v>1453.88</v>
       </c>
       <c r="I39" t="n">
-        <v>-85.37</v>
+        <v>-85.45999999999999</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2022,10 +2022,10 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>1270.89</v>
+        <v>1262.96</v>
       </c>
       <c r="I40" t="n">
-        <v>-87.29000000000001</v>
+        <v>-87.37</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2062,10 +2062,10 @@
         <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>1257.96</v>
+        <v>1261.51</v>
       </c>
       <c r="I41" t="n">
-        <v>-87.42</v>
+        <v>-87.38</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2102,10 +2102,10 @@
         <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>1231.54</v>
+        <v>1235.01</v>
       </c>
       <c r="I42" t="n">
-        <v>-87.68000000000001</v>
+        <v>-87.65000000000001</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>1207.37</v>
+        <v>1221.74</v>
       </c>
       <c r="I43" t="n">
-        <v>-87.93000000000001</v>
+        <v>-87.78</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2182,10 +2182,10 @@
         <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>1197.12</v>
+        <v>1211.36</v>
       </c>
       <c r="I44" t="n">
-        <v>-88.03</v>
+        <v>-87.89</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ICP/BNB</t>
+          <t>ADA/BTC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2213,7 +2213,7 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1682</v>
+        <v>1811</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2222,14 +2222,14 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>1186.98</v>
+        <v>1194.17</v>
       </c>
       <c r="I45" t="n">
-        <v>-88.13</v>
+        <v>-88.06</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>415.028914 ICP + cash 0.00</t>
+          <t>5281.154221 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ADA/BTC</t>
+          <t>ADA/TRX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2253,7 +2253,7 @@
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>1811</v>
+        <v>1783</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2262,14 +2262,14 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>1180.13</v>
+        <v>1184.29</v>
       </c>
       <c r="I46" t="n">
-        <v>-88.2</v>
+        <v>-88.16</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>5281.154221 ADA + cash 0.00</t>
+          <t>5237.423115 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ADA/TRX</t>
+          <t>ICP/BNB</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2293,7 +2293,7 @@
         <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>1783</v>
+        <v>1682</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2302,14 +2302,14 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>1170.36</v>
+        <v>1182.83</v>
       </c>
       <c r="I47" t="n">
-        <v>-88.3</v>
+        <v>-88.17</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>5237.423115 ADA + cash 0.00</t>
+          <t>415.028914 ICP + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -2342,10 +2342,10 @@
         <v>10000</v>
       </c>
       <c r="H48" t="n">
-        <v>1108.7</v>
+        <v>1104.83</v>
       </c>
       <c r="I48" t="n">
-        <v>-88.91</v>
+        <v>-88.95</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2382,10 +2382,10 @@
         <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>918.9400000000001</v>
+        <v>921.53</v>
       </c>
       <c r="I49" t="n">
-        <v>-90.81</v>
+        <v>-90.78</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2422,10 +2422,10 @@
         <v>10000</v>
       </c>
       <c r="H50" t="n">
-        <v>801.25</v>
+        <v>798.45</v>
       </c>
       <c r="I50" t="n">
-        <v>-91.98999999999999</v>
+        <v>-92.02</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ADA/DOT</t>
+          <t>ATOM/NEAR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>1325</v>
+        <v>1656</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2462,14 +2462,14 @@
         <v>10000</v>
       </c>
       <c r="H51" t="n">
-        <v>756.08</v>
+        <v>752.52</v>
       </c>
       <c r="I51" t="n">
-        <v>-92.44</v>
+        <v>-92.47</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>665.094194 DOT + cash 0.00</t>
+          <t>440.480933 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ATOM/NEAR</t>
+          <t>ADA/DOT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E52" t="n">
-        <v>1656</v>
+        <v>1325</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2502,14 +2502,14 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>750.4</v>
+        <v>751.36</v>
       </c>
       <c r="I52" t="n">
-        <v>-92.5</v>
+        <v>-92.48999999999999</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>440.480933 ATOM + cash 0.00</t>
+          <t>665.094194 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -2542,10 +2542,10 @@
         <v>10000</v>
       </c>
       <c r="H53" t="n">
-        <v>743.71</v>
+        <v>745.8</v>
       </c>
       <c r="I53" t="n">
-        <v>-92.56</v>
+        <v>-92.54000000000001</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2582,10 +2582,10 @@
         <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>691.63</v>
+        <v>693.5700000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>-93.08</v>
+        <v>-93.06</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2622,10 +2622,10 @@
         <v>10000</v>
       </c>
       <c r="H55" t="n">
-        <v>669.79</v>
+        <v>667.45</v>
       </c>
       <c r="I55" t="n">
-        <v>-93.3</v>
+        <v>-93.33</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2662,10 +2662,10 @@
         <v>10000</v>
       </c>
       <c r="H56" t="n">
-        <v>664.0700000000001</v>
+        <v>661.75</v>
       </c>
       <c r="I56" t="n">
-        <v>-93.36</v>
+        <v>-93.38</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2702,10 +2702,10 @@
         <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>621.37</v>
+        <v>617.49</v>
       </c>
       <c r="I57" t="n">
-        <v>-93.79000000000001</v>
+        <v>-93.83</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2742,10 +2742,10 @@
         <v>10000</v>
       </c>
       <c r="H58" t="n">
-        <v>614.84</v>
+        <v>616.5700000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>-93.84999999999999</v>
+        <v>-93.83</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2782,10 +2782,10 @@
         <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>606.78</v>
+        <v>602.99</v>
       </c>
       <c r="I59" t="n">
-        <v>-93.93000000000001</v>
+        <v>-93.97</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2822,10 +2822,10 @@
         <v>10000</v>
       </c>
       <c r="H60" t="n">
-        <v>604.89</v>
+        <v>601.12</v>
       </c>
       <c r="I60" t="n">
-        <v>-93.95</v>
+        <v>-93.98999999999999</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         <v>10000</v>
       </c>
       <c r="H61" t="n">
-        <v>575.34</v>
+        <v>573.33</v>
       </c>
       <c r="I61" t="n">
-        <v>-94.25</v>
+        <v>-94.27</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2902,10 +2902,10 @@
         <v>10000</v>
       </c>
       <c r="H62" t="n">
-        <v>575.34</v>
+        <v>573.33</v>
       </c>
       <c r="I62" t="n">
-        <v>-94.25</v>
+        <v>-94.27</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2942,10 +2942,10 @@
         <v>10000</v>
       </c>
       <c r="H63" t="n">
-        <v>575.34</v>
+        <v>573.33</v>
       </c>
       <c r="I63" t="n">
-        <v>-94.25</v>
+        <v>-94.27</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2982,10 +2982,10 @@
         <v>10000</v>
       </c>
       <c r="H64" t="n">
-        <v>542.95</v>
+        <v>539.5599999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>-94.56999999999999</v>
+        <v>-94.59999999999999</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
         <v>10000</v>
       </c>
       <c r="H65" t="n">
-        <v>496.37</v>
+        <v>493.27</v>
       </c>
       <c r="I65" t="n">
-        <v>-95.04000000000001</v>
+        <v>-95.06999999999999</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3062,10 +3062,10 @@
         <v>10000</v>
       </c>
       <c r="H66" t="n">
-        <v>493.82</v>
+        <v>490.74</v>
       </c>
       <c r="I66" t="n">
-        <v>-95.06</v>
+        <v>-95.09</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3102,10 +3102,10 @@
         <v>10000</v>
       </c>
       <c r="H67" t="n">
-        <v>432.4</v>
+        <v>429.7</v>
       </c>
       <c r="I67" t="n">
-        <v>-95.68000000000001</v>
+        <v>-95.7</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3142,10 +3142,10 @@
         <v>10000</v>
       </c>
       <c r="H68" t="n">
-        <v>259.21</v>
+        <v>261.91</v>
       </c>
       <c r="I68" t="n">
-        <v>-97.41</v>
+        <v>-97.38</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3182,10 +3182,10 @@
         <v>10000</v>
       </c>
       <c r="H69" t="n">
-        <v>207.7</v>
+        <v>209.86</v>
       </c>
       <c r="I69" t="n">
-        <v>-97.92</v>
+        <v>-97.90000000000001</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3222,10 +3222,10 @@
         <v>10000</v>
       </c>
       <c r="H70" t="n">
-        <v>192.25</v>
+        <v>194.25</v>
       </c>
       <c r="I70" t="n">
-        <v>-98.08</v>
+        <v>-98.06</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3262,10 +3262,10 @@
         <v>10000</v>
       </c>
       <c r="H71" t="n">
-        <v>154</v>
+        <v>155.6</v>
       </c>
       <c r="I71" t="n">
-        <v>-98.45999999999999</v>
+        <v>-98.44</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3302,10 +3302,10 @@
         <v>10000</v>
       </c>
       <c r="H72" t="n">
-        <v>131.76</v>
+        <v>133.13</v>
       </c>
       <c r="I72" t="n">
-        <v>-98.68000000000001</v>
+        <v>-98.67</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3342,10 +3342,10 @@
         <v>10000</v>
       </c>
       <c r="H73" t="n">
-        <v>110.14</v>
+        <v>111.29</v>
       </c>
       <c r="I73" t="n">
-        <v>-98.90000000000001</v>
+        <v>-98.89</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3382,10 +3382,10 @@
         <v>10000</v>
       </c>
       <c r="H74" t="n">
-        <v>107.65</v>
+        <v>108.77</v>
       </c>
       <c r="I74" t="n">
-        <v>-98.92</v>
+        <v>-98.91</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3422,10 +3422,10 @@
         <v>10000</v>
       </c>
       <c r="H75" t="n">
-        <v>106.82</v>
+        <v>107.93</v>
       </c>
       <c r="I75" t="n">
-        <v>-98.93000000000001</v>
+        <v>-98.92</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3462,10 +3462,10 @@
         <v>10000</v>
       </c>
       <c r="H76" t="n">
-        <v>93.83</v>
+        <v>94.8</v>
       </c>
       <c r="I76" t="n">
-        <v>-99.06</v>
+        <v>-99.05</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3502,10 +3502,10 @@
         <v>10000</v>
       </c>
       <c r="H77" t="n">
-        <v>93</v>
+        <v>93.97</v>
       </c>
       <c r="I77" t="n">
-        <v>-99.06999999999999</v>
+        <v>-99.06</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3542,10 +3542,10 @@
         <v>10000</v>
       </c>
       <c r="H78" t="n">
-        <v>90.44</v>
+        <v>91.39</v>
       </c>
       <c r="I78" t="n">
-        <v>-99.09999999999999</v>
+        <v>-99.09</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3582,10 +3582,10 @@
         <v>10000</v>
       </c>
       <c r="H79" t="n">
-        <v>90.41</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-99.09999999999999</v>
+        <v>-99.09</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3688,10 +3688,10 @@
         <v>10000</v>
       </c>
       <c r="H2" t="n">
-        <v>50972.33</v>
+        <v>50953.8</v>
       </c>
       <c r="I2" t="n">
-        <v>409.72</v>
+        <v>409.54</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -3728,10 +3728,10 @@
         <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>30647.06</v>
+        <v>31210.95</v>
       </c>
       <c r="I3" t="n">
-        <v>206.47</v>
+        <v>212.11</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -3768,10 +3768,10 @@
         <v>10000</v>
       </c>
       <c r="H4" t="n">
-        <v>20493.85</v>
+        <v>20442.41</v>
       </c>
       <c r="I4" t="n">
-        <v>104.94</v>
+        <v>104.42</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -3808,10 +3808,10 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>20363.61</v>
+        <v>20168.37</v>
       </c>
       <c r="I5" t="n">
-        <v>103.64</v>
+        <v>101.68</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ETH/TRX</t>
+          <t>BTC/NEAR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>1499</v>
+        <v>1388</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -3848,14 +3848,14 @@
         <v>10000</v>
       </c>
       <c r="H6" t="n">
-        <v>15516.21</v>
+        <v>15585.99</v>
       </c>
       <c r="I6" t="n">
-        <v>55.16</v>
+        <v>55.86</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.891635 ETH + cash 0.00</t>
+          <t>4153.272897 NEAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BTC/NEAR</t>
+          <t>ETH/TRX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>1388</v>
+        <v>1499</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3888,14 +3888,14 @@
         <v>10000</v>
       </c>
       <c r="H7" t="n">
-        <v>15304.4</v>
+        <v>15408.51</v>
       </c>
       <c r="I7" t="n">
-        <v>53.04</v>
+        <v>54.09</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4153.272897 NEAR + cash 0.00</t>
+          <t>5.891635 ETH + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -3928,10 +3928,10 @@
         <v>10000</v>
       </c>
       <c r="H8" t="n">
-        <v>13879.92</v>
+        <v>13843.66</v>
       </c>
       <c r="I8" t="n">
-        <v>38.8</v>
+        <v>38.44</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -3968,10 +3968,10 @@
         <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>13819.42</v>
+        <v>13694.11</v>
       </c>
       <c r="I9" t="n">
-        <v>38.19</v>
+        <v>36.94</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>12930.65</v>
+        <v>12896.87</v>
       </c>
       <c r="I10" t="n">
-        <v>29.31</v>
+        <v>28.97</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -4048,10 +4048,10 @@
         <v>10000</v>
       </c>
       <c r="H11" t="n">
-        <v>12649.81</v>
+        <v>12882.56</v>
       </c>
       <c r="I11" t="n">
-        <v>26.5</v>
+        <v>28.83</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -4088,10 +4088,10 @@
         <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>11384.56</v>
+        <v>11305.54</v>
       </c>
       <c r="I12" t="n">
-        <v>13.85</v>
+        <v>13.06</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>7402.11</v>
+        <v>7538.31</v>
       </c>
       <c r="I13" t="n">
-        <v>-25.98</v>
+        <v>-24.62</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -4168,10 +4168,10 @@
         <v>10000</v>
       </c>
       <c r="H14" t="n">
-        <v>6672.6</v>
+        <v>6612.09</v>
       </c>
       <c r="I14" t="n">
-        <v>-33.27</v>
+        <v>-33.88</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -4208,10 +4208,10 @@
         <v>10000</v>
       </c>
       <c r="H15" t="n">
-        <v>6135.23</v>
+        <v>6079.59</v>
       </c>
       <c r="I15" t="n">
-        <v>-38.65</v>
+        <v>-39.2</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -4248,10 +4248,10 @@
         <v>10000</v>
       </c>
       <c r="H16" t="n">
-        <v>6089.64</v>
+        <v>6031.25</v>
       </c>
       <c r="I16" t="n">
-        <v>-39.1</v>
+        <v>-39.69</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -4288,10 +4288,10 @@
         <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>5981.39</v>
+        <v>5939.87</v>
       </c>
       <c r="I17" t="n">
-        <v>-40.19</v>
+        <v>-40.6</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
         <v>10000</v>
       </c>
       <c r="H18" t="n">
-        <v>5843.91</v>
+        <v>5790.91</v>
       </c>
       <c r="I18" t="n">
-        <v>-41.56</v>
+        <v>-42.09</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>10000</v>
       </c>
       <c r="H19" t="n">
-        <v>5754.3</v>
+        <v>5702.12</v>
       </c>
       <c r="I19" t="n">
-        <v>-42.46</v>
+        <v>-42.98</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -4408,10 +4408,10 @@
         <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>5640.83</v>
+        <v>5586.74</v>
       </c>
       <c r="I20" t="n">
-        <v>-43.59</v>
+        <v>-44.13</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -4448,10 +4448,10 @@
         <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>5364.86</v>
+        <v>5316.21</v>
       </c>
       <c r="I21" t="n">
-        <v>-46.35</v>
+        <v>-46.84</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -4488,10 +4488,10 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>5217.99</v>
+        <v>5313.99</v>
       </c>
       <c r="I22" t="n">
-        <v>-47.82</v>
+        <v>-46.86</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -4528,10 +4528,10 @@
         <v>10000</v>
       </c>
       <c r="H23" t="n">
-        <v>4602.58</v>
+        <v>4558.45</v>
       </c>
       <c r="I23" t="n">
-        <v>-53.97</v>
+        <v>-54.42</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -4568,10 +4568,10 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>4047.98</v>
+        <v>4037.82</v>
       </c>
       <c r="I24" t="n">
-        <v>-59.52</v>
+        <v>-59.62</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -4608,10 +4608,10 @@
         <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>3250.59</v>
+        <v>3289.27</v>
       </c>
       <c r="I25" t="n">
-        <v>-67.48999999999999</v>
+        <v>-67.11</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -4648,10 +4648,10 @@
         <v>10000</v>
       </c>
       <c r="H26" t="n">
-        <v>2915.05</v>
+        <v>2923.26</v>
       </c>
       <c r="I26" t="n">
-        <v>-70.84999999999999</v>
+        <v>-70.77</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>2911.07</v>
+        <v>2903.77</v>
       </c>
       <c r="I27" t="n">
-        <v>-70.89</v>
+        <v>-70.95999999999999</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -4728,10 +4728,10 @@
         <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>2894.9</v>
+        <v>2887.63</v>
       </c>
       <c r="I28" t="n">
-        <v>-71.05</v>
+        <v>-71.12</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DOT/TRX</t>
+          <t>DOT/HBAR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>1446</v>
+        <v>1196</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4768,14 +4768,14 @@
         <v>10000</v>
       </c>
       <c r="H29" t="n">
-        <v>2813.92</v>
+        <v>2797.19</v>
       </c>
       <c r="I29" t="n">
-        <v>-71.86</v>
+        <v>-72.03</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2475.298542 DOT + cash 0.00</t>
+          <t>35194.467746 HBAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DOT/HBAR</t>
+          <t>DOT/TRX</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1196</v>
+        <v>1446</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -4808,14 +4808,14 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>2804.22</v>
+        <v>2796.34</v>
       </c>
       <c r="I30" t="n">
-        <v>-71.95999999999999</v>
+        <v>-72.04000000000001</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>35194.467746 HBAR + cash 0.00</t>
+          <t>2475.298542 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -4848,10 +4848,10 @@
         <v>10000</v>
       </c>
       <c r="H31" t="n">
-        <v>2763.02</v>
+        <v>2756.09</v>
       </c>
       <c r="I31" t="n">
-        <v>-72.37</v>
+        <v>-72.44</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -4888,10 +4888,10 @@
         <v>10000</v>
       </c>
       <c r="H32" t="n">
-        <v>2474.23</v>
+        <v>2458.78</v>
       </c>
       <c r="I32" t="n">
-        <v>-75.26000000000001</v>
+        <v>-75.41</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -4928,10 +4928,10 @@
         <v>10000</v>
       </c>
       <c r="H33" t="n">
-        <v>2416.79</v>
+        <v>2410.72</v>
       </c>
       <c r="I33" t="n">
-        <v>-75.83</v>
+        <v>-75.89</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -4968,10 +4968,10 @@
         <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>2394.39</v>
+        <v>2388.38</v>
       </c>
       <c r="I34" t="n">
-        <v>-76.06</v>
+        <v>-76.12</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -5008,10 +5008,10 @@
         <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>2217.47</v>
+        <v>2223.72</v>
       </c>
       <c r="I35" t="n">
-        <v>-77.83</v>
+        <v>-77.76000000000001</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -5048,10 +5048,10 @@
         <v>10000</v>
       </c>
       <c r="H36" t="n">
-        <v>2205.51</v>
+        <v>2197.8</v>
       </c>
       <c r="I36" t="n">
-        <v>-77.94</v>
+        <v>-78.02</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         <v>10000</v>
       </c>
       <c r="H37" t="n">
-        <v>1868.4</v>
+        <v>1873.66</v>
       </c>
       <c r="I37" t="n">
-        <v>-81.31999999999999</v>
+        <v>-81.26000000000001</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -5128,10 +5128,10 @@
         <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>1611.38</v>
+        <v>1630.56</v>
       </c>
       <c r="I38" t="n">
-        <v>-83.89</v>
+        <v>-83.69</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -5168,10 +5168,10 @@
         <v>10000</v>
       </c>
       <c r="H39" t="n">
-        <v>1584.12</v>
+        <v>1574.22</v>
       </c>
       <c r="I39" t="n">
-        <v>-84.16</v>
+        <v>-84.26000000000001</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -5208,10 +5208,10 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>1417.79</v>
+        <v>1421.79</v>
       </c>
       <c r="I40" t="n">
-        <v>-85.81999999999999</v>
+        <v>-85.78</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -5248,10 +5248,10 @@
         <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>1300.39</v>
+        <v>1315.87</v>
       </c>
       <c r="I41" t="n">
-        <v>-87</v>
+        <v>-86.84</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -5288,10 +5288,10 @@
         <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>1300.01</v>
+        <v>1315.48</v>
       </c>
       <c r="I42" t="n">
-        <v>-87</v>
+        <v>-86.84999999999999</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>1275.55</v>
+        <v>1290.73</v>
       </c>
       <c r="I43" t="n">
-        <v>-87.23999999999999</v>
+        <v>-87.09</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -5368,10 +5368,10 @@
         <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>1212.35</v>
+        <v>1226.77</v>
       </c>
       <c r="I44" t="n">
-        <v>-87.88</v>
+        <v>-87.73</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -5408,10 +5408,10 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>1207.37</v>
+        <v>1221.74</v>
       </c>
       <c r="I45" t="n">
-        <v>-87.93000000000001</v>
+        <v>-87.78</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>1197.12</v>
+        <v>1211.36</v>
       </c>
       <c r="I46" t="n">
-        <v>-88.03</v>
+        <v>-87.89</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DOT/BNB</t>
+          <t>ADA/HBAR</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5479,7 +5479,7 @@
         <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>1659</v>
+        <v>1286</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -5488,14 +5488,14 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>1190.15</v>
+        <v>1203.63</v>
       </c>
       <c r="I47" t="n">
-        <v>-88.09999999999999</v>
+        <v>-87.95999999999999</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1046.926411 DOT + cash 0.00</t>
+          <t>5322.952106 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ADA/HBAR</t>
+          <t>ADA/DOT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5519,7 +5519,7 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1286</v>
+        <v>1393</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -5528,14 +5528,14 @@
         <v>10000</v>
       </c>
       <c r="H48" t="n">
-        <v>1189.47</v>
+        <v>1197.01</v>
       </c>
       <c r="I48" t="n">
-        <v>-88.11</v>
+        <v>-88.03</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>5322.952106 ADA + cash 0.00</t>
+          <t>5293.715491 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ADA/DOT</t>
+          <t>ADA/BTC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5559,7 +5559,7 @@
         <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>1393</v>
+        <v>1811</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -5568,14 +5568,14 @@
         <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>1182.94</v>
+        <v>1194.17</v>
       </c>
       <c r="I49" t="n">
-        <v>-88.17</v>
+        <v>-88.06</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>5293.715491 ADA + cash 0.00</t>
+          <t>5281.154221 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ADA/BTC</t>
+          <t>ADA/TRX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5599,7 +5599,7 @@
         <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>1811</v>
+        <v>1783</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -5608,14 +5608,14 @@
         <v>10000</v>
       </c>
       <c r="H50" t="n">
-        <v>1180.13</v>
+        <v>1184.29</v>
       </c>
       <c r="I50" t="n">
-        <v>-88.2</v>
+        <v>-88.16</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>5281.154221 ADA + cash 0.00</t>
+          <t>5237.423115 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ADA/TRX</t>
+          <t>DOT/BNB</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5639,7 +5639,7 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1783</v>
+        <v>1659</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -5648,14 +5648,14 @@
         <v>10000</v>
       </c>
       <c r="H51" t="n">
-        <v>1170.36</v>
+        <v>1182.71</v>
       </c>
       <c r="I51" t="n">
-        <v>-88.3</v>
+        <v>-88.17</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>5237.423115 ADA + cash 0.00</t>
+          <t>1046.926411 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -5688,10 +5688,10 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>1124.83</v>
+        <v>1128</v>
       </c>
       <c r="I52" t="n">
-        <v>-88.75</v>
+        <v>-88.72</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -5728,10 +5728,10 @@
         <v>10000</v>
       </c>
       <c r="H53" t="n">
-        <v>738.65</v>
+        <v>736.0700000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>-92.61</v>
+        <v>-92.64</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -5768,10 +5768,10 @@
         <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>708.04</v>
+        <v>705.5599999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>-92.92</v>
+        <v>-92.94</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>10000</v>
       </c>
       <c r="H55" t="n">
-        <v>702.4299999999999</v>
+        <v>699.97</v>
       </c>
       <c r="I55" t="n">
-        <v>-92.98</v>
+        <v>-93</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -5848,10 +5848,10 @@
         <v>10000</v>
       </c>
       <c r="H56" t="n">
-        <v>680.04</v>
+        <v>677.66</v>
       </c>
       <c r="I56" t="n">
-        <v>-93.2</v>
+        <v>-93.22</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -5888,10 +5888,10 @@
         <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>673.8099999999999</v>
+        <v>675.71</v>
       </c>
       <c r="I57" t="n">
-        <v>-93.26000000000001</v>
+        <v>-93.23999999999999</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -5928,10 +5928,10 @@
         <v>10000</v>
       </c>
       <c r="H58" t="n">
-        <v>669.79</v>
+        <v>667.45</v>
       </c>
       <c r="I58" t="n">
-        <v>-93.3</v>
+        <v>-93.33</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -5968,10 +5968,10 @@
         <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>660.9</v>
+        <v>662.77</v>
       </c>
       <c r="I59" t="n">
-        <v>-93.39</v>
+        <v>-93.37</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -6008,10 +6008,10 @@
         <v>10000</v>
       </c>
       <c r="H60" t="n">
-        <v>625.33</v>
+        <v>621.4299999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-93.75</v>
+        <v>-93.79000000000001</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -6048,10 +6048,10 @@
         <v>10000</v>
       </c>
       <c r="H61" t="n">
-        <v>575.34</v>
+        <v>573.33</v>
       </c>
       <c r="I61" t="n">
-        <v>-94.25</v>
+        <v>-94.27</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -6088,10 +6088,10 @@
         <v>10000</v>
       </c>
       <c r="H62" t="n">
-        <v>575.34</v>
+        <v>573.33</v>
       </c>
       <c r="I62" t="n">
-        <v>-94.25</v>
+        <v>-94.27</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -6128,10 +6128,10 @@
         <v>10000</v>
       </c>
       <c r="H63" t="n">
-        <v>575.34</v>
+        <v>573.33</v>
       </c>
       <c r="I63" t="n">
-        <v>-94.25</v>
+        <v>-94.27</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -6168,10 +6168,10 @@
         <v>10000</v>
       </c>
       <c r="H64" t="n">
-        <v>575.34</v>
+        <v>573.33</v>
       </c>
       <c r="I64" t="n">
-        <v>-94.25</v>
+        <v>-94.27</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -6208,10 +6208,10 @@
         <v>10000</v>
       </c>
       <c r="H65" t="n">
-        <v>575.34</v>
+        <v>573.33</v>
       </c>
       <c r="I65" t="n">
-        <v>-94.25</v>
+        <v>-94.27</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -6248,10 +6248,10 @@
         <v>10000</v>
       </c>
       <c r="H66" t="n">
-        <v>525.74</v>
+        <v>522.45</v>
       </c>
       <c r="I66" t="n">
-        <v>-94.73999999999999</v>
+        <v>-94.78</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>10000</v>
       </c>
       <c r="H67" t="n">
-        <v>519.38</v>
+        <v>520.85</v>
       </c>
       <c r="I67" t="n">
-        <v>-94.81</v>
+        <v>-94.79000000000001</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -6328,10 +6328,10 @@
         <v>10000</v>
       </c>
       <c r="H68" t="n">
-        <v>493.82</v>
+        <v>490.74</v>
       </c>
       <c r="I68" t="n">
-        <v>-95.06</v>
+        <v>-95.09</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
         <v>10000</v>
       </c>
       <c r="H69" t="n">
-        <v>442.3</v>
+        <v>439.53</v>
       </c>
       <c r="I69" t="n">
-        <v>-95.58</v>
+        <v>-95.59999999999999</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -6408,10 +6408,10 @@
         <v>10000</v>
       </c>
       <c r="H70" t="n">
-        <v>140</v>
+        <v>141.46</v>
       </c>
       <c r="I70" t="n">
-        <v>-98.59999999999999</v>
+        <v>-98.59</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -6448,10 +6448,10 @@
         <v>10000</v>
       </c>
       <c r="H71" t="n">
-        <v>102.07</v>
+        <v>103.13</v>
       </c>
       <c r="I71" t="n">
-        <v>-98.98</v>
+        <v>-98.97</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         <v>10000</v>
       </c>
       <c r="H72" t="n">
-        <v>99.76000000000001</v>
+        <v>100.8</v>
       </c>
       <c r="I72" t="n">
-        <v>-99</v>
+        <v>-98.98999999999999</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -6528,10 +6528,10 @@
         <v>10000</v>
       </c>
       <c r="H73" t="n">
-        <v>99.04000000000001</v>
+        <v>100.07</v>
       </c>
       <c r="I73" t="n">
-        <v>-99.01000000000001</v>
+        <v>-99</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -6568,10 +6568,10 @@
         <v>10000</v>
       </c>
       <c r="H74" t="n">
-        <v>97.31999999999999</v>
+        <v>98.33</v>
       </c>
       <c r="I74" t="n">
-        <v>-99.03</v>
+        <v>-99.02</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -6608,10 +6608,10 @@
         <v>10000</v>
       </c>
       <c r="H75" t="n">
-        <v>93.83</v>
+        <v>94.8</v>
       </c>
       <c r="I75" t="n">
-        <v>-99.06</v>
+        <v>-99.05</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -6648,10 +6648,10 @@
         <v>10000</v>
       </c>
       <c r="H76" t="n">
-        <v>93.3</v>
+        <v>94.28</v>
       </c>
       <c r="I76" t="n">
-        <v>-99.06999999999999</v>
+        <v>-99.06</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -6688,10 +6688,10 @@
         <v>10000</v>
       </c>
       <c r="H77" t="n">
-        <v>91.22</v>
+        <v>92.17</v>
       </c>
       <c r="I77" t="n">
-        <v>-99.09</v>
+        <v>-99.08</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -6728,10 +6728,10 @@
         <v>10000</v>
       </c>
       <c r="H78" t="n">
-        <v>83.06999999999999</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>-99.17</v>
+        <v>-99.16</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         <v>10000</v>
       </c>
       <c r="H79" t="n">
-        <v>80.84999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="I79" t="n">
-        <v>-99.19</v>
+        <v>-99.18000000000001</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -6874,10 +6874,10 @@
         <v>10000</v>
       </c>
       <c r="H2" t="n">
-        <v>105834.93</v>
+        <v>104820.2</v>
       </c>
       <c r="I2" t="n">
-        <v>958.35</v>
+        <v>948.2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -6914,10 +6914,10 @@
         <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>98784.08</v>
+        <v>98525.97</v>
       </c>
       <c r="I3" t="n">
-        <v>887.84</v>
+        <v>885.26</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -6954,10 +6954,10 @@
         <v>10000</v>
       </c>
       <c r="H4" t="n">
-        <v>94224.85000000001</v>
+        <v>93321.42999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>842.25</v>
+        <v>833.21</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -6994,10 +6994,10 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>64239.94</v>
+        <v>63794.04</v>
       </c>
       <c r="I5" t="n">
-        <v>542.4</v>
+        <v>537.9400000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -7034,10 +7034,10 @@
         <v>10000</v>
       </c>
       <c r="H6" t="n">
-        <v>64218.42</v>
+        <v>63636.09</v>
       </c>
       <c r="I6" t="n">
-        <v>542.1799999999999</v>
+        <v>536.36</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -7074,10 +7074,10 @@
         <v>10000</v>
       </c>
       <c r="H7" t="n">
-        <v>58499.45</v>
+        <v>57938.57</v>
       </c>
       <c r="I7" t="n">
-        <v>484.99</v>
+        <v>479.39</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -7114,10 +7114,10 @@
         <v>10000</v>
       </c>
       <c r="H8" t="n">
-        <v>56127.73</v>
+        <v>56107.33</v>
       </c>
       <c r="I8" t="n">
-        <v>461.28</v>
+        <v>461.07</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -7154,10 +7154,10 @@
         <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>54651.29</v>
+        <v>54514.11</v>
       </c>
       <c r="I9" t="n">
-        <v>446.51</v>
+        <v>445.14</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -7194,10 +7194,10 @@
         <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>54151.39</v>
+        <v>53632.19</v>
       </c>
       <c r="I10" t="n">
-        <v>441.51</v>
+        <v>436.32</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -7234,10 +7234,10 @@
         <v>10000</v>
       </c>
       <c r="H11" t="n">
-        <v>52203.41</v>
+        <v>52072.37</v>
       </c>
       <c r="I11" t="n">
-        <v>422.03</v>
+        <v>420.72</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -7274,10 +7274,10 @@
         <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>46673.78</v>
+        <v>47532.55</v>
       </c>
       <c r="I12" t="n">
-        <v>366.74</v>
+        <v>375.33</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>45522.17</v>
+        <v>45407.91</v>
       </c>
       <c r="I13" t="n">
-        <v>355.22</v>
+        <v>354.08</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BTC/BNB</t>
+          <t>ADA/NEAR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -7342,10 +7342,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -7354,14 +7354,14 @@
         <v>10000</v>
       </c>
       <c r="H14" t="n">
-        <v>43844.58</v>
+        <v>43836.96</v>
       </c>
       <c r="I14" t="n">
-        <v>338.45</v>
+        <v>338.37</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.540504 BTC + cash 0.00</t>
+          <t>193865.923283 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ADA/NEAR</t>
+          <t>BTC/BNB</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -7394,14 +7394,14 @@
         <v>10000</v>
       </c>
       <c r="H15" t="n">
-        <v>43321.47</v>
+        <v>43828.65</v>
       </c>
       <c r="I15" t="n">
-        <v>333.21</v>
+        <v>338.29</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>193865.923283 ADA + cash 0.00</t>
+          <t>0.540504 BTC + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -7425,7 +7425,7 @@
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -7434,10 +7434,10 @@
         <v>10000</v>
       </c>
       <c r="H16" t="n">
-        <v>41722.59</v>
+        <v>42490.26</v>
       </c>
       <c r="I16" t="n">
-        <v>317.23</v>
+        <v>324.9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -7474,10 +7474,10 @@
         <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>41220.76</v>
+        <v>40846.98</v>
       </c>
       <c r="I17" t="n">
-        <v>312.21</v>
+        <v>308.47</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -7514,10 +7514,10 @@
         <v>10000</v>
       </c>
       <c r="H18" t="n">
-        <v>38650.4</v>
+        <v>39361.55</v>
       </c>
       <c r="I18" t="n">
-        <v>286.5</v>
+        <v>293.62</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -7554,10 +7554,10 @@
         <v>10000</v>
       </c>
       <c r="H19" t="n">
-        <v>36669.19</v>
+        <v>36577.15</v>
       </c>
       <c r="I19" t="n">
-        <v>266.69</v>
+        <v>265.77</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ETH/NEAR</t>
+          <t>ADA/ICP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>793</v>
+        <v>637</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -7594,14 +7594,14 @@
         <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>33674.07</v>
+        <v>33449.55</v>
       </c>
       <c r="I20" t="n">
-        <v>236.74</v>
+        <v>234.5</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12.786325 ETH + cash 0.00</t>
+          <t>11736.683740 ICP + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ADA/ICP</t>
+          <t>ETH/NEAR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -7622,10 +7622,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>637</v>
+        <v>793</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -7634,14 +7634,14 @@
         <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>33566.92</v>
+        <v>33440.33</v>
       </c>
       <c r="I21" t="n">
-        <v>235.67</v>
+        <v>234.4</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11736.683740 ICP + cash 0.00</t>
+          <t>12.786325 ETH + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -7674,10 +7674,10 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>33491.37</v>
+        <v>33187.67</v>
       </c>
       <c r="I22" t="n">
-        <v>234.91</v>
+        <v>231.88</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         <v>10000</v>
       </c>
       <c r="H23" t="n">
-        <v>31168.05</v>
+        <v>30885.42</v>
       </c>
       <c r="I23" t="n">
-        <v>211.68</v>
+        <v>208.85</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -7754,10 +7754,10 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>30341.52</v>
+        <v>30235.43</v>
       </c>
       <c r="I24" t="n">
-        <v>203.42</v>
+        <v>202.35</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -7794,10 +7794,10 @@
         <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>27770.3</v>
+        <v>27518.48</v>
       </c>
       <c r="I25" t="n">
-        <v>177.7</v>
+        <v>175.18</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -7834,10 +7834,10 @@
         <v>10000</v>
       </c>
       <c r="H26" t="n">
-        <v>26494.12</v>
+        <v>26253.87</v>
       </c>
       <c r="I26" t="n">
-        <v>164.94</v>
+        <v>162.54</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -7874,10 +7874,10 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>23407.27</v>
+        <v>23244.8</v>
       </c>
       <c r="I27" t="n">
-        <v>134.07</v>
+        <v>132.45</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ICP/BTC</t>
+          <t>ADA/AAVE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -7905,7 +7905,7 @@
         <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>824</v>
+        <v>767</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -7914,14 +7914,14 @@
         <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>21548.24</v>
+        <v>21680.06</v>
       </c>
       <c r="I28" t="n">
-        <v>115.48</v>
+        <v>116.8</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>7534.348009 ICP + cash 0.00</t>
+          <t>95878.580571 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NEAR/HBAR</t>
+          <t>ICP/BTC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>957</v>
+        <v>824</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -7954,14 +7954,14 @@
         <v>10000</v>
       </c>
       <c r="H29" t="n">
-        <v>21509.26</v>
+        <v>21472.89</v>
       </c>
       <c r="I29" t="n">
-        <v>115.09</v>
+        <v>114.73</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>269952.347078 HBAR + cash 0.00</t>
+          <t>7534.348009 ICP + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ADA/AAVE</t>
+          <t>NEAR/HBAR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>767</v>
+        <v>957</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -7994,14 +7994,14 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>21425.12</v>
+        <v>21455.27</v>
       </c>
       <c r="I30" t="n">
-        <v>114.25</v>
+        <v>114.55</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>95878.580571 ADA + cash 0.00</t>
+          <t>269952.347078 HBAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -8034,10 +8034,10 @@
         <v>10000</v>
       </c>
       <c r="H31" t="n">
-        <v>20866.93</v>
+        <v>21115.22</v>
       </c>
       <c r="I31" t="n">
-        <v>108.67</v>
+        <v>111.15</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -8074,10 +8074,10 @@
         <v>10000</v>
       </c>
       <c r="H32" t="n">
-        <v>20385.14</v>
+        <v>20627.7</v>
       </c>
       <c r="I32" t="n">
-        <v>103.85</v>
+        <v>106.28</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -8114,10 +8114,10 @@
         <v>10000</v>
       </c>
       <c r="H33" t="n">
-        <v>19139.68</v>
+        <v>19006.83</v>
       </c>
       <c r="I33" t="n">
-        <v>91.40000000000001</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -8154,10 +8154,10 @@
         <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>18469.11</v>
+        <v>18340.92</v>
       </c>
       <c r="I34" t="n">
-        <v>84.69</v>
+        <v>83.41</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -8194,10 +8194,10 @@
         <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>18131</v>
+        <v>18005.15</v>
       </c>
       <c r="I35" t="n">
-        <v>81.31</v>
+        <v>80.05</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -8234,10 +8234,10 @@
         <v>10000</v>
       </c>
       <c r="H36" t="n">
-        <v>16167.47</v>
+        <v>16055.25</v>
       </c>
       <c r="I36" t="n">
-        <v>61.67</v>
+        <v>60.55</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -8274,10 +8274,10 @@
         <v>10000</v>
       </c>
       <c r="H37" t="n">
-        <v>15700.62</v>
+        <v>15645.72</v>
       </c>
       <c r="I37" t="n">
-        <v>57.01</v>
+        <v>56.46</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -8314,10 +8314,10 @@
         <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>15331.59</v>
+        <v>15277.98</v>
       </c>
       <c r="I38" t="n">
-        <v>53.32</v>
+        <v>52.78</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -8354,10 +8354,10 @@
         <v>10000</v>
       </c>
       <c r="H39" t="n">
-        <v>14888.26</v>
+        <v>14836.21</v>
       </c>
       <c r="I39" t="n">
-        <v>48.88</v>
+        <v>48.36</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -8394,10 +8394,10 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>14175.64</v>
+        <v>14344.32</v>
       </c>
       <c r="I40" t="n">
-        <v>41.76</v>
+        <v>43.44</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -8434,10 +8434,10 @@
         <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>13898.98</v>
+        <v>14064.37</v>
       </c>
       <c r="I41" t="n">
-        <v>38.99</v>
+        <v>40.64</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -8474,10 +8474,10 @@
         <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>13216.98</v>
+        <v>13170.76</v>
       </c>
       <c r="I42" t="n">
-        <v>32.17</v>
+        <v>31.71</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ICP/HBAR</t>
+          <t>ADA/LINK</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>1052</v>
+        <v>711</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -8514,14 +8514,14 @@
         <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>13031.81</v>
+        <v>13168.24</v>
       </c>
       <c r="I43" t="n">
-        <v>30.32</v>
+        <v>31.68</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4556.576852 ICP + cash 0.00</t>
+          <t>58235.624433 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ADA/LINK</t>
+          <t>ICP/HBAR</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>711</v>
+        <v>1052</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -8554,14 +8554,14 @@
         <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>13013.39</v>
+        <v>12986.24</v>
       </c>
       <c r="I44" t="n">
-        <v>30.13</v>
+        <v>29.86</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>58235.624433 ADA + cash 0.00</t>
+          <t>4556.576852 ICP + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -8594,10 +8594,10 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>12690.87</v>
+        <v>12841.88</v>
       </c>
       <c r="I45" t="n">
-        <v>26.91</v>
+        <v>28.42</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -8634,10 +8634,10 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>11180.36</v>
+        <v>11141.27</v>
       </c>
       <c r="I46" t="n">
-        <v>11.8</v>
+        <v>11.41</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -8674,10 +8674,10 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>4462.07</v>
+        <v>4434.2</v>
       </c>
       <c r="I47" t="n">
-        <v>-55.38</v>
+        <v>-55.66</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -8714,10 +8714,10 @@
         <v>10000</v>
       </c>
       <c r="H48" t="n">
-        <v>3718.41</v>
+        <v>3695.18</v>
       </c>
       <c r="I48" t="n">
-        <v>-62.82</v>
+        <v>-63.05</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -8754,10 +8754,10 @@
         <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>3660.38</v>
+        <v>3670.7</v>
       </c>
       <c r="I49" t="n">
-        <v>-63.4</v>
+        <v>-63.29</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -8794,10 +8794,10 @@
         <v>10000</v>
       </c>
       <c r="H50" t="n">
-        <v>3229.26</v>
+        <v>3209.09</v>
       </c>
       <c r="I50" t="n">
-        <v>-67.70999999999999</v>
+        <v>-67.91</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DOT/BTC</t>
+          <t>DOT/ATOM</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -8822,10 +8822,10 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>976</v>
+        <v>864</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -8834,14 +8834,14 @@
         <v>10000</v>
       </c>
       <c r="H51" t="n">
-        <v>3183.29</v>
+        <v>3173.27</v>
       </c>
       <c r="I51" t="n">
-        <v>-68.17</v>
+        <v>-68.27</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2800.218632 DOT + cash 0.00</t>
+          <t>1857.450413 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DOT/ATOM</t>
+          <t>DOT/BTC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>864</v>
+        <v>976</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -8874,14 +8874,14 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>3164.35</v>
+        <v>3163.41</v>
       </c>
       <c r="I52" t="n">
-        <v>-68.36</v>
+        <v>-68.37</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>1857.450413 ATOM + cash 0.00</t>
+          <t>2800.218632 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -8914,10 +8914,10 @@
         <v>10000</v>
       </c>
       <c r="H53" t="n">
-        <v>3141.18</v>
+        <v>3121.57</v>
       </c>
       <c r="I53" t="n">
-        <v>-68.59</v>
+        <v>-68.78</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -8954,10 +8954,10 @@
         <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>3069.57</v>
+        <v>3050.4</v>
       </c>
       <c r="I54" t="n">
-        <v>-69.3</v>
+        <v>-69.5</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -8994,10 +8994,10 @@
         <v>10000</v>
       </c>
       <c r="H55" t="n">
-        <v>3041.6</v>
+        <v>3050.17</v>
       </c>
       <c r="I55" t="n">
-        <v>-69.58</v>
+        <v>-69.5</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -9034,10 +9034,10 @@
         <v>10000</v>
       </c>
       <c r="H56" t="n">
-        <v>2932.38</v>
+        <v>2940.64</v>
       </c>
       <c r="I56" t="n">
-        <v>-70.68000000000001</v>
+        <v>-70.59</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -9074,10 +9074,10 @@
         <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>2930.2</v>
+        <v>2911.9</v>
       </c>
       <c r="I57" t="n">
-        <v>-70.7</v>
+        <v>-70.88</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -9114,10 +9114,10 @@
         <v>10000</v>
       </c>
       <c r="H58" t="n">
-        <v>2911.94</v>
+        <v>2893.75</v>
       </c>
       <c r="I58" t="n">
-        <v>-70.88</v>
+        <v>-71.06</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -9154,10 +9154,10 @@
         <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>2767.22</v>
+        <v>2749.93</v>
       </c>
       <c r="I59" t="n">
-        <v>-72.33</v>
+        <v>-72.5</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -9194,10 +9194,10 @@
         <v>10000</v>
       </c>
       <c r="H60" t="n">
-        <v>2767.22</v>
+        <v>2749.93</v>
       </c>
       <c r="I60" t="n">
-        <v>-72.33</v>
+        <v>-72.5</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -9234,10 +9234,10 @@
         <v>10000</v>
       </c>
       <c r="H61" t="n">
-        <v>2647.96</v>
+        <v>2655.42</v>
       </c>
       <c r="I61" t="n">
-        <v>-73.52</v>
+        <v>-73.45</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -9274,10 +9274,10 @@
         <v>10000</v>
       </c>
       <c r="H62" t="n">
-        <v>2601.6</v>
+        <v>2608.93</v>
       </c>
       <c r="I62" t="n">
-        <v>-73.98</v>
+        <v>-73.91</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -9314,10 +9314,10 @@
         <v>10000</v>
       </c>
       <c r="H63" t="n">
-        <v>2525.98</v>
+        <v>2533.1</v>
       </c>
       <c r="I63" t="n">
-        <v>-74.73999999999999</v>
+        <v>-74.67</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -9354,10 +9354,10 @@
         <v>10000</v>
       </c>
       <c r="H64" t="n">
-        <v>2497.88</v>
+        <v>2504.91</v>
       </c>
       <c r="I64" t="n">
-        <v>-75.02</v>
+        <v>-74.95</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -9394,10 +9394,10 @@
         <v>10000</v>
       </c>
       <c r="H65" t="n">
-        <v>2464.1</v>
+        <v>2471.05</v>
       </c>
       <c r="I65" t="n">
-        <v>-75.36</v>
+        <v>-75.29000000000001</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -9434,10 +9434,10 @@
         <v>10000</v>
       </c>
       <c r="H66" t="n">
-        <v>2458.06</v>
+        <v>2464.99</v>
       </c>
       <c r="I66" t="n">
-        <v>-75.42</v>
+        <v>-75.34999999999999</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -9474,10 +9474,10 @@
         <v>10000</v>
       </c>
       <c r="H67" t="n">
-        <v>2341.46</v>
+        <v>2348.06</v>
       </c>
       <c r="I67" t="n">
-        <v>-76.59</v>
+        <v>-76.52</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -9514,10 +9514,10 @@
         <v>10000</v>
       </c>
       <c r="H68" t="n">
-        <v>889.1900000000001</v>
+        <v>898.4400000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>-91.11</v>
+        <v>-91.02</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -9554,10 +9554,10 @@
         <v>10000</v>
       </c>
       <c r="H69" t="n">
-        <v>884.33</v>
+        <v>893.53</v>
       </c>
       <c r="I69" t="n">
-        <v>-91.16</v>
+        <v>-91.06</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -9594,10 +9594,10 @@
         <v>10000</v>
       </c>
       <c r="H70" t="n">
-        <v>682.63</v>
+        <v>689.73</v>
       </c>
       <c r="I70" t="n">
-        <v>-93.17</v>
+        <v>-93.09999999999999</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -9634,10 +9634,10 @@
         <v>10000</v>
       </c>
       <c r="H71" t="n">
-        <v>680.39</v>
+        <v>687.47</v>
       </c>
       <c r="I71" t="n">
-        <v>-93.2</v>
+        <v>-93.13</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -9674,10 +9674,10 @@
         <v>10000</v>
       </c>
       <c r="H72" t="n">
-        <v>588.22</v>
+        <v>594.34</v>
       </c>
       <c r="I72" t="n">
-        <v>-94.12</v>
+        <v>-94.06</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -9714,10 +9714,10 @@
         <v>10000</v>
       </c>
       <c r="H73" t="n">
-        <v>586.25</v>
+        <v>592.35</v>
       </c>
       <c r="I73" t="n">
-        <v>-94.14</v>
+        <v>-94.08</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -9754,10 +9754,10 @@
         <v>10000</v>
       </c>
       <c r="H74" t="n">
-        <v>583.0700000000001</v>
+        <v>589.14</v>
       </c>
       <c r="I74" t="n">
-        <v>-94.17</v>
+        <v>-94.11</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -9794,10 +9794,10 @@
         <v>10000</v>
       </c>
       <c r="H75" t="n">
-        <v>576.4</v>
+        <v>582.4</v>
       </c>
       <c r="I75" t="n">
-        <v>-94.23999999999999</v>
+        <v>-94.18000000000001</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -9834,10 +9834,10 @@
         <v>10000</v>
       </c>
       <c r="H76" t="n">
-        <v>568.3</v>
+        <v>574.21</v>
       </c>
       <c r="I76" t="n">
-        <v>-94.31999999999999</v>
+        <v>-94.26000000000001</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -9874,10 +9874,10 @@
         <v>10000</v>
       </c>
       <c r="H77" t="n">
-        <v>566.22</v>
+        <v>572.11</v>
       </c>
       <c r="I77" t="n">
-        <v>-94.34</v>
+        <v>-94.28</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -9914,10 +9914,10 @@
         <v>10000</v>
       </c>
       <c r="H78" t="n">
-        <v>563.49</v>
+        <v>569.35</v>
       </c>
       <c r="I78" t="n">
-        <v>-94.37</v>
+        <v>-94.31</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -9954,10 +9954,10 @@
         <v>10000</v>
       </c>
       <c r="H79" t="n">
-        <v>538.12</v>
+        <v>543.72</v>
       </c>
       <c r="I79" t="n">
-        <v>-94.62</v>
+        <v>-94.56</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -10060,10 +10060,10 @@
         <v>10000</v>
       </c>
       <c r="H2" t="n">
-        <v>107183.48</v>
+        <v>106903.42</v>
       </c>
       <c r="I2" t="n">
-        <v>971.83</v>
+        <v>969.03</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AAVE/TRX</t>
+          <t>ADA/NEAR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -10091,7 +10091,7 @@
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>394</v>
+        <v>364</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -10100,14 +10100,14 @@
         <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>99179.66</v>
+        <v>99833.19</v>
       </c>
       <c r="I3" t="n">
-        <v>891.8</v>
+        <v>898.33</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>708.426626 AAVE + cash 0.00</t>
+          <t>441505.363776 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADA/NEAR</t>
+          <t>AAVE/TRX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -10131,7 +10131,7 @@
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>364</v>
+        <v>394</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -10140,14 +10140,14 @@
         <v>10000</v>
       </c>
       <c r="H4" t="n">
-        <v>98659.23</v>
+        <v>98228.74000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>886.59</v>
+        <v>882.29</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>441505.363776 ADA + cash 0.00</t>
+          <t>708.426626 AAVE + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -10180,10 +10180,10 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>92827.42999999999</v>
+        <v>91985.67999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>828.27</v>
+        <v>819.86</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -10220,10 +10220,10 @@
         <v>10000</v>
       </c>
       <c r="H6" t="n">
-        <v>64282.32</v>
+        <v>63836.13</v>
       </c>
       <c r="I6" t="n">
-        <v>542.8200000000001</v>
+        <v>538.36</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -10260,10 +10260,10 @@
         <v>10000</v>
       </c>
       <c r="H7" t="n">
-        <v>61879.54</v>
+        <v>63018.08</v>
       </c>
       <c r="I7" t="n">
-        <v>518.8</v>
+        <v>530.1799999999999</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -10300,10 +10300,10 @@
         <v>10000</v>
       </c>
       <c r="H8" t="n">
-        <v>55767.59</v>
+        <v>55747.32</v>
       </c>
       <c r="I8" t="n">
-        <v>457.68</v>
+        <v>457.47</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -10340,10 +10340,10 @@
         <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>54651.29</v>
+        <v>54514.11</v>
       </c>
       <c r="I9" t="n">
-        <v>446.51</v>
+        <v>445.14</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -10380,10 +10380,10 @@
         <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>53334.07</v>
+        <v>53200.19</v>
       </c>
       <c r="I10" t="n">
-        <v>433.34</v>
+        <v>432</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -10420,10 +10420,10 @@
         <v>10000</v>
       </c>
       <c r="H11" t="n">
-        <v>52500.25</v>
+        <v>52024.18</v>
       </c>
       <c r="I11" t="n">
-        <v>425</v>
+        <v>420.24</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AAVE/BTC</t>
+          <t>BTC/NEAR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -10448,10 +10448,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>533</v>
+        <v>966</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -10460,14 +10460,14 @@
         <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>51367.67</v>
+        <v>51740.47</v>
       </c>
       <c r="I12" t="n">
-        <v>413.68</v>
+        <v>417.4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>366.912175 AAVE + cash 0.00</t>
+          <t>13787.531741 NEAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BTC/NEAR</t>
+          <t>AAVE/BTC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>966</v>
+        <v>533</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -10500,14 +10500,14 @@
         <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>50805.68</v>
+        <v>50875.16</v>
       </c>
       <c r="I13" t="n">
-        <v>408.06</v>
+        <v>408.75</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13787.531741 NEAR + cash 0.00</t>
+          <t>366.912175 AAVE + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -10540,10 +10540,10 @@
         <v>10000</v>
       </c>
       <c r="H14" t="n">
-        <v>44353.46</v>
+        <v>44337.34</v>
       </c>
       <c r="I14" t="n">
-        <v>343.53</v>
+        <v>343.37</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -10580,10 +10580,10 @@
         <v>10000</v>
       </c>
       <c r="H15" t="n">
-        <v>44090.2</v>
+        <v>43784.17</v>
       </c>
       <c r="I15" t="n">
-        <v>340.9</v>
+        <v>337.84</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -10620,10 +10620,10 @@
         <v>10000</v>
       </c>
       <c r="H16" t="n">
-        <v>41722.59</v>
+        <v>42490.26</v>
       </c>
       <c r="I16" t="n">
-        <v>317.23</v>
+        <v>324.9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -10660,10 +10660,10 @@
         <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>41272.37</v>
+        <v>40898.12</v>
       </c>
       <c r="I17" t="n">
-        <v>312.72</v>
+        <v>308.98</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -10700,10 +10700,10 @@
         <v>10000</v>
       </c>
       <c r="H18" t="n">
-        <v>38735.95</v>
+        <v>39448.67</v>
       </c>
       <c r="I18" t="n">
-        <v>287.36</v>
+        <v>294.49</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -10740,10 +10740,10 @@
         <v>10000</v>
       </c>
       <c r="H19" t="n">
-        <v>38650.4</v>
+        <v>39361.55</v>
       </c>
       <c r="I19" t="n">
-        <v>286.5</v>
+        <v>293.62</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -10780,10 +10780,10 @@
         <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>38641.8</v>
+        <v>39101.6</v>
       </c>
       <c r="I20" t="n">
-        <v>286.42</v>
+        <v>291.02</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -10820,10 +10820,10 @@
         <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>35472.67</v>
+        <v>35132.56</v>
       </c>
       <c r="I21" t="n">
-        <v>254.73</v>
+        <v>251.33</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -10860,10 +10860,10 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>33491.37</v>
+        <v>33187.67</v>
       </c>
       <c r="I22" t="n">
-        <v>234.91</v>
+        <v>231.88</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -10900,10 +10900,10 @@
         <v>10000</v>
       </c>
       <c r="H23" t="n">
-        <v>30341.52</v>
+        <v>30235.43</v>
       </c>
       <c r="I23" t="n">
-        <v>203.42</v>
+        <v>202.35</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -10940,10 +10940,10 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>29852.9</v>
+        <v>29777.96</v>
       </c>
       <c r="I24" t="n">
-        <v>198.53</v>
+        <v>197.78</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -10980,10 +10980,10 @@
         <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>26494.12</v>
+        <v>26253.87</v>
       </c>
       <c r="I25" t="n">
-        <v>164.94</v>
+        <v>162.54</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -11020,10 +11020,10 @@
         <v>10000</v>
       </c>
       <c r="H26" t="n">
-        <v>23407.27</v>
+        <v>23244.8</v>
       </c>
       <c r="I26" t="n">
-        <v>134.07</v>
+        <v>132.45</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -11060,10 +11060,10 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>22969.04</v>
+        <v>22911.39</v>
       </c>
       <c r="I27" t="n">
-        <v>129.69</v>
+        <v>129.11</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ICP/BTC</t>
+          <t>ADA/AAVE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -11091,7 +11091,7 @@
         <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>824</v>
+        <v>767</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -11100,14 +11100,14 @@
         <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>21548.24</v>
+        <v>21680.06</v>
       </c>
       <c r="I28" t="n">
-        <v>115.48</v>
+        <v>116.8</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>7534.348009 ICP + cash 0.00</t>
+          <t>95878.580571 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ADA/AAVE</t>
+          <t>ICP/BTC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -11131,7 +11131,7 @@
         <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>767</v>
+        <v>824</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -11140,14 +11140,14 @@
         <v>10000</v>
       </c>
       <c r="H29" t="n">
-        <v>21425.12</v>
+        <v>21472.89</v>
       </c>
       <c r="I29" t="n">
-        <v>114.25</v>
+        <v>114.73</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>95878.580571 ADA + cash 0.00</t>
+          <t>7534.348009 ICP + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -11180,10 +11180,10 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>19936.65</v>
+        <v>19755.86</v>
       </c>
       <c r="I30" t="n">
-        <v>99.37</v>
+        <v>97.56</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -11220,10 +11220,10 @@
         <v>10000</v>
       </c>
       <c r="H31" t="n">
-        <v>19362.74</v>
+        <v>19295.04</v>
       </c>
       <c r="I31" t="n">
-        <v>93.63</v>
+        <v>92.95</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -11260,10 +11260,10 @@
         <v>10000</v>
       </c>
       <c r="H32" t="n">
-        <v>19139.68</v>
+        <v>19006.83</v>
       </c>
       <c r="I32" t="n">
-        <v>91.40000000000001</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         <v>10000</v>
       </c>
       <c r="H33" t="n">
-        <v>18469.11</v>
+        <v>18340.92</v>
       </c>
       <c r="I33" t="n">
-        <v>84.69</v>
+        <v>83.41</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -11340,10 +11340,10 @@
         <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>18381.4</v>
+        <v>18253.81</v>
       </c>
       <c r="I34" t="n">
-        <v>83.81</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -11380,10 +11380,10 @@
         <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>17881.08</v>
+        <v>17818.56</v>
       </c>
       <c r="I35" t="n">
-        <v>78.81</v>
+        <v>78.19</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -11420,10 +11420,10 @@
         <v>10000</v>
       </c>
       <c r="H36" t="n">
-        <v>16167.47</v>
+        <v>16055.25</v>
       </c>
       <c r="I36" t="n">
-        <v>61.67</v>
+        <v>60.55</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -11460,10 +11460,10 @@
         <v>10000</v>
       </c>
       <c r="H37" t="n">
-        <v>15700.62</v>
+        <v>15645.72</v>
       </c>
       <c r="I37" t="n">
-        <v>57.01</v>
+        <v>56.46</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -11500,10 +11500,10 @@
         <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>15132.99</v>
+        <v>15313.06</v>
       </c>
       <c r="I38" t="n">
-        <v>51.33</v>
+        <v>53.13</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -11540,10 +11540,10 @@
         <v>10000</v>
       </c>
       <c r="H39" t="n">
-        <v>13898.98</v>
+        <v>14064.37</v>
       </c>
       <c r="I39" t="n">
-        <v>38.99</v>
+        <v>40.64</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -11580,10 +11580,10 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>13503.52</v>
+        <v>13664.2</v>
       </c>
       <c r="I40" t="n">
-        <v>35.04</v>
+        <v>36.64</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -11620,10 +11620,10 @@
         <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>13216.98</v>
+        <v>13170.76</v>
       </c>
       <c r="I41" t="n">
-        <v>32.17</v>
+        <v>31.71</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ICP/HBAR</t>
+          <t>ADA/ETH</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -11648,10 +11648,10 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>1052</v>
+        <v>851</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -11660,14 +11660,14 @@
         <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>13031.81</v>
+        <v>13049.43</v>
       </c>
       <c r="I42" t="n">
-        <v>30.32</v>
+        <v>30.49</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>4556.576852 ICP + cash 0.00</t>
+          <t>57710.177652 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ADA/ETH</t>
+          <t>ICP/HBAR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -11688,10 +11688,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>851</v>
+        <v>1052</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -11700,14 +11700,14 @@
         <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>12895.97</v>
+        <v>12986.24</v>
       </c>
       <c r="I43" t="n">
-        <v>28.96</v>
+        <v>29.86</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>57710.177652 ADA + cash 0.00</t>
+          <t>4556.576852 ICP + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -11740,10 +11740,10 @@
         <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>12416.48</v>
+        <v>12564.22</v>
       </c>
       <c r="I44" t="n">
-        <v>24.16</v>
+        <v>25.64</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -11780,10 +11780,10 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>11320.29</v>
+        <v>11280.71</v>
       </c>
       <c r="I45" t="n">
-        <v>13.2</v>
+        <v>12.81</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -11820,10 +11820,10 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>11180.36</v>
+        <v>11141.27</v>
       </c>
       <c r="I46" t="n">
-        <v>11.8</v>
+        <v>11.41</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -11860,10 +11860,10 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>6092.04</v>
+        <v>6109.21</v>
       </c>
       <c r="I47" t="n">
-        <v>-39.08</v>
+        <v>-38.91</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -11900,10 +11900,10 @@
         <v>10000</v>
       </c>
       <c r="H48" t="n">
-        <v>3810.68</v>
+        <v>3786.88</v>
       </c>
       <c r="I48" t="n">
-        <v>-61.89</v>
+        <v>-62.13</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -11940,10 +11940,10 @@
         <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>3326.85</v>
+        <v>3336.22</v>
       </c>
       <c r="I49" t="n">
-        <v>-66.73</v>
+        <v>-66.64</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -11980,10 +11980,10 @@
         <v>10000</v>
       </c>
       <c r="H50" t="n">
-        <v>3229.26</v>
+        <v>3209.09</v>
       </c>
       <c r="I50" t="n">
-        <v>-67.70999999999999</v>
+        <v>-67.91</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -12020,10 +12020,10 @@
         <v>10000</v>
       </c>
       <c r="H51" t="n">
-        <v>3183.29</v>
+        <v>3163.41</v>
       </c>
       <c r="I51" t="n">
-        <v>-68.17</v>
+        <v>-68.37</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -12060,10 +12060,10 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>3141.18</v>
+        <v>3121.57</v>
       </c>
       <c r="I52" t="n">
-        <v>-68.59</v>
+        <v>-68.78</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -12100,10 +12100,10 @@
         <v>10000</v>
       </c>
       <c r="H53" t="n">
-        <v>3122.26</v>
+        <v>3102.76</v>
       </c>
       <c r="I53" t="n">
-        <v>-68.78</v>
+        <v>-68.97</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -12140,10 +12140,10 @@
         <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>3069.57</v>
+        <v>3050.4</v>
       </c>
       <c r="I54" t="n">
-        <v>-69.3</v>
+        <v>-69.5</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -12180,10 +12180,10 @@
         <v>10000</v>
       </c>
       <c r="H55" t="n">
-        <v>3041.6</v>
+        <v>3050.17</v>
       </c>
       <c r="I55" t="n">
-        <v>-69.58</v>
+        <v>-69.5</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -12220,10 +12220,10 @@
         <v>10000</v>
       </c>
       <c r="H56" t="n">
-        <v>2982.7</v>
+        <v>2964.07</v>
       </c>
       <c r="I56" t="n">
-        <v>-70.17</v>
+        <v>-70.36</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -12260,10 +12260,10 @@
         <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>2911.94</v>
+        <v>2893.75</v>
       </c>
       <c r="I57" t="n">
-        <v>-70.88</v>
+        <v>-71.06</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DOT/LINK</t>
+          <t>ATOM/XCH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -12288,10 +12288,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>1088</v>
+        <v>820</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -12300,14 +12300,14 @@
         <v>10000</v>
       </c>
       <c r="H58" t="n">
-        <v>2767.22</v>
+        <v>2762.39</v>
       </c>
       <c r="I58" t="n">
-        <v>-72.33</v>
+        <v>-72.38</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2434.215331 DOT + cash 0.00</t>
+          <t>1616.946556 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -12340,10 +12340,10 @@
         <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>2767.22</v>
+        <v>2749.93</v>
       </c>
       <c r="I59" t="n">
-        <v>-72.33</v>
+        <v>-72.5</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ATOM/XCH</t>
+          <t>DOT/LINK</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -12368,10 +12368,10 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>820</v>
+        <v>1088</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -12380,14 +12380,14 @@
         <v>10000</v>
       </c>
       <c r="H60" t="n">
-        <v>2754.63</v>
+        <v>2749.93</v>
       </c>
       <c r="I60" t="n">
-        <v>-72.45</v>
+        <v>-72.5</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>1616.946556 ATOM + cash 0.00</t>
+          <t>2434.215331 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -12420,10 +12420,10 @@
         <v>10000</v>
       </c>
       <c r="H61" t="n">
-        <v>2647.96</v>
+        <v>2655.42</v>
       </c>
       <c r="I61" t="n">
-        <v>-73.52</v>
+        <v>-73.45</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -12460,10 +12460,10 @@
         <v>10000</v>
       </c>
       <c r="H62" t="n">
-        <v>2601.6</v>
+        <v>2608.93</v>
       </c>
       <c r="I62" t="n">
-        <v>-73.98</v>
+        <v>-73.91</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -12500,10 +12500,10 @@
         <v>10000</v>
       </c>
       <c r="H63" t="n">
-        <v>2525.98</v>
+        <v>2533.1</v>
       </c>
       <c r="I63" t="n">
-        <v>-74.73999999999999</v>
+        <v>-74.67</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -12540,10 +12540,10 @@
         <v>10000</v>
       </c>
       <c r="H64" t="n">
-        <v>2513.06</v>
+        <v>2520.14</v>
       </c>
       <c r="I64" t="n">
-        <v>-74.87</v>
+        <v>-74.8</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -12580,10 +12580,10 @@
         <v>10000</v>
       </c>
       <c r="H65" t="n">
-        <v>2497.88</v>
+        <v>2504.91</v>
       </c>
       <c r="I65" t="n">
-        <v>-75.02</v>
+        <v>-74.95</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -12620,10 +12620,10 @@
         <v>10000</v>
       </c>
       <c r="H66" t="n">
-        <v>2497.23</v>
+        <v>2504.26</v>
       </c>
       <c r="I66" t="n">
-        <v>-75.03</v>
+        <v>-74.95999999999999</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -12660,10 +12660,10 @@
         <v>10000</v>
       </c>
       <c r="H67" t="n">
-        <v>2458.06</v>
+        <v>2464.99</v>
       </c>
       <c r="I67" t="n">
-        <v>-75.42</v>
+        <v>-75.34999999999999</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -12700,10 +12700,10 @@
         <v>10000</v>
       </c>
       <c r="H68" t="n">
-        <v>2341.46</v>
+        <v>2348.06</v>
       </c>
       <c r="I68" t="n">
-        <v>-76.59</v>
+        <v>-76.52</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -12740,10 +12740,10 @@
         <v>10000</v>
       </c>
       <c r="H69" t="n">
-        <v>1763.81</v>
+        <v>1782.16</v>
       </c>
       <c r="I69" t="n">
-        <v>-82.36</v>
+        <v>-82.18000000000001</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -12780,10 +12780,10 @@
         <v>10000</v>
       </c>
       <c r="H70" t="n">
-        <v>884.33</v>
+        <v>893.53</v>
       </c>
       <c r="I70" t="n">
-        <v>-91.16</v>
+        <v>-91.06</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -12820,10 +12820,10 @@
         <v>10000</v>
       </c>
       <c r="H71" t="n">
-        <v>682.63</v>
+        <v>689.73</v>
       </c>
       <c r="I71" t="n">
-        <v>-93.17</v>
+        <v>-93.09999999999999</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -12860,10 +12860,10 @@
         <v>10000</v>
       </c>
       <c r="H72" t="n">
-        <v>588.22</v>
+        <v>594.34</v>
       </c>
       <c r="I72" t="n">
-        <v>-94.12</v>
+        <v>-94.06</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -12900,10 +12900,10 @@
         <v>10000</v>
       </c>
       <c r="H73" t="n">
-        <v>586.25</v>
+        <v>592.35</v>
       </c>
       <c r="I73" t="n">
-        <v>-94.14</v>
+        <v>-94.08</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -12940,10 +12940,10 @@
         <v>10000</v>
       </c>
       <c r="H74" t="n">
-        <v>583.0700000000001</v>
+        <v>589.14</v>
       </c>
       <c r="I74" t="n">
-        <v>-94.17</v>
+        <v>-94.11</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -12980,10 +12980,10 @@
         <v>10000</v>
       </c>
       <c r="H75" t="n">
-        <v>576.4</v>
+        <v>582.4</v>
       </c>
       <c r="I75" t="n">
-        <v>-94.23999999999999</v>
+        <v>-94.18000000000001</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -13020,10 +13020,10 @@
         <v>10000</v>
       </c>
       <c r="H76" t="n">
-        <v>568.3</v>
+        <v>574.21</v>
       </c>
       <c r="I76" t="n">
-        <v>-94.31999999999999</v>
+        <v>-94.26000000000001</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -13060,10 +13060,10 @@
         <v>10000</v>
       </c>
       <c r="H77" t="n">
-        <v>566.22</v>
+        <v>572.11</v>
       </c>
       <c r="I77" t="n">
-        <v>-94.34</v>
+        <v>-94.28</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -13100,10 +13100,10 @@
         <v>10000</v>
       </c>
       <c r="H78" t="n">
-        <v>563.49</v>
+        <v>569.35</v>
       </c>
       <c r="I78" t="n">
-        <v>-94.37</v>
+        <v>-94.31</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -13140,10 +13140,10 @@
         <v>10000</v>
       </c>
       <c r="H79" t="n">
-        <v>538.12</v>
+        <v>543.72</v>
       </c>
       <c r="I79" t="n">
-        <v>-94.62</v>
+        <v>-94.56</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -13246,10 +13246,10 @@
         <v>10000</v>
       </c>
       <c r="H2" t="n">
-        <v>14969.06</v>
+        <v>14865.16</v>
       </c>
       <c r="I2" t="n">
-        <v>49.69</v>
+        <v>48.65</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -13286,10 +13286,10 @@
         <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>14627.72</v>
+        <v>14526.19</v>
       </c>
       <c r="I3" t="n">
-        <v>46.28</v>
+        <v>45.26</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -13326,10 +13326,10 @@
         <v>10000</v>
       </c>
       <c r="H4" t="n">
-        <v>12912.92</v>
+        <v>12916.28</v>
       </c>
       <c r="I4" t="n">
-        <v>29.13</v>
+        <v>29.16</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -13366,10 +13366,10 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>11359.63</v>
+        <v>11329.94</v>
       </c>
       <c r="I5" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -13526,10 +13526,10 @@
         <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>10530.39</v>
+        <v>10493.57</v>
       </c>
       <c r="I9" t="n">
-        <v>5.3</v>
+        <v>4.94</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -13566,10 +13566,10 @@
         <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>10271.44</v>
+        <v>10235.52</v>
       </c>
       <c r="I10" t="n">
-        <v>2.71</v>
+        <v>2.36</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -13646,10 +13646,10 @@
         <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>9723.299999999999</v>
+        <v>9719.76</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.77</v>
+        <v>-2.8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -13686,10 +13686,10 @@
         <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>9475</v>
+        <v>9441.870000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.25</v>
+        <v>-5.58</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -13726,10 +13726,10 @@
         <v>10000</v>
       </c>
       <c r="H14" t="n">
-        <v>9023.690000000001</v>
+        <v>9000.120000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.76</v>
+        <v>-10</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -13806,10 +13806,10 @@
         <v>10000</v>
       </c>
       <c r="H16" t="n">
-        <v>8286.450000000001</v>
+        <v>8265.65</v>
       </c>
       <c r="I16" t="n">
-        <v>-17.14</v>
+        <v>-17.34</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -13846,10 +13846,10 @@
         <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>8271.92</v>
+        <v>8196.91</v>
       </c>
       <c r="I17" t="n">
-        <v>-17.28</v>
+        <v>-18.03</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -13886,10 +13886,10 @@
         <v>10000</v>
       </c>
       <c r="H18" t="n">
-        <v>8212.450000000001</v>
+        <v>8183.74</v>
       </c>
       <c r="I18" t="n">
-        <v>-17.88</v>
+        <v>-18.16</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -13926,10 +13926,10 @@
         <v>10000</v>
       </c>
       <c r="H19" t="n">
-        <v>8104.39</v>
+        <v>8127.22</v>
       </c>
       <c r="I19" t="n">
-        <v>-18.96</v>
+        <v>-18.73</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -13966,10 +13966,10 @@
         <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>8077.4</v>
+        <v>8074.47</v>
       </c>
       <c r="I20" t="n">
-        <v>-19.23</v>
+        <v>-19.26</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -14006,10 +14006,10 @@
         <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>7751.31</v>
+        <v>7748.49</v>
       </c>
       <c r="I21" t="n">
-        <v>-22.49</v>
+        <v>-22.52</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -14046,10 +14046,10 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>7620.94</v>
+        <v>7547.87</v>
       </c>
       <c r="I22" t="n">
-        <v>-23.79</v>
+        <v>-24.52</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -14086,10 +14086,10 @@
         <v>10000</v>
       </c>
       <c r="H23" t="n">
-        <v>7535.13</v>
+        <v>7508.78</v>
       </c>
       <c r="I23" t="n">
-        <v>-24.65</v>
+        <v>-24.91</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -14126,10 +14126,10 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>7104.88</v>
+        <v>7124.9</v>
       </c>
       <c r="I24" t="n">
-        <v>-28.95</v>
+        <v>-28.75</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -14166,10 +14166,10 @@
         <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>6977.1</v>
+        <v>6996.76</v>
       </c>
       <c r="I25" t="n">
-        <v>-30.23</v>
+        <v>-30.03</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -14206,10 +14206,10 @@
         <v>10000</v>
       </c>
       <c r="H26" t="n">
-        <v>6900.28</v>
+        <v>6852.39</v>
       </c>
       <c r="I26" t="n">
-        <v>-31</v>
+        <v>-31.48</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -14246,10 +14246,10 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>6688.89</v>
+        <v>6672.1</v>
       </c>
       <c r="I27" t="n">
-        <v>-33.11</v>
+        <v>-33.28</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -14286,10 +14286,10 @@
         <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>6038.62</v>
+        <v>5983.86</v>
       </c>
       <c r="I28" t="n">
-        <v>-39.61</v>
+        <v>-40.16</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -14326,10 +14326,10 @@
         <v>10000</v>
       </c>
       <c r="H29" t="n">
-        <v>5885.76</v>
+        <v>5844.9</v>
       </c>
       <c r="I29" t="n">
-        <v>-41.14</v>
+        <v>-41.55</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -14366,10 +14366,10 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>5885.76</v>
+        <v>5844.9</v>
       </c>
       <c r="I30" t="n">
-        <v>-41.14</v>
+        <v>-41.55</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -14406,10 +14406,10 @@
         <v>10000</v>
       </c>
       <c r="H31" t="n">
-        <v>5850.92</v>
+        <v>5794.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-41.49</v>
+        <v>-42.05</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -14446,10 +14446,10 @@
         <v>10000</v>
       </c>
       <c r="H32" t="n">
-        <v>5766.29</v>
+        <v>5782.54</v>
       </c>
       <c r="I32" t="n">
-        <v>-42.34</v>
+        <v>-42.17</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ETH/LINK</t>
+          <t>ICP/ATOM</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -14474,10 +14474,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>332</v>
+        <v>244</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -14486,14 +14486,14 @@
         <v>10000</v>
       </c>
       <c r="H33" t="n">
-        <v>5507.91</v>
+        <v>5498.45</v>
       </c>
       <c r="I33" t="n">
-        <v>-44.92</v>
+        <v>-45.02</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>444.354442 LINK + cash 0.00</t>
+          <t>3218.482067 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -14505,7 +14505,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ICP/ATOM</t>
+          <t>ETH/LINK</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -14514,10 +14514,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>244</v>
+        <v>332</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -14526,14 +14526,14 @@
         <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>5483.01</v>
+        <v>5457.96</v>
       </c>
       <c r="I34" t="n">
-        <v>-45.17</v>
+        <v>-45.42</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>3218.482067 ATOM + cash 0.00</t>
+          <t>444.354442 LINK + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -14545,19 +14545,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ICP/AAVE</t>
+          <t>ZRO/HBAR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -14566,14 +14566,14 @@
         <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>5299.67</v>
+        <v>5254.44</v>
       </c>
       <c r="I35" t="n">
-        <v>-47</v>
+        <v>-47.46</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>37.854819 AAVE + cash 0.00</t>
+          <t>66111.832284 HBAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -14585,19 +14585,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ZRO/HBAR</t>
+          <t>ICP/AAVE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -14606,14 +14606,14 @@
         <v>10000</v>
       </c>
       <c r="H36" t="n">
-        <v>5267.66</v>
+        <v>5248.86</v>
       </c>
       <c r="I36" t="n">
-        <v>-47.32</v>
+        <v>-47.51</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>66111.832284 HBAR + cash 0.00</t>
+          <t>37.854819 AAVE + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -14646,10 +14646,10 @@
         <v>10000</v>
       </c>
       <c r="H37" t="n">
-        <v>5251.27</v>
+        <v>5203.65</v>
       </c>
       <c r="I37" t="n">
-        <v>-47.49</v>
+        <v>-47.96</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -14686,10 +14686,10 @@
         <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>5251.27</v>
+        <v>5203.65</v>
       </c>
       <c r="I38" t="n">
-        <v>-47.49</v>
+        <v>-47.96</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -14726,10 +14726,10 @@
         <v>10000</v>
       </c>
       <c r="H39" t="n">
-        <v>5251.27</v>
+        <v>5203.65</v>
       </c>
       <c r="I39" t="n">
-        <v>-47.49</v>
+        <v>-47.96</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -14766,10 +14766,10 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>5251.27</v>
+        <v>5203.65</v>
       </c>
       <c r="I40" t="n">
-        <v>-47.49</v>
+        <v>-47.96</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -14806,10 +14806,10 @@
         <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>4916.92</v>
+        <v>4869.78</v>
       </c>
       <c r="I41" t="n">
-        <v>-50.83</v>
+        <v>-51.3</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -14846,10 +14846,10 @@
         <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>4893.21</v>
+        <v>4846.29</v>
       </c>
       <c r="I42" t="n">
-        <v>-51.07</v>
+        <v>-51.54</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>4656.82</v>
+        <v>4645.13</v>
       </c>
       <c r="I43" t="n">
-        <v>-53.43</v>
+        <v>-53.55</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -14926,10 +14926,10 @@
         <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>4640.86</v>
+        <v>4596.36</v>
       </c>
       <c r="I44" t="n">
-        <v>-53.59</v>
+        <v>-54.04</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -14966,10 +14966,10 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>4640.86</v>
+        <v>4596.36</v>
       </c>
       <c r="I45" t="n">
-        <v>-53.59</v>
+        <v>-54.04</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -15006,10 +15006,10 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>4640.86</v>
+        <v>4596.36</v>
       </c>
       <c r="I46" t="n">
-        <v>-53.59</v>
+        <v>-54.04</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -15046,10 +15046,10 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>4343.05</v>
+        <v>4332.15</v>
       </c>
       <c r="I47" t="n">
-        <v>-56.57</v>
+        <v>-56.68</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -15086,10 +15086,10 @@
         <v>10000</v>
       </c>
       <c r="H48" t="n">
-        <v>4006.67</v>
+        <v>4017.96</v>
       </c>
       <c r="I48" t="n">
-        <v>-59.93</v>
+        <v>-59.82</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -15126,10 +15126,10 @@
         <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>3969.73</v>
+        <v>3980.91</v>
       </c>
       <c r="I49" t="n">
-        <v>-60.3</v>
+        <v>-60.19</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -15166,10 +15166,10 @@
         <v>10000</v>
       </c>
       <c r="H50" t="n">
-        <v>3921.6</v>
+        <v>3962.4</v>
       </c>
       <c r="I50" t="n">
-        <v>-60.78</v>
+        <v>-60.38</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -15206,10 +15206,10 @@
         <v>10000</v>
       </c>
       <c r="H51" t="n">
-        <v>3747.22</v>
+        <v>3757.78</v>
       </c>
       <c r="I51" t="n">
-        <v>-62.53</v>
+        <v>-62.42</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -15246,10 +15246,10 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>3747.22</v>
+        <v>3757.78</v>
       </c>
       <c r="I52" t="n">
-        <v>-62.53</v>
+        <v>-62.42</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -15286,10 +15286,10 @@
         <v>10000</v>
       </c>
       <c r="H53" t="n">
-        <v>3620.84</v>
+        <v>3611.75</v>
       </c>
       <c r="I53" t="n">
-        <v>-63.79</v>
+        <v>-63.88</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DOT/ATOM</t>
+          <t>ETH/HBAR</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -15314,10 +15314,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>222</v>
+        <v>278</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -15326,14 +15326,14 @@
         <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>3564.51</v>
+        <v>3554.44</v>
       </c>
       <c r="I54" t="n">
-        <v>-64.34999999999999</v>
+        <v>-64.45999999999999</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>3135.560550 DOT + cash 0.00</t>
+          <t>44722.308707 HBAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ETH/HBAR</t>
+          <t>DOT/ATOM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -15354,10 +15354,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>278</v>
+        <v>222</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -15366,14 +15366,14 @@
         <v>10000</v>
       </c>
       <c r="H55" t="n">
-        <v>3563.38</v>
+        <v>3542.24</v>
       </c>
       <c r="I55" t="n">
-        <v>-64.37</v>
+        <v>-64.58</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>44722.308707 HBAR + cash 0.00</t>
+          <t>3135.560550 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15406,10 +15406,10 @@
         <v>10000</v>
       </c>
       <c r="H56" t="n">
-        <v>3526.25</v>
+        <v>3517.4</v>
       </c>
       <c r="I56" t="n">
-        <v>-64.73999999999999</v>
+        <v>-64.83</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -15446,10 +15446,10 @@
         <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>3509.24</v>
+        <v>3500.43</v>
       </c>
       <c r="I57" t="n">
-        <v>-64.91</v>
+        <v>-65</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -15486,10 +15486,10 @@
         <v>10000</v>
       </c>
       <c r="H58" t="n">
-        <v>3342.84</v>
+        <v>3334.45</v>
       </c>
       <c r="I58" t="n">
-        <v>-66.56999999999999</v>
+        <v>-66.66</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -15526,10 +15526,10 @@
         <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>3175.17</v>
+        <v>3208.21</v>
       </c>
       <c r="I59" t="n">
-        <v>-68.25</v>
+        <v>-67.92</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -15566,10 +15566,10 @@
         <v>10000</v>
       </c>
       <c r="H60" t="n">
-        <v>3160.6</v>
+        <v>3140.86</v>
       </c>
       <c r="I60" t="n">
-        <v>-68.39</v>
+        <v>-68.59</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -15606,10 +15606,10 @@
         <v>10000</v>
       </c>
       <c r="H61" t="n">
-        <v>2987.6</v>
+        <v>2968.94</v>
       </c>
       <c r="I61" t="n">
-        <v>-70.12</v>
+        <v>-70.31</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DOT/AAVE</t>
+          <t>ADA/NEAR</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -15637,7 +15637,7 @@
         <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>215</v>
+        <v>274</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -15646,14 +15646,14 @@
         <v>10000</v>
       </c>
       <c r="H62" t="n">
-        <v>2959.91</v>
+        <v>2950.37</v>
       </c>
       <c r="I62" t="n">
-        <v>-70.40000000000001</v>
+        <v>-70.5</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2603.717002 DOT + cash 0.00</t>
+          <t>13047.794641 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ADA/NEAR</t>
+          <t>DOT/AAVE</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -15677,7 +15677,7 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>274</v>
+        <v>215</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -15686,14 +15686,14 @@
         <v>10000</v>
       </c>
       <c r="H63" t="n">
-        <v>2915.67</v>
+        <v>2941.42</v>
       </c>
       <c r="I63" t="n">
-        <v>-70.84</v>
+        <v>-70.59</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>13047.794641 ADA + cash 0.00</t>
+          <t>2603.717002 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15726,10 +15726,10 @@
         <v>10000</v>
       </c>
       <c r="H64" t="n">
-        <v>2875.1</v>
+        <v>2905.01</v>
       </c>
       <c r="I64" t="n">
-        <v>-71.25</v>
+        <v>-70.95</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -15766,10 +15766,10 @@
         <v>10000</v>
       </c>
       <c r="H65" t="n">
-        <v>2870.25</v>
+        <v>2904.41</v>
       </c>
       <c r="I65" t="n">
-        <v>-71.3</v>
+        <v>-70.95999999999999</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -15806,10 +15806,10 @@
         <v>10000</v>
       </c>
       <c r="H66" t="n">
-        <v>2829.9</v>
+        <v>2812.23</v>
       </c>
       <c r="I66" t="n">
-        <v>-71.7</v>
+        <v>-71.88</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DOT/HBAR</t>
+          <t>ADA/ICP</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -15837,7 +15837,7 @@
         <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>282</v>
+        <v>331</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -15846,14 +15846,14 @@
         <v>10000</v>
       </c>
       <c r="H67" t="n">
-        <v>2826.5</v>
+        <v>2811.22</v>
       </c>
       <c r="I67" t="n">
-        <v>-71.73999999999999</v>
+        <v>-71.89</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2486.362185 DOT + cash 0.00</t>
+          <t>12432.415237 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15865,7 +15865,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ICP/DOT</t>
+          <t>DOT/HBAR</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -15874,10 +15874,10 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>331</v>
+        <v>282</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -15886,14 +15886,14 @@
         <v>10000</v>
       </c>
       <c r="H68" t="n">
-        <v>2790.2</v>
+        <v>2808.84</v>
       </c>
       <c r="I68" t="n">
-        <v>-72.09999999999999</v>
+        <v>-71.91</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2454.429919 DOT + cash 0.00</t>
+          <t>2486.362185 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15905,7 +15905,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ADA/ICP</t>
+          <t>ICP/DOT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -15914,7 +15914,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
         <v>331</v>
@@ -15926,14 +15926,14 @@
         <v>10000</v>
       </c>
       <c r="H69" t="n">
-        <v>2778.16</v>
+        <v>2772.77</v>
       </c>
       <c r="I69" t="n">
-        <v>-72.22</v>
+        <v>-72.27</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>12432.415237 ADA + cash 0.00</t>
+          <t>2454.429919 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15966,10 +15966,10 @@
         <v>10000</v>
       </c>
       <c r="H70" t="n">
-        <v>2716.21</v>
+        <v>2699.24</v>
       </c>
       <c r="I70" t="n">
-        <v>-72.84</v>
+        <v>-73.01000000000001</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -16006,10 +16006,10 @@
         <v>10000</v>
       </c>
       <c r="H71" t="n">
-        <v>2559.38</v>
+        <v>2543.4</v>
       </c>
       <c r="I71" t="n">
-        <v>-74.41</v>
+        <v>-74.56999999999999</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -16046,10 +16046,10 @@
         <v>10000</v>
       </c>
       <c r="H72" t="n">
-        <v>2559.38</v>
+        <v>2543.4</v>
       </c>
       <c r="I72" t="n">
-        <v>-74.41</v>
+        <v>-74.56999999999999</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -16086,10 +16086,10 @@
         <v>10000</v>
       </c>
       <c r="H73" t="n">
-        <v>2559.38</v>
+        <v>2543.4</v>
       </c>
       <c r="I73" t="n">
-        <v>-74.41</v>
+        <v>-74.56999999999999</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -16126,10 +16126,10 @@
         <v>10000</v>
       </c>
       <c r="H74" t="n">
-        <v>2559.38</v>
+        <v>2543.4</v>
       </c>
       <c r="I74" t="n">
-        <v>-74.41</v>
+        <v>-74.56999999999999</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -16166,10 +16166,10 @@
         <v>10000</v>
       </c>
       <c r="H75" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I75" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -16206,10 +16206,10 @@
         <v>10000</v>
       </c>
       <c r="H76" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I76" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -16246,10 +16246,10 @@
         <v>10000</v>
       </c>
       <c r="H77" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I77" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -16286,10 +16286,10 @@
         <v>10000</v>
       </c>
       <c r="H78" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I78" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -16326,10 +16326,10 @@
         <v>10000</v>
       </c>
       <c r="H79" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I79" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -16366,10 +16366,10 @@
         <v>10000</v>
       </c>
       <c r="H80" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I80" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -16406,10 +16406,10 @@
         <v>10000</v>
       </c>
       <c r="H81" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I81" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -16446,10 +16446,10 @@
         <v>10000</v>
       </c>
       <c r="H82" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I82" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -16486,10 +16486,10 @@
         <v>10000</v>
       </c>
       <c r="H83" t="n">
-        <v>2394.06</v>
+        <v>2418.97</v>
       </c>
       <c r="I83" t="n">
-        <v>-76.06</v>
+        <v>-75.81</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -16526,10 +16526,10 @@
         <v>10000</v>
       </c>
       <c r="H84" t="n">
-        <v>2258.17</v>
+        <v>2281.67</v>
       </c>
       <c r="I84" t="n">
-        <v>-77.42</v>
+        <v>-77.18000000000001</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -16566,10 +16566,10 @@
         <v>10000</v>
       </c>
       <c r="H85" t="n">
-        <v>2102.67</v>
+        <v>2124.54</v>
       </c>
       <c r="I85" t="n">
-        <v>-78.97</v>
+        <v>-78.75</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -16606,10 +16606,10 @@
         <v>10000</v>
       </c>
       <c r="H86" t="n">
-        <v>2052.16</v>
+        <v>2073.51</v>
       </c>
       <c r="I86" t="n">
-        <v>-79.48</v>
+        <v>-79.26000000000001</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -16646,10 +16646,10 @@
         <v>10000</v>
       </c>
       <c r="H87" t="n">
-        <v>2028.57</v>
+        <v>2049.67</v>
       </c>
       <c r="I87" t="n">
-        <v>-79.70999999999999</v>
+        <v>-79.5</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -16686,10 +16686,10 @@
         <v>10000</v>
       </c>
       <c r="H88" t="n">
-        <v>1968</v>
+        <v>1988.48</v>
       </c>
       <c r="I88" t="n">
-        <v>-80.31999999999999</v>
+        <v>-80.12</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -16726,10 +16726,10 @@
         <v>10000</v>
       </c>
       <c r="H89" t="n">
-        <v>1802.59</v>
+        <v>1821.34</v>
       </c>
       <c r="I89" t="n">
-        <v>-81.97</v>
+        <v>-81.79000000000001</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -16766,10 +16766,10 @@
         <v>10000</v>
       </c>
       <c r="H90" t="n">
-        <v>1632.27</v>
+        <v>1649.26</v>
       </c>
       <c r="I90" t="n">
-        <v>-83.68000000000001</v>
+        <v>-83.51000000000001</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -16806,10 +16806,10 @@
         <v>10000</v>
       </c>
       <c r="H91" t="n">
-        <v>1628.44</v>
+        <v>1645.39</v>
       </c>
       <c r="I91" t="n">
-        <v>-83.72</v>
+        <v>-83.55</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -16846,10 +16846,10 @@
         <v>10000</v>
       </c>
       <c r="H92" t="n">
-        <v>1556.03</v>
+        <v>1572.22</v>
       </c>
       <c r="I92" t="n">
-        <v>-84.44</v>
+        <v>-84.28</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -16992,10 +16992,10 @@
         <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>14187.98</v>
+        <v>14138.37</v>
       </c>
       <c r="I3" t="n">
-        <v>41.88</v>
+        <v>41.38</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -17072,10 +17072,10 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>12876.92</v>
+        <v>12843.27</v>
       </c>
       <c r="I5" t="n">
-        <v>28.77</v>
+        <v>28.43</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -17112,10 +17112,10 @@
         <v>10000</v>
       </c>
       <c r="H6" t="n">
-        <v>12767.55</v>
+        <v>12762.91</v>
       </c>
       <c r="I6" t="n">
-        <v>27.68</v>
+        <v>27.63</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -17152,10 +17152,10 @@
         <v>10000</v>
       </c>
       <c r="H7" t="n">
-        <v>11674.98</v>
+        <v>11645.68</v>
       </c>
       <c r="I7" t="n">
-        <v>16.75</v>
+        <v>16.46</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -17192,10 +17192,10 @@
         <v>10000</v>
       </c>
       <c r="H8" t="n">
-        <v>11658.05</v>
+        <v>11627.59</v>
       </c>
       <c r="I8" t="n">
-        <v>16.58</v>
+        <v>16.28</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -17232,10 +17232,10 @@
         <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>11611.04</v>
+        <v>11606.82</v>
       </c>
       <c r="I9" t="n">
-        <v>16.11</v>
+        <v>16.07</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NEAR/TRX</t>
+          <t>NEAR/XCH</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -17263,7 +17263,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>352</v>
+        <v>273</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -17272,14 +17272,14 @@
         <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>11499.48</v>
+        <v>11503.8</v>
       </c>
       <c r="I10" t="n">
-        <v>14.99</v>
+        <v>15.04</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>33955.228617 TRX + cash 0.00</t>
+          <t>7642.704492 XCH + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -17291,7 +17291,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NEAR/XCH</t>
+          <t>NEAR/TRX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -17303,7 +17303,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>273</v>
+        <v>352</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -17312,14 +17312,14 @@
         <v>10000</v>
       </c>
       <c r="H11" t="n">
-        <v>11385.34</v>
+        <v>11502.47</v>
       </c>
       <c r="I11" t="n">
-        <v>13.85</v>
+        <v>15.02</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>7642.704492 XCH + cash 0.00</t>
+          <t>33955.228617 TRX + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -17352,10 +17352,10 @@
         <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>10893.65</v>
+        <v>10855.56</v>
       </c>
       <c r="I12" t="n">
-        <v>8.94</v>
+        <v>8.56</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -17392,10 +17392,10 @@
         <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>10770.91</v>
+        <v>10767</v>
       </c>
       <c r="I13" t="n">
-        <v>7.71</v>
+        <v>7.67</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -17472,10 +17472,10 @@
         <v>10000</v>
       </c>
       <c r="H15" t="n">
-        <v>9528.15</v>
+        <v>9462.01</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.72</v>
+        <v>-5.38</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -17512,10 +17512,10 @@
         <v>10000</v>
       </c>
       <c r="H16" t="n">
-        <v>9475</v>
+        <v>9441.870000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-5.25</v>
+        <v>-5.58</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -17552,10 +17552,10 @@
         <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>9387.73</v>
+        <v>9302.6</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.12</v>
+        <v>-6.97</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -17592,10 +17592,10 @@
         <v>10000</v>
       </c>
       <c r="H18" t="n">
-        <v>9225.129999999999</v>
+        <v>9201.030000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-7.75</v>
+        <v>-7.99</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -17632,10 +17632,10 @@
         <v>10000</v>
       </c>
       <c r="H19" t="n">
-        <v>8996.58</v>
+        <v>8993.309999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-10.03</v>
+        <v>-10.07</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -17672,10 +17672,10 @@
         <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>8595.4</v>
+        <v>8535.74</v>
       </c>
       <c r="I20" t="n">
-        <v>-14.05</v>
+        <v>-14.64</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -17712,10 +17712,10 @@
         <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>8023.26</v>
+        <v>7946.33</v>
       </c>
       <c r="I21" t="n">
-        <v>-19.77</v>
+        <v>-20.54</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -17752,10 +17752,10 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>7698.54</v>
+        <v>7645.11</v>
       </c>
       <c r="I22" t="n">
-        <v>-23.01</v>
+        <v>-23.55</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -17792,10 +17792,10 @@
         <v>10000</v>
       </c>
       <c r="H23" t="n">
-        <v>7568.81</v>
+        <v>7590.14</v>
       </c>
       <c r="I23" t="n">
-        <v>-24.31</v>
+        <v>-24.1</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -17832,10 +17832,10 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>6999.37</v>
+        <v>6996.83</v>
       </c>
       <c r="I24" t="n">
-        <v>-30.01</v>
+        <v>-30.03</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -17872,10 +17872,10 @@
         <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>5885.76</v>
+        <v>5844.9</v>
       </c>
       <c r="I25" t="n">
-        <v>-41.14</v>
+        <v>-41.55</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -17912,10 +17912,10 @@
         <v>10000</v>
       </c>
       <c r="H26" t="n">
-        <v>5885.76</v>
+        <v>5844.9</v>
       </c>
       <c r="I26" t="n">
-        <v>-41.14</v>
+        <v>-41.55</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -17952,10 +17952,10 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>5885.76</v>
+        <v>5844.9</v>
       </c>
       <c r="I27" t="n">
-        <v>-41.14</v>
+        <v>-41.55</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -17992,10 +17992,10 @@
         <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>5885.76</v>
+        <v>5844.9</v>
       </c>
       <c r="I28" t="n">
-        <v>-41.14</v>
+        <v>-41.55</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -18032,10 +18032,10 @@
         <v>10000</v>
       </c>
       <c r="H29" t="n">
-        <v>5595</v>
+        <v>5541.36</v>
       </c>
       <c r="I29" t="n">
-        <v>-44.05</v>
+        <v>-44.59</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -18072,10 +18072,10 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>5507.91</v>
+        <v>5457.96</v>
       </c>
       <c r="I30" t="n">
-        <v>-44.92</v>
+        <v>-45.42</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -18112,10 +18112,10 @@
         <v>10000</v>
       </c>
       <c r="H31" t="n">
-        <v>5274.67</v>
+        <v>5261.43</v>
       </c>
       <c r="I31" t="n">
-        <v>-47.25</v>
+        <v>-47.39</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -18152,10 +18152,10 @@
         <v>10000</v>
       </c>
       <c r="H32" t="n">
-        <v>5251.27</v>
+        <v>5203.65</v>
       </c>
       <c r="I32" t="n">
-        <v>-47.49</v>
+        <v>-47.96</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>10000</v>
       </c>
       <c r="H33" t="n">
-        <v>5251.27</v>
+        <v>5203.65</v>
       </c>
       <c r="I33" t="n">
-        <v>-47.49</v>
+        <v>-47.96</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -18232,10 +18232,10 @@
         <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>5251.27</v>
+        <v>5203.65</v>
       </c>
       <c r="I34" t="n">
-        <v>-47.49</v>
+        <v>-47.96</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -18272,10 +18272,10 @@
         <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>5251.27</v>
+        <v>5203.65</v>
       </c>
       <c r="I35" t="n">
-        <v>-47.49</v>
+        <v>-47.96</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -18312,10 +18312,10 @@
         <v>10000</v>
       </c>
       <c r="H36" t="n">
-        <v>5251.27</v>
+        <v>5203.65</v>
       </c>
       <c r="I36" t="n">
-        <v>-47.49</v>
+        <v>-47.96</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -18352,10 +18352,10 @@
         <v>10000</v>
       </c>
       <c r="H37" t="n">
-        <v>5251.27</v>
+        <v>5203.65</v>
       </c>
       <c r="I37" t="n">
-        <v>-47.49</v>
+        <v>-47.96</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -18392,10 +18392,10 @@
         <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>5251.27</v>
+        <v>5203.65</v>
       </c>
       <c r="I38" t="n">
-        <v>-47.49</v>
+        <v>-47.96</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -18432,10 +18432,10 @@
         <v>10000</v>
       </c>
       <c r="H39" t="n">
-        <v>5251.27</v>
+        <v>5203.65</v>
       </c>
       <c r="I39" t="n">
-        <v>-47.49</v>
+        <v>-47.96</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>5251.27</v>
+        <v>5203.65</v>
       </c>
       <c r="I40" t="n">
-        <v>-47.49</v>
+        <v>-47.96</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -18512,10 +18512,10 @@
         <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>5000.92</v>
+        <v>4969.69</v>
       </c>
       <c r="I41" t="n">
-        <v>-49.99</v>
+        <v>-50.3</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -18552,10 +18552,10 @@
         <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>4865.3</v>
+        <v>4818.65</v>
       </c>
       <c r="I42" t="n">
-        <v>-51.35</v>
+        <v>-51.81</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -18592,10 +18592,10 @@
         <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>4640.86</v>
+        <v>4596.36</v>
       </c>
       <c r="I43" t="n">
-        <v>-53.59</v>
+        <v>-54.04</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -18632,10 +18632,10 @@
         <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>4640.86</v>
+        <v>4596.36</v>
       </c>
       <c r="I44" t="n">
-        <v>-53.59</v>
+        <v>-54.04</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>4640.86</v>
+        <v>4596.36</v>
       </c>
       <c r="I45" t="n">
-        <v>-53.59</v>
+        <v>-54.04</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -18712,10 +18712,10 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>4640.86</v>
+        <v>4596.36</v>
       </c>
       <c r="I46" t="n">
-        <v>-53.59</v>
+        <v>-54.04</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -18752,10 +18752,10 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>4640.86</v>
+        <v>4596.36</v>
       </c>
       <c r="I47" t="n">
-        <v>-53.59</v>
+        <v>-54.04</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -18792,10 +18792,10 @@
         <v>10000</v>
       </c>
       <c r="H48" t="n">
-        <v>4640.86</v>
+        <v>4596.36</v>
       </c>
       <c r="I48" t="n">
-        <v>-53.59</v>
+        <v>-54.04</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -18832,10 +18832,10 @@
         <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>4640.86</v>
+        <v>4596.36</v>
       </c>
       <c r="I49" t="n">
-        <v>-53.59</v>
+        <v>-54.04</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -18872,10 +18872,10 @@
         <v>10000</v>
       </c>
       <c r="H50" t="n">
-        <v>4534.9</v>
+        <v>4547.68</v>
       </c>
       <c r="I50" t="n">
-        <v>-54.65</v>
+        <v>-54.52</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -18912,10 +18912,10 @@
         <v>10000</v>
       </c>
       <c r="H51" t="n">
-        <v>4096.87</v>
+        <v>4108.41</v>
       </c>
       <c r="I51" t="n">
-        <v>-59.03</v>
+        <v>-58.92</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -18952,10 +18952,10 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>3993.01</v>
+        <v>4004.26</v>
       </c>
       <c r="I52" t="n">
-        <v>-60.07</v>
+        <v>-59.96</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -18992,10 +18992,10 @@
         <v>10000</v>
       </c>
       <c r="H53" t="n">
-        <v>3951.8</v>
+        <v>3941.88</v>
       </c>
       <c r="I53" t="n">
-        <v>-60.48</v>
+        <v>-60.58</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -19032,10 +19032,10 @@
         <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>3747.22</v>
+        <v>3757.78</v>
       </c>
       <c r="I54" t="n">
-        <v>-62.53</v>
+        <v>-62.42</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -19072,10 +19072,10 @@
         <v>10000</v>
       </c>
       <c r="H55" t="n">
-        <v>3747.22</v>
+        <v>3757.78</v>
       </c>
       <c r="I55" t="n">
-        <v>-62.53</v>
+        <v>-62.42</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -19112,10 +19112,10 @@
         <v>10000</v>
       </c>
       <c r="H56" t="n">
-        <v>3747.22</v>
+        <v>3757.78</v>
       </c>
       <c r="I56" t="n">
-        <v>-62.53</v>
+        <v>-62.42</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -19152,10 +19152,10 @@
         <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>3747.22</v>
+        <v>3757.78</v>
       </c>
       <c r="I57" t="n">
-        <v>-62.53</v>
+        <v>-62.42</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -19192,10 +19192,10 @@
         <v>10000</v>
       </c>
       <c r="H58" t="n">
-        <v>3747.22</v>
+        <v>3757.78</v>
       </c>
       <c r="I58" t="n">
-        <v>-62.53</v>
+        <v>-62.42</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -19232,10 +19232,10 @@
         <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>3620.84</v>
+        <v>3611.75</v>
       </c>
       <c r="I59" t="n">
-        <v>-63.79</v>
+        <v>-63.88</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -19272,10 +19272,10 @@
         <v>10000</v>
       </c>
       <c r="H60" t="n">
-        <v>3612.56</v>
+        <v>3603.5</v>
       </c>
       <c r="I60" t="n">
-        <v>-63.87</v>
+        <v>-63.97</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -19312,10 +19312,10 @@
         <v>10000</v>
       </c>
       <c r="H61" t="n">
-        <v>3563.38</v>
+        <v>3554.44</v>
       </c>
       <c r="I61" t="n">
-        <v>-64.37</v>
+        <v>-64.45999999999999</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -19352,10 +19352,10 @@
         <v>10000</v>
       </c>
       <c r="H62" t="n">
-        <v>3342.84</v>
+        <v>3334.45</v>
       </c>
       <c r="I62" t="n">
-        <v>-66.56999999999999</v>
+        <v>-66.66</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -19392,10 +19392,10 @@
         <v>10000</v>
       </c>
       <c r="H63" t="n">
-        <v>2743.85</v>
+        <v>2772.4</v>
       </c>
       <c r="I63" t="n">
-        <v>-72.56</v>
+        <v>-72.28</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -19432,10 +19432,10 @@
         <v>10000</v>
       </c>
       <c r="H64" t="n">
-        <v>2702.86</v>
+        <v>2685.98</v>
       </c>
       <c r="I64" t="n">
-        <v>-72.97</v>
+        <v>-73.14</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -19472,10 +19472,10 @@
         <v>10000</v>
       </c>
       <c r="H65" t="n">
-        <v>2559.38</v>
+        <v>2543.4</v>
       </c>
       <c r="I65" t="n">
-        <v>-74.41</v>
+        <v>-74.56999999999999</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -19512,10 +19512,10 @@
         <v>10000</v>
       </c>
       <c r="H66" t="n">
-        <v>2559.38</v>
+        <v>2543.4</v>
       </c>
       <c r="I66" t="n">
-        <v>-74.41</v>
+        <v>-74.56999999999999</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -19552,10 +19552,10 @@
         <v>10000</v>
       </c>
       <c r="H67" t="n">
-        <v>2559.38</v>
+        <v>2543.4</v>
       </c>
       <c r="I67" t="n">
-        <v>-74.41</v>
+        <v>-74.56999999999999</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -19592,10 +19592,10 @@
         <v>10000</v>
       </c>
       <c r="H68" t="n">
-        <v>2559.38</v>
+        <v>2543.4</v>
       </c>
       <c r="I68" t="n">
-        <v>-74.41</v>
+        <v>-74.56999999999999</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -19632,10 +19632,10 @@
         <v>10000</v>
       </c>
       <c r="H69" t="n">
-        <v>2559.38</v>
+        <v>2543.4</v>
       </c>
       <c r="I69" t="n">
-        <v>-74.41</v>
+        <v>-74.56999999999999</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -19672,10 +19672,10 @@
         <v>10000</v>
       </c>
       <c r="H70" t="n">
-        <v>2559.38</v>
+        <v>2543.4</v>
       </c>
       <c r="I70" t="n">
-        <v>-74.41</v>
+        <v>-74.56999999999999</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -19712,10 +19712,10 @@
         <v>10000</v>
       </c>
       <c r="H71" t="n">
-        <v>2559.38</v>
+        <v>2543.4</v>
       </c>
       <c r="I71" t="n">
-        <v>-74.41</v>
+        <v>-74.56999999999999</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -19752,10 +19752,10 @@
         <v>10000</v>
       </c>
       <c r="H72" t="n">
-        <v>2559.38</v>
+        <v>2543.4</v>
       </c>
       <c r="I72" t="n">
-        <v>-74.41</v>
+        <v>-74.56999999999999</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -19792,10 +19792,10 @@
         <v>10000</v>
       </c>
       <c r="H73" t="n">
-        <v>2559.38</v>
+        <v>2543.4</v>
       </c>
       <c r="I73" t="n">
-        <v>-74.41</v>
+        <v>-74.56999999999999</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -19832,10 +19832,10 @@
         <v>10000</v>
       </c>
       <c r="H74" t="n">
-        <v>2559.38</v>
+        <v>2543.4</v>
       </c>
       <c r="I74" t="n">
-        <v>-74.41</v>
+        <v>-74.56999999999999</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -19872,10 +19872,10 @@
         <v>10000</v>
       </c>
       <c r="H75" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I75" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -19912,10 +19912,10 @@
         <v>10000</v>
       </c>
       <c r="H76" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I76" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -19952,10 +19952,10 @@
         <v>10000</v>
       </c>
       <c r="H77" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I77" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -19992,10 +19992,10 @@
         <v>10000</v>
       </c>
       <c r="H78" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I78" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -20032,10 +20032,10 @@
         <v>10000</v>
       </c>
       <c r="H79" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I79" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -20072,10 +20072,10 @@
         <v>10000</v>
       </c>
       <c r="H80" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I80" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -20112,10 +20112,10 @@
         <v>10000</v>
       </c>
       <c r="H81" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I81" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -20152,10 +20152,10 @@
         <v>10000</v>
       </c>
       <c r="H82" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I82" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -20192,10 +20192,10 @@
         <v>10000</v>
       </c>
       <c r="H83" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I83" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -20232,10 +20232,10 @@
         <v>10000</v>
       </c>
       <c r="H84" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I84" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -20272,10 +20272,10 @@
         <v>10000</v>
       </c>
       <c r="H85" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I85" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -20312,10 +20312,10 @@
         <v>10000</v>
       </c>
       <c r="H86" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I86" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -20352,10 +20352,10 @@
         <v>10000</v>
       </c>
       <c r="H87" t="n">
-        <v>2491.46</v>
+        <v>2521.1</v>
       </c>
       <c r="I87" t="n">
-        <v>-75.09</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -20392,10 +20392,10 @@
         <v>10000</v>
       </c>
       <c r="H88" t="n">
-        <v>1803.85</v>
+        <v>1822.62</v>
       </c>
       <c r="I88" t="n">
-        <v>-81.95999999999999</v>
+        <v>-81.77</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -20432,10 +20432,10 @@
         <v>10000</v>
       </c>
       <c r="H89" t="n">
-        <v>1735.5</v>
+        <v>1753.55</v>
       </c>
       <c r="I89" t="n">
-        <v>-82.65000000000001</v>
+        <v>-82.45999999999999</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -20472,10 +20472,10 @@
         <v>10000</v>
       </c>
       <c r="H90" t="n">
-        <v>1556.03</v>
+        <v>1572.22</v>
       </c>
       <c r="I90" t="n">
-        <v>-84.44</v>
+        <v>-84.28</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -20512,10 +20512,10 @@
         <v>10000</v>
       </c>
       <c r="H91" t="n">
-        <v>1556.03</v>
+        <v>1572.22</v>
       </c>
       <c r="I91" t="n">
-        <v>-84.44</v>
+        <v>-84.28</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -20552,10 +20552,10 @@
         <v>10000</v>
       </c>
       <c r="H92" t="n">
-        <v>1556.03</v>
+        <v>1572.22</v>
       </c>
       <c r="I92" t="n">
-        <v>-84.44</v>
+        <v>-84.28</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>

--- a/pair_strategies_analysis.xlsx
+++ b/pair_strategies_analysis.xlsx
@@ -502,10 +502,10 @@
         <v>10000</v>
       </c>
       <c r="H2" t="n">
-        <v>46786.18</v>
+        <v>48404.05</v>
       </c>
       <c r="I2" t="n">
-        <v>367.86</v>
+        <v>384.04</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>27255.24</v>
+        <v>27260.65</v>
       </c>
       <c r="I3" t="n">
-        <v>172.55</v>
+        <v>172.61</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>10000</v>
       </c>
       <c r="H4" t="n">
-        <v>23257.93</v>
+        <v>23392.42</v>
       </c>
       <c r="I4" t="n">
-        <v>132.58</v>
+        <v>133.92</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -622,10 +622,10 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>17981.72</v>
+        <v>18603.53</v>
       </c>
       <c r="I5" t="n">
-        <v>79.81999999999999</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -662,10 +662,10 @@
         <v>10000</v>
       </c>
       <c r="H6" t="n">
-        <v>17721.41</v>
+        <v>17823.88</v>
       </c>
       <c r="I6" t="n">
-        <v>77.20999999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -702,10 +702,10 @@
         <v>10000</v>
       </c>
       <c r="H7" t="n">
-        <v>17070.86</v>
+        <v>17001.55</v>
       </c>
       <c r="I7" t="n">
-        <v>70.70999999999999</v>
+        <v>70.02</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         <v>10000</v>
       </c>
       <c r="H8" t="n">
-        <v>14288.35</v>
+        <v>14230.33</v>
       </c>
       <c r="I8" t="n">
-        <v>42.88</v>
+        <v>42.3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
         <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>12986.11</v>
+        <v>13061.2</v>
       </c>
       <c r="I9" t="n">
-        <v>29.86</v>
+        <v>30.61</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>11695.22</v>
+        <v>11716.32</v>
       </c>
       <c r="I10" t="n">
-        <v>16.95</v>
+        <v>17.16</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -862,10 +862,10 @@
         <v>10000</v>
       </c>
       <c r="H11" t="n">
-        <v>11286.81</v>
+        <v>11526.21</v>
       </c>
       <c r="I11" t="n">
-        <v>12.87</v>
+        <v>15.26</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
         <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>10197.01</v>
+        <v>10215.42</v>
       </c>
       <c r="I12" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -942,10 +942,10 @@
         <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>9212.74</v>
+        <v>9266.02</v>
       </c>
       <c r="I13" t="n">
-        <v>-7.87</v>
+        <v>-7.34</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -982,10 +982,10 @@
         <v>10000</v>
       </c>
       <c r="H14" t="n">
-        <v>8727.24</v>
+        <v>8809.450000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-12.73</v>
+        <v>-11.91</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1022,10 +1022,10 @@
         <v>10000</v>
       </c>
       <c r="H15" t="n">
-        <v>8575.5</v>
+        <v>8656.280000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-14.24</v>
+        <v>-13.44</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1062,10 +1062,10 @@
         <v>10000</v>
       </c>
       <c r="H16" t="n">
-        <v>8514.73</v>
+        <v>8530.1</v>
       </c>
       <c r="I16" t="n">
-        <v>-14.85</v>
+        <v>-14.7</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1102,10 +1102,10 @@
         <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>7927.69</v>
+        <v>8201.83</v>
       </c>
       <c r="I17" t="n">
-        <v>-20.72</v>
+        <v>-17.98</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         <v>10000</v>
       </c>
       <c r="H18" t="n">
-        <v>6571.31</v>
+        <v>6633.21</v>
       </c>
       <c r="I18" t="n">
-        <v>-34.29</v>
+        <v>-33.67</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         <v>10000</v>
       </c>
       <c r="H19" t="n">
-        <v>5790.91</v>
+        <v>5845.46</v>
       </c>
       <c r="I19" t="n">
-        <v>-42.09</v>
+        <v>-41.55</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1222,10 +1222,10 @@
         <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>5586.74</v>
+        <v>5779.93</v>
       </c>
       <c r="I20" t="n">
-        <v>-44.13</v>
+        <v>-42.2</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
         <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>5449.31</v>
+        <v>5480.82</v>
       </c>
       <c r="I21" t="n">
-        <v>-45.51</v>
+        <v>-45.19</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>5389.86</v>
+        <v>5412.65</v>
       </c>
       <c r="I22" t="n">
-        <v>-46.1</v>
+        <v>-45.87</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1342,10 +1342,10 @@
         <v>10000</v>
       </c>
       <c r="H23" t="n">
-        <v>5236.7</v>
+        <v>5266.98</v>
       </c>
       <c r="I23" t="n">
-        <v>-47.63</v>
+        <v>-47.33</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1382,10 +1382,10 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>4856.91</v>
+        <v>4877.45</v>
       </c>
       <c r="I24" t="n">
-        <v>-51.43</v>
+        <v>-51.23</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
         <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>4736.55</v>
+        <v>4756.57</v>
       </c>
       <c r="I25" t="n">
-        <v>-52.63</v>
+        <v>-52.43</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1462,10 +1462,10 @@
         <v>10000</v>
       </c>
       <c r="H26" t="n">
-        <v>4558.45</v>
+        <v>4716.08</v>
       </c>
       <c r="I26" t="n">
-        <v>-54.42</v>
+        <v>-52.84</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1502,10 +1502,10 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>3898.91</v>
+        <v>3912.59</v>
       </c>
       <c r="I27" t="n">
-        <v>-61.01</v>
+        <v>-60.87</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1542,10 +1542,10 @@
         <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>3774.54</v>
+        <v>3790.5</v>
       </c>
       <c r="I28" t="n">
-        <v>-62.25</v>
+        <v>-62.1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         <v>10000</v>
       </c>
       <c r="H29" t="n">
-        <v>3682.4</v>
+        <v>3695.32</v>
       </c>
       <c r="I29" t="n">
-        <v>-63.18</v>
+        <v>-63.05</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>2936.48</v>
+        <v>2948.9</v>
       </c>
       <c r="I30" t="n">
-        <v>-70.64</v>
+        <v>-70.51000000000001</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1662,10 +1662,10 @@
         <v>10000</v>
       </c>
       <c r="H31" t="n">
-        <v>2806.75</v>
+        <v>2818.61</v>
       </c>
       <c r="I31" t="n">
-        <v>-71.93000000000001</v>
+        <v>-71.81</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1702,10 +1702,10 @@
         <v>10000</v>
       </c>
       <c r="H32" t="n">
-        <v>2756.09</v>
+        <v>2767.74</v>
       </c>
       <c r="I32" t="n">
-        <v>-72.44</v>
+        <v>-72.31999999999999</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
         <v>10000</v>
       </c>
       <c r="H33" t="n">
-        <v>2504.49</v>
+        <v>2557.61</v>
       </c>
       <c r="I33" t="n">
-        <v>-74.95999999999999</v>
+        <v>-74.42</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1782,10 +1782,10 @@
         <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>2106.56</v>
+        <v>2135.29</v>
       </c>
       <c r="I34" t="n">
-        <v>-78.93000000000001</v>
+        <v>-78.65000000000001</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
         <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>1939.94</v>
+        <v>1966.4</v>
       </c>
       <c r="I35" t="n">
-        <v>-80.59999999999999</v>
+        <v>-80.34</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1862,10 +1862,10 @@
         <v>10000</v>
       </c>
       <c r="H36" t="n">
-        <v>1810.1</v>
+        <v>1848.49</v>
       </c>
       <c r="I36" t="n">
-        <v>-81.90000000000001</v>
+        <v>-81.52</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1902,10 +1902,10 @@
         <v>10000</v>
       </c>
       <c r="H37" t="n">
-        <v>1783.75</v>
+        <v>1821.59</v>
       </c>
       <c r="I37" t="n">
-        <v>-82.16</v>
+        <v>-81.78</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1942,10 +1942,10 @@
         <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>1753.9</v>
+        <v>1772.07</v>
       </c>
       <c r="I38" t="n">
-        <v>-82.45999999999999</v>
+        <v>-82.28</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
         <v>10000</v>
       </c>
       <c r="H39" t="n">
-        <v>1453.88</v>
+        <v>1468.94</v>
       </c>
       <c r="I39" t="n">
-        <v>-85.45999999999999</v>
+        <v>-85.31</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ICP/DOT</t>
+          <t>ADA/ATOM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2013,7 +2013,7 @@
         <v>7</v>
       </c>
       <c r="E40" t="n">
-        <v>1044</v>
+        <v>1347</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2022,14 +2022,14 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>1262.96</v>
+        <v>1278.71</v>
       </c>
       <c r="I40" t="n">
-        <v>-87.37</v>
+        <v>-87.20999999999999</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1117.957175 DOT + cash 0.00</t>
+          <t>738.413353 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ADA/ATOM</t>
+          <t>ICP/DOT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2053,7 +2053,7 @@
         <v>7</v>
       </c>
       <c r="E41" t="n">
-        <v>1347</v>
+        <v>1044</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2062,14 +2062,14 @@
         <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>1261.51</v>
+        <v>1276.04</v>
       </c>
       <c r="I41" t="n">
-        <v>-87.38</v>
+        <v>-87.23999999999999</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>738.413353 ATOM + cash 0.00</t>
+          <t>1117.957175 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -2102,10 +2102,10 @@
         <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>1235.01</v>
+        <v>1251.85</v>
       </c>
       <c r="I42" t="n">
-        <v>-87.65000000000001</v>
+        <v>-87.48</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>1221.74</v>
+        <v>1247.65</v>
       </c>
       <c r="I43" t="n">
-        <v>-87.78</v>
+        <v>-87.52</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2182,10 +2182,10 @@
         <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>1211.36</v>
+        <v>1237.05</v>
       </c>
       <c r="I44" t="n">
-        <v>-87.89</v>
+        <v>-87.63</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2222,10 +2222,10 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>1194.17</v>
+        <v>1219.5</v>
       </c>
       <c r="I45" t="n">
-        <v>-88.06</v>
+        <v>-87.8</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>1184.29</v>
+        <v>1209.4</v>
       </c>
       <c r="I46" t="n">
-        <v>-88.16</v>
+        <v>-87.91</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2302,10 +2302,10 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>1182.83</v>
+        <v>1186.98</v>
       </c>
       <c r="I47" t="n">
-        <v>-88.17</v>
+        <v>-88.13</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2342,10 +2342,10 @@
         <v>10000</v>
       </c>
       <c r="H48" t="n">
-        <v>1104.83</v>
+        <v>1108.7</v>
       </c>
       <c r="I48" t="n">
-        <v>-88.95</v>
+        <v>-88.91</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2382,10 +2382,10 @@
         <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>921.53</v>
+        <v>934.09</v>
       </c>
       <c r="I49" t="n">
-        <v>-90.78</v>
+        <v>-90.66</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2422,10 +2422,10 @@
         <v>10000</v>
       </c>
       <c r="H50" t="n">
-        <v>798.45</v>
+        <v>801.25</v>
       </c>
       <c r="I50" t="n">
-        <v>-92.02</v>
+        <v>-91.98999999999999</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2462,10 +2462,10 @@
         <v>10000</v>
       </c>
       <c r="H51" t="n">
-        <v>752.52</v>
+        <v>762.78</v>
       </c>
       <c r="I51" t="n">
-        <v>-92.47</v>
+        <v>-92.37</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2502,10 +2502,10 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>751.36</v>
+        <v>759.14</v>
       </c>
       <c r="I52" t="n">
-        <v>-92.48999999999999</v>
+        <v>-92.41</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         <v>10000</v>
       </c>
       <c r="H53" t="n">
-        <v>745.8</v>
+        <v>755.97</v>
       </c>
       <c r="I53" t="n">
-        <v>-92.54000000000001</v>
+        <v>-92.44</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2582,10 +2582,10 @@
         <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>693.5700000000001</v>
+        <v>703.03</v>
       </c>
       <c r="I54" t="n">
-        <v>-93.06</v>
+        <v>-92.97</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2622,10 +2622,10 @@
         <v>10000</v>
       </c>
       <c r="H55" t="n">
-        <v>667.45</v>
+        <v>669.79</v>
       </c>
       <c r="I55" t="n">
-        <v>-93.33</v>
+        <v>-93.3</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2662,10 +2662,10 @@
         <v>10000</v>
       </c>
       <c r="H56" t="n">
-        <v>661.75</v>
+        <v>664.0700000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-93.38</v>
+        <v>-93.36</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DOT/BTC</t>
+          <t>ETH/ATOM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>1711</v>
+        <v>1751</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2702,14 +2702,14 @@
         <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>617.49</v>
+        <v>624.98</v>
       </c>
       <c r="I57" t="n">
-        <v>-93.83</v>
+        <v>-93.75</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>546.595924 DOT + cash 0.00</t>
+          <t>360.907629 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ETH/ATOM</t>
+          <t>DOT/BTC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>1751</v>
+        <v>1711</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -2742,14 +2742,14 @@
         <v>10000</v>
       </c>
       <c r="H58" t="n">
-        <v>616.5700000000001</v>
+        <v>623.88</v>
       </c>
       <c r="I58" t="n">
-        <v>-93.83</v>
+        <v>-93.76000000000001</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>360.907629 ATOM + cash 0.00</t>
+          <t>546.595924 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -2782,10 +2782,10 @@
         <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>602.99</v>
+        <v>609.23</v>
       </c>
       <c r="I59" t="n">
-        <v>-93.97</v>
+        <v>-93.91</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2822,10 +2822,10 @@
         <v>10000</v>
       </c>
       <c r="H60" t="n">
-        <v>601.12</v>
+        <v>607.34</v>
       </c>
       <c r="I60" t="n">
-        <v>-93.98999999999999</v>
+        <v>-93.93000000000001</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         <v>10000</v>
       </c>
       <c r="H61" t="n">
-        <v>573.33</v>
+        <v>575.34</v>
       </c>
       <c r="I61" t="n">
-        <v>-94.27</v>
+        <v>-94.25</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2902,10 +2902,10 @@
         <v>10000</v>
       </c>
       <c r="H62" t="n">
-        <v>573.33</v>
+        <v>575.34</v>
       </c>
       <c r="I62" t="n">
-        <v>-94.27</v>
+        <v>-94.25</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2942,10 +2942,10 @@
         <v>10000</v>
       </c>
       <c r="H63" t="n">
-        <v>573.33</v>
+        <v>575.34</v>
       </c>
       <c r="I63" t="n">
-        <v>-94.27</v>
+        <v>-94.25</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2982,10 +2982,10 @@
         <v>10000</v>
       </c>
       <c r="H64" t="n">
-        <v>539.5599999999999</v>
+        <v>545.15</v>
       </c>
       <c r="I64" t="n">
-        <v>-94.59999999999999</v>
+        <v>-94.55</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
         <v>10000</v>
       </c>
       <c r="H65" t="n">
-        <v>493.27</v>
+        <v>498.38</v>
       </c>
       <c r="I65" t="n">
-        <v>-95.06999999999999</v>
+        <v>-95.02</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3062,10 +3062,10 @@
         <v>10000</v>
       </c>
       <c r="H66" t="n">
-        <v>490.74</v>
+        <v>495.82</v>
       </c>
       <c r="I66" t="n">
-        <v>-95.09</v>
+        <v>-95.04000000000001</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3102,10 +3102,10 @@
         <v>10000</v>
       </c>
       <c r="H67" t="n">
-        <v>429.7</v>
+        <v>434.15</v>
       </c>
       <c r="I67" t="n">
-        <v>-95.7</v>
+        <v>-95.66</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3142,10 +3142,10 @@
         <v>10000</v>
       </c>
       <c r="H68" t="n">
-        <v>261.91</v>
+        <v>265.27</v>
       </c>
       <c r="I68" t="n">
-        <v>-97.38</v>
+        <v>-97.34999999999999</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3182,10 +3182,10 @@
         <v>10000</v>
       </c>
       <c r="H69" t="n">
-        <v>209.86</v>
+        <v>212.55</v>
       </c>
       <c r="I69" t="n">
-        <v>-97.90000000000001</v>
+        <v>-97.87</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3222,10 +3222,10 @@
         <v>10000</v>
       </c>
       <c r="H70" t="n">
-        <v>194.25</v>
+        <v>196.74</v>
       </c>
       <c r="I70" t="n">
-        <v>-98.06</v>
+        <v>-98.03</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3262,10 +3262,10 @@
         <v>10000</v>
       </c>
       <c r="H71" t="n">
-        <v>155.6</v>
+        <v>157.6</v>
       </c>
       <c r="I71" t="n">
-        <v>-98.44</v>
+        <v>-98.42</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3302,10 +3302,10 @@
         <v>10000</v>
       </c>
       <c r="H72" t="n">
-        <v>133.13</v>
+        <v>134.84</v>
       </c>
       <c r="I72" t="n">
-        <v>-98.67</v>
+        <v>-98.65000000000001</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3342,10 +3342,10 @@
         <v>10000</v>
       </c>
       <c r="H73" t="n">
-        <v>111.29</v>
+        <v>112.71</v>
       </c>
       <c r="I73" t="n">
-        <v>-98.89</v>
+        <v>-98.87</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3382,10 +3382,10 @@
         <v>10000</v>
       </c>
       <c r="H74" t="n">
-        <v>108.77</v>
+        <v>110.16</v>
       </c>
       <c r="I74" t="n">
-        <v>-98.91</v>
+        <v>-98.90000000000001</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3422,10 +3422,10 @@
         <v>10000</v>
       </c>
       <c r="H75" t="n">
-        <v>107.93</v>
+        <v>109.32</v>
       </c>
       <c r="I75" t="n">
-        <v>-98.92</v>
+        <v>-98.91</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3462,10 +3462,10 @@
         <v>10000</v>
       </c>
       <c r="H76" t="n">
-        <v>94.8</v>
+        <v>96.02</v>
       </c>
       <c r="I76" t="n">
-        <v>-99.05</v>
+        <v>-99.04000000000001</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3502,10 +3502,10 @@
         <v>10000</v>
       </c>
       <c r="H77" t="n">
-        <v>93.97</v>
+        <v>95.17</v>
       </c>
       <c r="I77" t="n">
-        <v>-99.06</v>
+        <v>-99.05</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3542,10 +3542,10 @@
         <v>10000</v>
       </c>
       <c r="H78" t="n">
-        <v>91.39</v>
+        <v>92.56</v>
       </c>
       <c r="I78" t="n">
-        <v>-99.09</v>
+        <v>-99.06999999999999</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3582,10 +3582,10 @@
         <v>10000</v>
       </c>
       <c r="H79" t="n">
-        <v>91.34999999999999</v>
+        <v>92.52</v>
       </c>
       <c r="I79" t="n">
-        <v>-99.09</v>
+        <v>-99.06999999999999</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3688,10 +3688,10 @@
         <v>10000</v>
       </c>
       <c r="H2" t="n">
-        <v>50953.8</v>
+        <v>50963.91</v>
       </c>
       <c r="I2" t="n">
-        <v>409.54</v>
+        <v>409.64</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -3728,10 +3728,10 @@
         <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>31210.95</v>
+        <v>31391.42</v>
       </c>
       <c r="I3" t="n">
-        <v>212.11</v>
+        <v>213.91</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BNB/HBAR</t>
+          <t>AAVE/BNB</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>1323</v>
+        <v>1133</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -3768,14 +3768,14 @@
         <v>10000</v>
       </c>
       <c r="H4" t="n">
-        <v>20442.41</v>
+        <v>20865.79</v>
       </c>
       <c r="I4" t="n">
-        <v>104.42</v>
+        <v>108.66</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>257208.437107 HBAR + cash 0.00</t>
+          <t>145.454476 AAVE + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AAVE/BNB</t>
+          <t>BNB/HBAR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>1133</v>
+        <v>1323</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -3808,14 +3808,14 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>20168.37</v>
+        <v>20528.83</v>
       </c>
       <c r="I5" t="n">
-        <v>101.68</v>
+        <v>105.29</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>145.454476 AAVE + cash 0.00</t>
+          <t>257208.437107 HBAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -3848,10 +3848,10 @@
         <v>10000</v>
       </c>
       <c r="H6" t="n">
-        <v>15585.99</v>
+        <v>15676.11</v>
       </c>
       <c r="I6" t="n">
-        <v>55.86</v>
+        <v>56.76</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>10000</v>
       </c>
       <c r="H7" t="n">
-        <v>15408.51</v>
+        <v>15436.32</v>
       </c>
       <c r="I7" t="n">
-        <v>54.09</v>
+        <v>54.36</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BTC/BNB</t>
+          <t>LINK/TRX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>1565</v>
+        <v>1466</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -3928,14 +3928,14 @@
         <v>10000</v>
       </c>
       <c r="H8" t="n">
-        <v>13843.66</v>
+        <v>13823.1</v>
       </c>
       <c r="I8" t="n">
-        <v>38.44</v>
+        <v>38.23</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>18.133498 BNB + cash 0.00</t>
+          <t>1114.891895 LINK + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LINK/TRX</t>
+          <t>BTC/BNB</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1466</v>
+        <v>1565</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -3968,14 +3968,14 @@
         <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>13694.11</v>
+        <v>13787.44</v>
       </c>
       <c r="I9" t="n">
-        <v>36.94</v>
+        <v>37.87</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1114.891895 LINK + cash 0.00</t>
+          <t>18.133498 BNB + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BNB/TRX</t>
+          <t>ETH/NEAR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>1650</v>
+        <v>1378</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -4008,14 +4008,14 @@
         <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>12896.87</v>
+        <v>12957.05</v>
       </c>
       <c r="I10" t="n">
-        <v>28.97</v>
+        <v>29.57</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16.893319 BNB + cash 0.00</t>
+          <t>3432.876700 NEAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ETH/NEAR</t>
+          <t>BNB/TRX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1378</v>
+        <v>1650</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -4048,14 +4048,14 @@
         <v>10000</v>
       </c>
       <c r="H11" t="n">
-        <v>12882.56</v>
+        <v>12844.5</v>
       </c>
       <c r="I11" t="n">
-        <v>28.83</v>
+        <v>28.44</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3432.876700 NEAR + cash 0.00</t>
+          <t>16.893319 BNB + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -4088,10 +4088,10 @@
         <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>11305.54</v>
+        <v>11325.95</v>
       </c>
       <c r="I12" t="n">
-        <v>13.06</v>
+        <v>13.26</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>7538.31</v>
+        <v>7581.9</v>
       </c>
       <c r="I13" t="n">
-        <v>-24.62</v>
+        <v>-24.18</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -4168,10 +4168,10 @@
         <v>10000</v>
       </c>
       <c r="H14" t="n">
-        <v>6612.09</v>
+        <v>6674.37</v>
       </c>
       <c r="I14" t="n">
-        <v>-33.88</v>
+        <v>-33.26</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LINK/NEAR</t>
+          <t>ETH/AAVE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>1538</v>
+        <v>1618</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -4208,14 +4208,14 @@
         <v>10000</v>
       </c>
       <c r="H15" t="n">
-        <v>6079.59</v>
+        <v>6239.81</v>
       </c>
       <c r="I15" t="n">
-        <v>-39.2</v>
+        <v>-37.6</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>494.964121 LINK + cash 0.00</t>
+          <t>43.497424 AAVE + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ETH/AAVE</t>
+          <t>LINK/NEAR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>1618</v>
+        <v>1538</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -4248,14 +4248,14 @@
         <v>10000</v>
       </c>
       <c r="H16" t="n">
-        <v>6031.25</v>
+        <v>6136.86</v>
       </c>
       <c r="I16" t="n">
-        <v>-39.69</v>
+        <v>-38.63</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>43.497424 AAVE + cash 0.00</t>
+          <t>494.964121 LINK + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -4288,10 +4288,10 @@
         <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>5939.87</v>
+        <v>5950.59</v>
       </c>
       <c r="I17" t="n">
-        <v>-40.6</v>
+        <v>-40.49</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
         <v>10000</v>
       </c>
       <c r="H18" t="n">
-        <v>5790.91</v>
+        <v>5845.46</v>
       </c>
       <c r="I18" t="n">
-        <v>-42.09</v>
+        <v>-41.55</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LINK/AAVE</t>
+          <t>AAVE/TRX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4359,7 +4359,7 @@
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>1143</v>
+        <v>1741</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -4368,14 +4368,14 @@
         <v>10000</v>
       </c>
       <c r="H19" t="n">
-        <v>5702.12</v>
+        <v>5779.93</v>
       </c>
       <c r="I19" t="n">
-        <v>-42.98</v>
+        <v>-42.2</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>464.232018 LINK + cash 0.00</t>
+          <t>40.291654 AAVE + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AAVE/TRX</t>
+          <t>LINK/AAVE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4399,7 +4399,7 @@
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>1741</v>
+        <v>1143</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -4408,14 +4408,14 @@
         <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>5586.74</v>
+        <v>5755.83</v>
       </c>
       <c r="I20" t="n">
-        <v>-44.13</v>
+        <v>-42.44</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>40.291654 AAVE + cash 0.00</t>
+          <t>464.232018 LINK + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -4448,10 +4448,10 @@
         <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>5316.21</v>
+        <v>5366.29</v>
       </c>
       <c r="I21" t="n">
-        <v>-46.84</v>
+        <v>-46.34</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -4488,10 +4488,10 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>5313.99</v>
+        <v>5344.72</v>
       </c>
       <c r="I22" t="n">
-        <v>-46.86</v>
+        <v>-46.55</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -4528,10 +4528,10 @@
         <v>10000</v>
       </c>
       <c r="H23" t="n">
-        <v>4558.45</v>
+        <v>4716.08</v>
       </c>
       <c r="I23" t="n">
-        <v>-54.42</v>
+        <v>-52.84</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -4568,10 +4568,10 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>4037.82</v>
+        <v>4054.89</v>
       </c>
       <c r="I24" t="n">
-        <v>-59.62</v>
+        <v>-59.45</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -4608,10 +4608,10 @@
         <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>3289.27</v>
+        <v>3359.03</v>
       </c>
       <c r="I25" t="n">
-        <v>-67.11</v>
+        <v>-66.41</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -4648,10 +4648,10 @@
         <v>10000</v>
       </c>
       <c r="H26" t="n">
-        <v>2923.26</v>
+        <v>2963.13</v>
       </c>
       <c r="I26" t="n">
-        <v>-70.77</v>
+        <v>-70.37</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -4688,10 +4688,10 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>2903.77</v>
+        <v>2916.04</v>
       </c>
       <c r="I27" t="n">
-        <v>-70.95999999999999</v>
+        <v>-70.84</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -4728,10 +4728,10 @@
         <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>2887.63</v>
+        <v>2899.84</v>
       </c>
       <c r="I28" t="n">
-        <v>-71.12</v>
+        <v>-71</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DOT/HBAR</t>
+          <t>DOT/TRX</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>1196</v>
+        <v>1446</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4768,14 +4768,14 @@
         <v>10000</v>
       </c>
       <c r="H29" t="n">
-        <v>2797.19</v>
+        <v>2825.31</v>
       </c>
       <c r="I29" t="n">
-        <v>-72.03</v>
+        <v>-71.75</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>35194.467746 HBAR + cash 0.00</t>
+          <t>2475.298542 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DOT/TRX</t>
+          <t>DOT/HBAR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>1446</v>
+        <v>1196</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -4808,14 +4808,14 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>2796.34</v>
+        <v>2809.01</v>
       </c>
       <c r="I30" t="n">
-        <v>-72.04000000000001</v>
+        <v>-71.91</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2475.298542 DOT + cash 0.00</t>
+          <t>35194.467746 HBAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -4848,10 +4848,10 @@
         <v>10000</v>
       </c>
       <c r="H31" t="n">
-        <v>2756.09</v>
+        <v>2767.74</v>
       </c>
       <c r="I31" t="n">
-        <v>-72.44</v>
+        <v>-72.31999999999999</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -4888,10 +4888,10 @@
         <v>10000</v>
       </c>
       <c r="H32" t="n">
-        <v>2458.78</v>
+        <v>2484.24</v>
       </c>
       <c r="I32" t="n">
-        <v>-75.41</v>
+        <v>-75.16</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -4928,10 +4928,10 @@
         <v>10000</v>
       </c>
       <c r="H33" t="n">
-        <v>2410.72</v>
+        <v>2420.91</v>
       </c>
       <c r="I33" t="n">
-        <v>-75.89</v>
+        <v>-75.79000000000001</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -4968,10 +4968,10 @@
         <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>2388.38</v>
+        <v>2398.47</v>
       </c>
       <c r="I34" t="n">
-        <v>-76.12</v>
+        <v>-76.02</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -5008,10 +5008,10 @@
         <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>2223.72</v>
+        <v>2254.05</v>
       </c>
       <c r="I35" t="n">
-        <v>-77.76000000000001</v>
+        <v>-77.45999999999999</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -5048,10 +5048,10 @@
         <v>10000</v>
       </c>
       <c r="H36" t="n">
-        <v>2197.8</v>
+        <v>2205.51</v>
       </c>
       <c r="I36" t="n">
-        <v>-78.02</v>
+        <v>-77.94</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         <v>10000</v>
       </c>
       <c r="H37" t="n">
-        <v>1873.66</v>
+        <v>1899.21</v>
       </c>
       <c r="I37" t="n">
-        <v>-81.26000000000001</v>
+        <v>-81.01000000000001</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -5128,10 +5128,10 @@
         <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>1630.56</v>
+        <v>1665.14</v>
       </c>
       <c r="I38" t="n">
-        <v>-83.69</v>
+        <v>-83.34999999999999</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -5168,10 +5168,10 @@
         <v>10000</v>
       </c>
       <c r="H39" t="n">
-        <v>1574.22</v>
+        <v>1590.53</v>
       </c>
       <c r="I39" t="n">
-        <v>-84.26000000000001</v>
+        <v>-84.09</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -5208,10 +5208,10 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>1421.79</v>
+        <v>1441.18</v>
       </c>
       <c r="I40" t="n">
-        <v>-85.78</v>
+        <v>-85.59</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -5248,10 +5248,10 @@
         <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>1315.87</v>
+        <v>1343.78</v>
       </c>
       <c r="I41" t="n">
-        <v>-86.84</v>
+        <v>-86.56</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -5288,10 +5288,10 @@
         <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>1315.48</v>
+        <v>1343.38</v>
       </c>
       <c r="I42" t="n">
-        <v>-86.84999999999999</v>
+        <v>-86.56999999999999</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>1290.73</v>
+        <v>1318.11</v>
       </c>
       <c r="I43" t="n">
-        <v>-87.09</v>
+        <v>-86.81999999999999</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -5368,10 +5368,10 @@
         <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>1226.77</v>
+        <v>1252.79</v>
       </c>
       <c r="I44" t="n">
-        <v>-87.73</v>
+        <v>-87.47</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -5408,10 +5408,10 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>1221.74</v>
+        <v>1247.65</v>
       </c>
       <c r="I45" t="n">
-        <v>-87.78</v>
+        <v>-87.52</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>1211.36</v>
+        <v>1237.05</v>
       </c>
       <c r="I46" t="n">
-        <v>-87.89</v>
+        <v>-87.63</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -5488,10 +5488,10 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>1203.63</v>
+        <v>1229.15</v>
       </c>
       <c r="I47" t="n">
-        <v>-87.95999999999999</v>
+        <v>-87.70999999999999</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -5528,10 +5528,10 @@
         <v>10000</v>
       </c>
       <c r="H48" t="n">
-        <v>1197.01</v>
+        <v>1222.4</v>
       </c>
       <c r="I48" t="n">
-        <v>-88.03</v>
+        <v>-87.78</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -5568,10 +5568,10 @@
         <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>1194.17</v>
+        <v>1219.5</v>
       </c>
       <c r="I49" t="n">
-        <v>-88.06</v>
+        <v>-87.8</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -5608,10 +5608,10 @@
         <v>10000</v>
       </c>
       <c r="H50" t="n">
-        <v>1184.29</v>
+        <v>1209.4</v>
       </c>
       <c r="I50" t="n">
-        <v>-88.16</v>
+        <v>-87.91</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -5648,10 +5648,10 @@
         <v>10000</v>
       </c>
       <c r="H51" t="n">
-        <v>1182.71</v>
+        <v>1194.96</v>
       </c>
       <c r="I51" t="n">
-        <v>-88.17</v>
+        <v>-88.05</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -5688,10 +5688,10 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>1128</v>
+        <v>1143.38</v>
       </c>
       <c r="I52" t="n">
-        <v>-88.72</v>
+        <v>-88.56999999999999</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -5728,10 +5728,10 @@
         <v>10000</v>
       </c>
       <c r="H53" t="n">
-        <v>736.0700000000001</v>
+        <v>738.65</v>
       </c>
       <c r="I53" t="n">
-        <v>-92.64</v>
+        <v>-92.61</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -5768,10 +5768,10 @@
         <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>705.5599999999999</v>
+        <v>708.04</v>
       </c>
       <c r="I54" t="n">
-        <v>-92.94</v>
+        <v>-92.92</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>10000</v>
       </c>
       <c r="H55" t="n">
-        <v>699.97</v>
+        <v>702.4299999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>-93</v>
+        <v>-92.98</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ICP/ATOM</t>
+          <t>BTC/ATOM</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5836,10 +5836,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>1203</v>
+        <v>1757</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -5848,14 +5848,14 @@
         <v>10000</v>
       </c>
       <c r="H56" t="n">
-        <v>677.66</v>
+        <v>684.92</v>
       </c>
       <c r="I56" t="n">
-        <v>-93.22</v>
+        <v>-93.15000000000001</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>237.776773 ICP + cash 0.00</t>
+          <t>395.521717 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BTC/ATOM</t>
+          <t>ICP/ATOM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1757</v>
+        <v>1203</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -5888,14 +5888,14 @@
         <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>675.71</v>
+        <v>680.04</v>
       </c>
       <c r="I57" t="n">
-        <v>-93.23999999999999</v>
+        <v>-93.2</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>395.521717 ATOM + cash 0.00</t>
+          <t>237.776773 ICP + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ICP/TRX</t>
+          <t>ETH/ATOM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1790</v>
+        <v>1724</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -5928,14 +5928,14 @@
         <v>10000</v>
       </c>
       <c r="H58" t="n">
-        <v>667.45</v>
+        <v>671.8</v>
       </c>
       <c r="I58" t="n">
-        <v>-93.33</v>
+        <v>-93.28</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>234.191349 ICP + cash 0.00</t>
+          <t>387.945228 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ETH/ATOM</t>
+          <t>ICP/TRX</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5956,10 +5956,10 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>1724</v>
+        <v>1790</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -5968,14 +5968,14 @@
         <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>662.77</v>
+        <v>669.79</v>
       </c>
       <c r="I59" t="n">
-        <v>-93.37</v>
+        <v>-93.3</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>387.945228 ATOM + cash 0.00</t>
+          <t>234.191349 ICP + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -6008,10 +6008,10 @@
         <v>10000</v>
       </c>
       <c r="H60" t="n">
-        <v>621.4299999999999</v>
+        <v>627.86</v>
       </c>
       <c r="I60" t="n">
-        <v>-93.79000000000001</v>
+        <v>-93.72</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -6048,10 +6048,10 @@
         <v>10000</v>
       </c>
       <c r="H61" t="n">
-        <v>573.33</v>
+        <v>575.34</v>
       </c>
       <c r="I61" t="n">
-        <v>-94.27</v>
+        <v>-94.25</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -6088,10 +6088,10 @@
         <v>10000</v>
       </c>
       <c r="H62" t="n">
-        <v>573.33</v>
+        <v>575.34</v>
       </c>
       <c r="I62" t="n">
-        <v>-94.27</v>
+        <v>-94.25</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -6128,10 +6128,10 @@
         <v>10000</v>
       </c>
       <c r="H63" t="n">
-        <v>573.33</v>
+        <v>575.34</v>
       </c>
       <c r="I63" t="n">
-        <v>-94.27</v>
+        <v>-94.25</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -6168,10 +6168,10 @@
         <v>10000</v>
       </c>
       <c r="H64" t="n">
-        <v>573.33</v>
+        <v>575.34</v>
       </c>
       <c r="I64" t="n">
-        <v>-94.27</v>
+        <v>-94.25</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -6208,10 +6208,10 @@
         <v>10000</v>
       </c>
       <c r="H65" t="n">
-        <v>573.33</v>
+        <v>575.34</v>
       </c>
       <c r="I65" t="n">
-        <v>-94.27</v>
+        <v>-94.25</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -6248,10 +6248,10 @@
         <v>10000</v>
       </c>
       <c r="H66" t="n">
-        <v>522.45</v>
+        <v>527.86</v>
       </c>
       <c r="I66" t="n">
-        <v>-94.78</v>
+        <v>-94.72</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>10000</v>
       </c>
       <c r="H67" t="n">
-        <v>520.85</v>
+        <v>527.95</v>
       </c>
       <c r="I67" t="n">
-        <v>-94.79000000000001</v>
+        <v>-94.72</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -6328,10 +6328,10 @@
         <v>10000</v>
       </c>
       <c r="H68" t="n">
-        <v>490.74</v>
+        <v>495.82</v>
       </c>
       <c r="I68" t="n">
-        <v>-95.09</v>
+        <v>-95.04000000000001</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
         <v>10000</v>
       </c>
       <c r="H69" t="n">
-        <v>439.53</v>
+        <v>444.09</v>
       </c>
       <c r="I69" t="n">
-        <v>-95.59999999999999</v>
+        <v>-95.56</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -6408,10 +6408,10 @@
         <v>10000</v>
       </c>
       <c r="H70" t="n">
-        <v>141.46</v>
+        <v>143.27</v>
       </c>
       <c r="I70" t="n">
-        <v>-98.59</v>
+        <v>-98.56999999999999</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -6448,10 +6448,10 @@
         <v>10000</v>
       </c>
       <c r="H71" t="n">
-        <v>103.13</v>
+        <v>104.45</v>
       </c>
       <c r="I71" t="n">
-        <v>-98.97</v>
+        <v>-98.95999999999999</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         <v>10000</v>
       </c>
       <c r="H72" t="n">
-        <v>100.8</v>
+        <v>102.09</v>
       </c>
       <c r="I72" t="n">
-        <v>-98.98999999999999</v>
+        <v>-98.98</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -6528,10 +6528,10 @@
         <v>10000</v>
       </c>
       <c r="H73" t="n">
-        <v>100.07</v>
+        <v>101.36</v>
       </c>
       <c r="I73" t="n">
-        <v>-99</v>
+        <v>-98.98999999999999</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -6568,10 +6568,10 @@
         <v>10000</v>
       </c>
       <c r="H74" t="n">
-        <v>98.33</v>
+        <v>99.59</v>
       </c>
       <c r="I74" t="n">
-        <v>-99.02</v>
+        <v>-99</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -6608,10 +6608,10 @@
         <v>10000</v>
       </c>
       <c r="H75" t="n">
-        <v>94.8</v>
+        <v>96.02</v>
       </c>
       <c r="I75" t="n">
-        <v>-99.05</v>
+        <v>-99.04000000000001</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -6648,10 +6648,10 @@
         <v>10000</v>
       </c>
       <c r="H76" t="n">
-        <v>94.28</v>
+        <v>95.48</v>
       </c>
       <c r="I76" t="n">
-        <v>-99.06</v>
+        <v>-99.05</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -6688,10 +6688,10 @@
         <v>10000</v>
       </c>
       <c r="H77" t="n">
-        <v>92.17</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>-99.08</v>
+        <v>-99.06999999999999</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -6728,10 +6728,10 @@
         <v>10000</v>
       </c>
       <c r="H78" t="n">
-        <v>83.93000000000001</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>-99.16</v>
+        <v>-99.15000000000001</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         <v>10000</v>
       </c>
       <c r="H79" t="n">
-        <v>81.7</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-99.18000000000001</v>
+        <v>-99.17</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -6874,10 +6874,10 @@
         <v>10000</v>
       </c>
       <c r="H2" t="n">
-        <v>104820.2</v>
+        <v>108444.9</v>
       </c>
       <c r="I2" t="n">
-        <v>948.2</v>
+        <v>984.45</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -6914,10 +6914,10 @@
         <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>98525.97</v>
+        <v>98125.89</v>
       </c>
       <c r="I3" t="n">
-        <v>885.26</v>
+        <v>881.26</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -6954,10 +6954,10 @@
         <v>10000</v>
       </c>
       <c r="H4" t="n">
-        <v>93321.42999999999</v>
+        <v>96548.5</v>
       </c>
       <c r="I4" t="n">
-        <v>833.21</v>
+        <v>865.48</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETH/HBAR</t>
+          <t>LINK/NEAR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6982,10 +6982,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -6994,14 +6994,14 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>63794.04</v>
+        <v>64235.52</v>
       </c>
       <c r="I5" t="n">
-        <v>537.9400000000001</v>
+        <v>542.36</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>24.392443 ETH + cash 0.00</t>
+          <t>5180.868692 LINK + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LINK/NEAR</t>
+          <t>ETH/HBAR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7022,10 +7022,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -7034,14 +7034,14 @@
         <v>10000</v>
       </c>
       <c r="H6" t="n">
-        <v>63636.09</v>
+        <v>63909.18</v>
       </c>
       <c r="I6" t="n">
-        <v>536.36</v>
+        <v>539.09</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5180.868692 LINK + cash 0.00</t>
+          <t>24.392443 ETH + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -7074,10 +7074,10 @@
         <v>10000</v>
       </c>
       <c r="H7" t="n">
-        <v>57938.57</v>
+        <v>59942.09</v>
       </c>
       <c r="I7" t="n">
-        <v>479.39</v>
+        <v>499.42</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -7114,10 +7114,10 @@
         <v>10000</v>
       </c>
       <c r="H8" t="n">
-        <v>56107.33</v>
+        <v>56118.45</v>
       </c>
       <c r="I8" t="n">
-        <v>461.07</v>
+        <v>461.18</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BTC/HBAR</t>
+          <t>AAVE/BNB</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7142,10 +7142,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>533</v>
+        <v>773</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -7154,14 +7154,14 @@
         <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>54514.11</v>
+        <v>55486.8</v>
       </c>
       <c r="I9" t="n">
-        <v>445.14</v>
+        <v>454.87</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>685901.865781 HBAR + cash 0.00</t>
+          <t>386.795903 AAVE + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AAVE/BNB</t>
+          <t>BTC/HBAR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>773</v>
+        <v>533</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -7194,14 +7194,14 @@
         <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>53632.19</v>
+        <v>54744.57</v>
       </c>
       <c r="I10" t="n">
-        <v>436.32</v>
+        <v>447.45</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>386.795903 AAVE + cash 0.00</t>
+          <t>685901.865781 HBAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -7234,10 +7234,10 @@
         <v>10000</v>
       </c>
       <c r="H11" t="n">
-        <v>52072.37</v>
+        <v>52292.51</v>
       </c>
       <c r="I11" t="n">
-        <v>420.72</v>
+        <v>422.93</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -7274,10 +7274,10 @@
         <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>47532.55</v>
+        <v>47807.41</v>
       </c>
       <c r="I12" t="n">
-        <v>375.33</v>
+        <v>378.07</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>45407.91</v>
+        <v>45599.88</v>
       </c>
       <c r="I13" t="n">
-        <v>354.08</v>
+        <v>356</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -7354,10 +7354,10 @@
         <v>10000</v>
       </c>
       <c r="H14" t="n">
-        <v>43836.96</v>
+        <v>44766.74</v>
       </c>
       <c r="I14" t="n">
-        <v>338.37</v>
+        <v>347.67</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -7394,10 +7394,10 @@
         <v>10000</v>
       </c>
       <c r="H15" t="n">
-        <v>43828.65</v>
+        <v>43837.34</v>
       </c>
       <c r="I15" t="n">
-        <v>338.29</v>
+        <v>338.37</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -7434,10 +7434,10 @@
         <v>10000</v>
       </c>
       <c r="H16" t="n">
-        <v>42490.26</v>
+        <v>42735.96</v>
       </c>
       <c r="I16" t="n">
-        <v>324.9</v>
+        <v>327.36</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -7474,10 +7474,10 @@
         <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>40846.98</v>
+        <v>41231.74</v>
       </c>
       <c r="I17" t="n">
-        <v>308.47</v>
+        <v>312.32</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -7514,10 +7514,10 @@
         <v>10000</v>
       </c>
       <c r="H18" t="n">
-        <v>39361.55</v>
+        <v>39589.15</v>
       </c>
       <c r="I18" t="n">
-        <v>293.62</v>
+        <v>295.89</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -7554,10 +7554,10 @@
         <v>10000</v>
       </c>
       <c r="H19" t="n">
-        <v>36577.15</v>
+        <v>36731.78</v>
       </c>
       <c r="I19" t="n">
-        <v>265.77</v>
+        <v>267.32</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -7594,10 +7594,10 @@
         <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>33449.55</v>
+        <v>33566.92</v>
       </c>
       <c r="I20" t="n">
-        <v>234.5</v>
+        <v>235.67</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -7634,10 +7634,10 @@
         <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>33440.33</v>
+        <v>33500.68</v>
       </c>
       <c r="I21" t="n">
-        <v>234.4</v>
+        <v>235.01</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -7674,10 +7674,10 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>33187.67</v>
+        <v>33500.28</v>
       </c>
       <c r="I22" t="n">
-        <v>231.88</v>
+        <v>235</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         <v>10000</v>
       </c>
       <c r="H23" t="n">
-        <v>30885.42</v>
+        <v>31176.35</v>
       </c>
       <c r="I23" t="n">
-        <v>208.85</v>
+        <v>211.76</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -7754,10 +7754,10 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>30235.43</v>
+        <v>30341.52</v>
       </c>
       <c r="I24" t="n">
-        <v>202.35</v>
+        <v>203.42</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -7794,10 +7794,10 @@
         <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>27518.48</v>
+        <v>27777.69</v>
       </c>
       <c r="I25" t="n">
-        <v>175.18</v>
+        <v>177.78</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -7834,10 +7834,10 @@
         <v>10000</v>
       </c>
       <c r="H26" t="n">
-        <v>26253.87</v>
+        <v>26501.17</v>
       </c>
       <c r="I26" t="n">
-        <v>162.54</v>
+        <v>165.01</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -7874,10 +7874,10 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>23244.8</v>
+        <v>23286.75</v>
       </c>
       <c r="I27" t="n">
-        <v>132.45</v>
+        <v>132.87</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -7914,10 +7914,10 @@
         <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>21680.06</v>
+        <v>22139.9</v>
       </c>
       <c r="I28" t="n">
-        <v>116.8</v>
+        <v>121.4</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ICP/BTC</t>
+          <t>ADA/HBAR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>824</v>
+        <v>642</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -7954,14 +7954,14 @@
         <v>10000</v>
       </c>
       <c r="H29" t="n">
-        <v>21472.89</v>
+        <v>21563.08</v>
       </c>
       <c r="I29" t="n">
-        <v>114.73</v>
+        <v>115.63</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>7534.348009 ICP + cash 0.00</t>
+          <t>93380.613466 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NEAR/HBAR</t>
+          <t>ICP/BTC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>957</v>
+        <v>824</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -7994,14 +7994,14 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>21455.27</v>
+        <v>21548.24</v>
       </c>
       <c r="I30" t="n">
-        <v>114.55</v>
+        <v>115.48</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>269952.347078 HBAR + cash 0.00</t>
+          <t>7534.348009 ICP + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -8013,7 +8013,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ADA/HBAR</t>
+          <t>NEAR/HBAR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>642</v>
+        <v>957</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -8034,14 +8034,14 @@
         <v>10000</v>
       </c>
       <c r="H31" t="n">
-        <v>21115.22</v>
+        <v>21545.98</v>
       </c>
       <c r="I31" t="n">
-        <v>111.15</v>
+        <v>115.46</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>93380.613466 ADA + cash 0.00</t>
+          <t>269952.347078 HBAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -8074,10 +8074,10 @@
         <v>10000</v>
       </c>
       <c r="H32" t="n">
-        <v>20627.7</v>
+        <v>21065.22</v>
       </c>
       <c r="I32" t="n">
-        <v>106.28</v>
+        <v>110.65</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -8114,10 +8114,10 @@
         <v>10000</v>
       </c>
       <c r="H33" t="n">
-        <v>19006.83</v>
+        <v>19041.13</v>
       </c>
       <c r="I33" t="n">
-        <v>90.06999999999999</v>
+        <v>90.41</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -8154,10 +8154,10 @@
         <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>18340.92</v>
+        <v>18374.02</v>
       </c>
       <c r="I34" t="n">
-        <v>83.41</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -8194,10 +8194,10 @@
         <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>18005.15</v>
+        <v>18037.64</v>
       </c>
       <c r="I35" t="n">
-        <v>80.05</v>
+        <v>80.38</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -8234,10 +8234,10 @@
         <v>10000</v>
       </c>
       <c r="H36" t="n">
-        <v>16055.25</v>
+        <v>16084.23</v>
       </c>
       <c r="I36" t="n">
-        <v>60.55</v>
+        <v>60.84</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -8274,10 +8274,10 @@
         <v>10000</v>
       </c>
       <c r="H37" t="n">
-        <v>15645.72</v>
+        <v>15700.62</v>
       </c>
       <c r="I37" t="n">
-        <v>56.46</v>
+        <v>57.01</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -8314,10 +8314,10 @@
         <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>15277.98</v>
+        <v>15331.59</v>
       </c>
       <c r="I38" t="n">
-        <v>52.78</v>
+        <v>53.32</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -8354,10 +8354,10 @@
         <v>10000</v>
       </c>
       <c r="H39" t="n">
-        <v>14836.21</v>
+        <v>14888.26</v>
       </c>
       <c r="I39" t="n">
-        <v>48.36</v>
+        <v>48.88</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -8394,10 +8394,10 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>14344.32</v>
+        <v>14648.56</v>
       </c>
       <c r="I40" t="n">
-        <v>43.44</v>
+        <v>46.49</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -8434,10 +8434,10 @@
         <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>14064.37</v>
+        <v>14362.67</v>
       </c>
       <c r="I41" t="n">
-        <v>40.64</v>
+        <v>43.63</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ICP/BNB</t>
+          <t>ADA/LINK</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -8465,7 +8465,7 @@
         <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>868</v>
+        <v>711</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -8474,14 +8474,14 @@
         <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>13170.76</v>
+        <v>13447.54</v>
       </c>
       <c r="I42" t="n">
-        <v>31.71</v>
+        <v>34.48</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>4621.320698 ICP + cash 0.00</t>
+          <t>58235.624433 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ADA/LINK</t>
+          <t>ICP/BNB</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -8505,7 +8505,7 @@
         <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>711</v>
+        <v>868</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -8514,14 +8514,14 @@
         <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>13168.24</v>
+        <v>13216.98</v>
       </c>
       <c r="I43" t="n">
-        <v>31.68</v>
+        <v>32.17</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>58235.624433 ADA + cash 0.00</t>
+          <t>4621.320698 ICP + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ICP/HBAR</t>
+          <t>ADA/ETH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>1052</v>
+        <v>847</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -8554,14 +8554,14 @@
         <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>12986.24</v>
+        <v>13114.26</v>
       </c>
       <c r="I44" t="n">
-        <v>29.86</v>
+        <v>31.14</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>4556.576852 ICP + cash 0.00</t>
+          <t>56792.328455 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ADA/ETH</t>
+          <t>ICP/HBAR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8582,10 +8582,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>847</v>
+        <v>1052</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -8594,14 +8594,14 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>12841.88</v>
+        <v>13031.81</v>
       </c>
       <c r="I45" t="n">
-        <v>28.42</v>
+        <v>30.32</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>56792.328455 ADA + cash 0.00</t>
+          <t>4556.576852 ICP + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -8634,10 +8634,10 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>11141.27</v>
+        <v>11180.36</v>
       </c>
       <c r="I46" t="n">
-        <v>11.41</v>
+        <v>11.8</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -8674,10 +8674,10 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>4434.2</v>
+        <v>4480.12</v>
       </c>
       <c r="I47" t="n">
-        <v>-55.66</v>
+        <v>-55.2</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -8714,10 +8714,10 @@
         <v>10000</v>
       </c>
       <c r="H48" t="n">
-        <v>3695.18</v>
+        <v>3733.45</v>
       </c>
       <c r="I48" t="n">
-        <v>-63.05</v>
+        <v>-62.67</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -8754,10 +8754,10 @@
         <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>3670.7</v>
+        <v>3720.76</v>
       </c>
       <c r="I49" t="n">
-        <v>-63.29</v>
+        <v>-62.79</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -8794,10 +8794,10 @@
         <v>10000</v>
       </c>
       <c r="H50" t="n">
-        <v>3209.09</v>
+        <v>3242.33</v>
       </c>
       <c r="I50" t="n">
-        <v>-67.91</v>
+        <v>-67.58</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -8834,10 +8834,10 @@
         <v>10000</v>
       </c>
       <c r="H51" t="n">
-        <v>3173.27</v>
+        <v>3216.55</v>
       </c>
       <c r="I51" t="n">
-        <v>-68.27</v>
+        <v>-67.83</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -8874,10 +8874,10 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>3163.41</v>
+        <v>3196.17</v>
       </c>
       <c r="I52" t="n">
-        <v>-68.37</v>
+        <v>-68.04000000000001</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -8914,10 +8914,10 @@
         <v>10000</v>
       </c>
       <c r="H53" t="n">
-        <v>3121.57</v>
+        <v>3153.89</v>
       </c>
       <c r="I53" t="n">
-        <v>-68.78</v>
+        <v>-68.45999999999999</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DOT/TRX</t>
+          <t>AAVE/ATOM</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -8942,10 +8942,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>1003</v>
+        <v>933</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -8954,14 +8954,14 @@
         <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>3050.4</v>
+        <v>3091.77</v>
       </c>
       <c r="I54" t="n">
-        <v>-69.5</v>
+        <v>-69.08</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2700.187544 DOT + cash 0.00</t>
+          <t>1785.393146 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AAVE/ATOM</t>
+          <t>DOT/TRX</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -8982,10 +8982,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>933</v>
+        <v>1003</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -8994,14 +8994,14 @@
         <v>10000</v>
       </c>
       <c r="H55" t="n">
-        <v>3050.17</v>
+        <v>3081.99</v>
       </c>
       <c r="I55" t="n">
-        <v>-69.5</v>
+        <v>-69.18000000000001</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>1785.393146 ATOM + cash 0.00</t>
+          <t>2700.187544 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -9034,10 +9034,10 @@
         <v>10000</v>
       </c>
       <c r="H56" t="n">
-        <v>2940.64</v>
+        <v>2980.75</v>
       </c>
       <c r="I56" t="n">
-        <v>-70.59</v>
+        <v>-70.19</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -9074,10 +9074,10 @@
         <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>2911.9</v>
+        <v>2942.05</v>
       </c>
       <c r="I57" t="n">
-        <v>-70.88</v>
+        <v>-70.58</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -9114,10 +9114,10 @@
         <v>10000</v>
       </c>
       <c r="H58" t="n">
-        <v>2893.75</v>
+        <v>2923.72</v>
       </c>
       <c r="I58" t="n">
-        <v>-71.06</v>
+        <v>-70.76000000000001</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -9154,10 +9154,10 @@
         <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>2749.93</v>
+        <v>2778.41</v>
       </c>
       <c r="I59" t="n">
-        <v>-72.5</v>
+        <v>-72.22</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -9194,10 +9194,10 @@
         <v>10000</v>
       </c>
       <c r="H60" t="n">
-        <v>2749.93</v>
+        <v>2778.41</v>
       </c>
       <c r="I60" t="n">
-        <v>-72.5</v>
+        <v>-72.22</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -9234,10 +9234,10 @@
         <v>10000</v>
       </c>
       <c r="H61" t="n">
-        <v>2655.42</v>
+        <v>2691.63</v>
       </c>
       <c r="I61" t="n">
-        <v>-73.45</v>
+        <v>-73.08</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -9274,10 +9274,10 @@
         <v>10000</v>
       </c>
       <c r="H62" t="n">
-        <v>2608.93</v>
+        <v>2644.51</v>
       </c>
       <c r="I62" t="n">
-        <v>-73.91</v>
+        <v>-73.55</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -9314,10 +9314,10 @@
         <v>10000</v>
       </c>
       <c r="H63" t="n">
-        <v>2533.1</v>
+        <v>2567.64</v>
       </c>
       <c r="I63" t="n">
-        <v>-74.67</v>
+        <v>-74.31999999999999</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -9354,10 +9354,10 @@
         <v>10000</v>
       </c>
       <c r="H64" t="n">
-        <v>2504.91</v>
+        <v>2539.08</v>
       </c>
       <c r="I64" t="n">
-        <v>-74.95</v>
+        <v>-74.61</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -9394,10 +9394,10 @@
         <v>10000</v>
       </c>
       <c r="H65" t="n">
-        <v>2471.05</v>
+        <v>2504.75</v>
       </c>
       <c r="I65" t="n">
-        <v>-75.29000000000001</v>
+        <v>-74.95</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -9434,10 +9434,10 @@
         <v>10000</v>
       </c>
       <c r="H66" t="n">
-        <v>2464.99</v>
+        <v>2498.61</v>
       </c>
       <c r="I66" t="n">
-        <v>-75.34999999999999</v>
+        <v>-75.01000000000001</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -9474,10 +9474,10 @@
         <v>10000</v>
       </c>
       <c r="H67" t="n">
-        <v>2348.06</v>
+        <v>2380.08</v>
       </c>
       <c r="I67" t="n">
-        <v>-76.52</v>
+        <v>-76.2</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -9514,10 +9514,10 @@
         <v>10000</v>
       </c>
       <c r="H68" t="n">
-        <v>898.4400000000001</v>
+        <v>909.96</v>
       </c>
       <c r="I68" t="n">
-        <v>-91.02</v>
+        <v>-90.90000000000001</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -9554,10 +9554,10 @@
         <v>10000</v>
       </c>
       <c r="H69" t="n">
-        <v>893.53</v>
+        <v>904.98</v>
       </c>
       <c r="I69" t="n">
-        <v>-91.06</v>
+        <v>-90.95</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -9594,10 +9594,10 @@
         <v>10000</v>
       </c>
       <c r="H70" t="n">
-        <v>689.73</v>
+        <v>698.58</v>
       </c>
       <c r="I70" t="n">
-        <v>-93.09999999999999</v>
+        <v>-93.01000000000001</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -9634,10 +9634,10 @@
         <v>10000</v>
       </c>
       <c r="H71" t="n">
-        <v>687.47</v>
+        <v>696.29</v>
       </c>
       <c r="I71" t="n">
-        <v>-93.13</v>
+        <v>-93.04000000000001</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -9674,10 +9674,10 @@
         <v>10000</v>
       </c>
       <c r="H72" t="n">
-        <v>594.34</v>
+        <v>601.96</v>
       </c>
       <c r="I72" t="n">
-        <v>-94.06</v>
+        <v>-93.98</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -9714,10 +9714,10 @@
         <v>10000</v>
       </c>
       <c r="H73" t="n">
-        <v>592.35</v>
+        <v>599.9400000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>-94.08</v>
+        <v>-94</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -9754,10 +9754,10 @@
         <v>10000</v>
       </c>
       <c r="H74" t="n">
-        <v>589.14</v>
+        <v>596.6900000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>-94.11</v>
+        <v>-94.03</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -9794,10 +9794,10 @@
         <v>10000</v>
       </c>
       <c r="H75" t="n">
-        <v>582.4</v>
+        <v>589.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-94.18000000000001</v>
+        <v>-94.09999999999999</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -9834,10 +9834,10 @@
         <v>10000</v>
       </c>
       <c r="H76" t="n">
-        <v>574.21</v>
+        <v>581.5700000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-94.26000000000001</v>
+        <v>-94.18000000000001</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -9874,10 +9874,10 @@
         <v>10000</v>
       </c>
       <c r="H77" t="n">
-        <v>572.11</v>
+        <v>579.45</v>
       </c>
       <c r="I77" t="n">
-        <v>-94.28</v>
+        <v>-94.20999999999999</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -9914,10 +9914,10 @@
         <v>10000</v>
       </c>
       <c r="H78" t="n">
-        <v>569.35</v>
+        <v>576.65</v>
       </c>
       <c r="I78" t="n">
-        <v>-94.31</v>
+        <v>-94.23</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -9954,10 +9954,10 @@
         <v>10000</v>
       </c>
       <c r="H79" t="n">
-        <v>543.72</v>
+        <v>550.6900000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-94.56</v>
+        <v>-94.48999999999999</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -10060,10 +10060,10 @@
         <v>10000</v>
       </c>
       <c r="H2" t="n">
-        <v>106903.42</v>
+        <v>106469.33</v>
       </c>
       <c r="I2" t="n">
-        <v>969.03</v>
+        <v>964.6900000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -10100,10 +10100,10 @@
         <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>99833.19</v>
+        <v>101950.65</v>
       </c>
       <c r="I3" t="n">
-        <v>898.33</v>
+        <v>919.51</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -10140,10 +10140,10 @@
         <v>10000</v>
       </c>
       <c r="H4" t="n">
-        <v>98228.74000000001</v>
+        <v>101625.5</v>
       </c>
       <c r="I4" t="n">
-        <v>882.29</v>
+        <v>916.25</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -10180,10 +10180,10 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>91985.67999999999</v>
+        <v>92852.14999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>819.86</v>
+        <v>828.52</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -10220,10 +10220,10 @@
         <v>10000</v>
       </c>
       <c r="H6" t="n">
-        <v>63836.13</v>
+        <v>63951.34</v>
       </c>
       <c r="I6" t="n">
-        <v>538.36</v>
+        <v>539.51</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -10260,10 +10260,10 @@
         <v>10000</v>
       </c>
       <c r="H7" t="n">
-        <v>63018.08</v>
+        <v>63382.49</v>
       </c>
       <c r="I7" t="n">
-        <v>530.1799999999999</v>
+        <v>533.8200000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -10300,10 +10300,10 @@
         <v>10000</v>
       </c>
       <c r="H8" t="n">
-        <v>55747.32</v>
+        <v>55758.38</v>
       </c>
       <c r="I8" t="n">
-        <v>457.47</v>
+        <v>457.58</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -10340,10 +10340,10 @@
         <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>54514.11</v>
+        <v>54744.57</v>
       </c>
       <c r="I9" t="n">
-        <v>445.14</v>
+        <v>447.45</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -10380,10 +10380,10 @@
         <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>53200.19</v>
+        <v>53425.1</v>
       </c>
       <c r="I10" t="n">
-        <v>432</v>
+        <v>434.25</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LINK/TRX</t>
+          <t>AAVE/BTC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -10411,7 +10411,7 @@
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>786</v>
+        <v>533</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -10420,14 +10420,14 @@
         <v>10000</v>
       </c>
       <c r="H11" t="n">
-        <v>52024.18</v>
+        <v>52634.43</v>
       </c>
       <c r="I11" t="n">
-        <v>420.24</v>
+        <v>426.34</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4235.496742 LINK + cash 0.00</t>
+          <t>366.912175 AAVE + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BTC/NEAR</t>
+          <t>LINK/TRX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -10448,10 +10448,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>966</v>
+        <v>786</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -10460,14 +10460,14 @@
         <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>51740.47</v>
+        <v>52514.23</v>
       </c>
       <c r="I12" t="n">
-        <v>417.4</v>
+        <v>425.14</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13787.531741 NEAR + cash 0.00</t>
+          <t>4235.496742 LINK + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AAVE/BTC</t>
+          <t>BTC/NEAR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>533</v>
+        <v>966</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -10500,14 +10500,14 @@
         <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>50875.16</v>
+        <v>52039.66</v>
       </c>
       <c r="I13" t="n">
-        <v>408.75</v>
+        <v>420.4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>366.912175 AAVE + cash 0.00</t>
+          <t>13787.531741 NEAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -10540,10 +10540,10 @@
         <v>10000</v>
       </c>
       <c r="H14" t="n">
-        <v>44337.34</v>
+        <v>44346.13</v>
       </c>
       <c r="I14" t="n">
-        <v>343.37</v>
+        <v>343.46</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -10580,10 +10580,10 @@
         <v>10000</v>
       </c>
       <c r="H15" t="n">
-        <v>43784.17</v>
+        <v>43863.19</v>
       </c>
       <c r="I15" t="n">
-        <v>337.84</v>
+        <v>338.63</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -10620,10 +10620,10 @@
         <v>10000</v>
       </c>
       <c r="H16" t="n">
-        <v>42490.26</v>
+        <v>42735.96</v>
       </c>
       <c r="I16" t="n">
-        <v>324.9</v>
+        <v>327.36</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -10660,10 +10660,10 @@
         <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>40898.12</v>
+        <v>41283.36</v>
       </c>
       <c r="I17" t="n">
-        <v>308.98</v>
+        <v>312.83</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NEAR/HBAR</t>
+          <t>ADA/HBAR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>985</v>
+        <v>641</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -10700,14 +10700,14 @@
         <v>10000</v>
       </c>
       <c r="H18" t="n">
-        <v>39448.67</v>
+        <v>39930.95</v>
       </c>
       <c r="I18" t="n">
-        <v>294.49</v>
+        <v>299.31</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>10512.076760 NEAR + cash 0.00</t>
+          <t>172924.125106 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NEAR/BNB</t>
+          <t>NEAR/HBAR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -10731,7 +10731,7 @@
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>1011</v>
+        <v>985</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -10740,14 +10740,14 @@
         <v>10000</v>
       </c>
       <c r="H19" t="n">
-        <v>39361.55</v>
+        <v>39676.78</v>
       </c>
       <c r="I19" t="n">
-        <v>293.62</v>
+        <v>296.77</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10488.860079 NEAR + cash 0.00</t>
+          <t>10512.076760 NEAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ADA/HBAR</t>
+          <t>NEAR/BNB</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -10768,10 +10768,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>641</v>
+        <v>1011</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -10780,14 +10780,14 @@
         <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>39101.6</v>
+        <v>39589.15</v>
       </c>
       <c r="I20" t="n">
-        <v>291.02</v>
+        <v>295.89</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>172924.125106 ADA + cash 0.00</t>
+          <t>10488.860079 NEAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -10820,10 +10820,10 @@
         <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>35132.56</v>
+        <v>36347.45</v>
       </c>
       <c r="I21" t="n">
-        <v>251.33</v>
+        <v>263.47</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -10860,10 +10860,10 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>33187.67</v>
+        <v>33500.28</v>
       </c>
       <c r="I22" t="n">
-        <v>231.88</v>
+        <v>235</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -10900,10 +10900,10 @@
         <v>10000</v>
       </c>
       <c r="H23" t="n">
-        <v>30235.43</v>
+        <v>30341.52</v>
       </c>
       <c r="I23" t="n">
-        <v>202.35</v>
+        <v>203.42</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -10940,10 +10940,10 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>29777.96</v>
+        <v>29903.85</v>
       </c>
       <c r="I24" t="n">
-        <v>197.78</v>
+        <v>199.04</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -10980,10 +10980,10 @@
         <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>26253.87</v>
+        <v>26501.17</v>
       </c>
       <c r="I25" t="n">
-        <v>162.54</v>
+        <v>165.01</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -11020,10 +11020,10 @@
         <v>10000</v>
       </c>
       <c r="H26" t="n">
-        <v>23244.8</v>
+        <v>23286.75</v>
       </c>
       <c r="I26" t="n">
-        <v>132.45</v>
+        <v>132.87</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -11060,10 +11060,10 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>22911.39</v>
+        <v>23008.25</v>
       </c>
       <c r="I27" t="n">
-        <v>129.11</v>
+        <v>130.08</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -11100,10 +11100,10 @@
         <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>21680.06</v>
+        <v>22139.9</v>
       </c>
       <c r="I28" t="n">
-        <v>116.8</v>
+        <v>121.4</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -11140,10 +11140,10 @@
         <v>10000</v>
       </c>
       <c r="H29" t="n">
-        <v>21472.89</v>
+        <v>21548.24</v>
       </c>
       <c r="I29" t="n">
-        <v>114.73</v>
+        <v>115.48</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -11180,10 +11180,10 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>19755.86</v>
+        <v>19941.95</v>
       </c>
       <c r="I30" t="n">
-        <v>97.56</v>
+        <v>99.42</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -11220,10 +11220,10 @@
         <v>10000</v>
       </c>
       <c r="H31" t="n">
-        <v>19295.04</v>
+        <v>19362.74</v>
       </c>
       <c r="I31" t="n">
-        <v>92.95</v>
+        <v>93.63</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -11260,10 +11260,10 @@
         <v>10000</v>
       </c>
       <c r="H32" t="n">
-        <v>19006.83</v>
+        <v>19041.13</v>
       </c>
       <c r="I32" t="n">
-        <v>90.06999999999999</v>
+        <v>90.41</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         <v>10000</v>
       </c>
       <c r="H33" t="n">
-        <v>18340.92</v>
+        <v>18374.02</v>
       </c>
       <c r="I33" t="n">
-        <v>83.41</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -11340,10 +11340,10 @@
         <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>18253.81</v>
+        <v>18286.76</v>
       </c>
       <c r="I34" t="n">
-        <v>82.54000000000001</v>
+        <v>82.87</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -11380,10 +11380,10 @@
         <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>17818.56</v>
+        <v>17881.08</v>
       </c>
       <c r="I35" t="n">
-        <v>78.19</v>
+        <v>78.81</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -11420,10 +11420,10 @@
         <v>10000</v>
       </c>
       <c r="H36" t="n">
-        <v>16055.25</v>
+        <v>16084.23</v>
       </c>
       <c r="I36" t="n">
-        <v>60.55</v>
+        <v>60.84</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -11460,10 +11460,10 @@
         <v>10000</v>
       </c>
       <c r="H37" t="n">
-        <v>15645.72</v>
+        <v>15700.62</v>
       </c>
       <c r="I37" t="n">
-        <v>56.46</v>
+        <v>57.01</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -11500,10 +11500,10 @@
         <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>15313.06</v>
+        <v>15637.85</v>
       </c>
       <c r="I38" t="n">
-        <v>53.13</v>
+        <v>56.38</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -11540,10 +11540,10 @@
         <v>10000</v>
       </c>
       <c r="H39" t="n">
-        <v>14064.37</v>
+        <v>14362.67</v>
       </c>
       <c r="I39" t="n">
-        <v>40.64</v>
+        <v>43.63</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -11580,10 +11580,10 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>13664.2</v>
+        <v>13954.01</v>
       </c>
       <c r="I40" t="n">
-        <v>36.64</v>
+        <v>39.54</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ICP/BNB</t>
+          <t>ADA/ETH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -11611,7 +11611,7 @@
         <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>868</v>
+        <v>851</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -11620,14 +11620,14 @@
         <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>13170.76</v>
+        <v>13326.2</v>
       </c>
       <c r="I41" t="n">
-        <v>31.71</v>
+        <v>33.26</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4621.320698 ICP + cash 0.00</t>
+          <t>57710.177652 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ADA/ETH</t>
+          <t>ICP/BNB</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -11651,7 +11651,7 @@
         <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>851</v>
+        <v>868</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -11660,14 +11660,14 @@
         <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>13049.43</v>
+        <v>13216.98</v>
       </c>
       <c r="I42" t="n">
-        <v>30.49</v>
+        <v>32.17</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>57710.177652 ADA + cash 0.00</t>
+          <t>4621.320698 ICP + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -11700,10 +11700,10 @@
         <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>12986.24</v>
+        <v>13031.81</v>
       </c>
       <c r="I43" t="n">
-        <v>29.86</v>
+        <v>30.32</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -11740,10 +11740,10 @@
         <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>12564.22</v>
+        <v>12830.71</v>
       </c>
       <c r="I44" t="n">
-        <v>25.64</v>
+        <v>28.31</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -11780,10 +11780,10 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>11280.71</v>
+        <v>11320.29</v>
       </c>
       <c r="I45" t="n">
-        <v>12.81</v>
+        <v>13.2</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -11820,10 +11820,10 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>11141.27</v>
+        <v>11180.36</v>
       </c>
       <c r="I46" t="n">
-        <v>11.41</v>
+        <v>11.8</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -11860,10 +11860,10 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>6109.21</v>
+        <v>6192.53</v>
       </c>
       <c r="I47" t="n">
-        <v>-38.91</v>
+        <v>-38.07</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -11900,10 +11900,10 @@
         <v>10000</v>
       </c>
       <c r="H48" t="n">
-        <v>3786.88</v>
+        <v>3826.1</v>
       </c>
       <c r="I48" t="n">
-        <v>-62.13</v>
+        <v>-61.74</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -11940,10 +11940,10 @@
         <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>3336.22</v>
+        <v>3381.72</v>
       </c>
       <c r="I49" t="n">
-        <v>-66.64</v>
+        <v>-66.18000000000001</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -11980,10 +11980,10 @@
         <v>10000</v>
       </c>
       <c r="H50" t="n">
-        <v>3209.09</v>
+        <v>3242.33</v>
       </c>
       <c r="I50" t="n">
-        <v>-67.91</v>
+        <v>-67.58</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -12020,10 +12020,10 @@
         <v>10000</v>
       </c>
       <c r="H51" t="n">
-        <v>3163.41</v>
+        <v>3196.17</v>
       </c>
       <c r="I51" t="n">
-        <v>-68.37</v>
+        <v>-68.04000000000001</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -12060,10 +12060,10 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>3121.57</v>
+        <v>3153.89</v>
       </c>
       <c r="I52" t="n">
-        <v>-68.78</v>
+        <v>-68.45999999999999</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -12100,10 +12100,10 @@
         <v>10000</v>
       </c>
       <c r="H53" t="n">
-        <v>3102.76</v>
+        <v>3134.9</v>
       </c>
       <c r="I53" t="n">
-        <v>-68.97</v>
+        <v>-68.65000000000001</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DOT/TRX</t>
+          <t>AAVE/ATOM</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -12128,10 +12128,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>1003</v>
+        <v>933</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -12140,14 +12140,14 @@
         <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>3050.4</v>
+        <v>3091.77</v>
       </c>
       <c r="I54" t="n">
-        <v>-69.5</v>
+        <v>-69.08</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2700.187544 DOT + cash 0.00</t>
+          <t>1785.393146 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -12159,7 +12159,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AAVE/ATOM</t>
+          <t>DOT/TRX</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -12168,10 +12168,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>933</v>
+        <v>1003</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -12180,14 +12180,14 @@
         <v>10000</v>
       </c>
       <c r="H55" t="n">
-        <v>3050.17</v>
+        <v>3081.99</v>
       </c>
       <c r="I55" t="n">
-        <v>-69.5</v>
+        <v>-69.18000000000001</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>1785.393146 ATOM + cash 0.00</t>
+          <t>2700.187544 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -12220,10 +12220,10 @@
         <v>10000</v>
       </c>
       <c r="H56" t="n">
-        <v>2964.07</v>
+        <v>2994.77</v>
       </c>
       <c r="I56" t="n">
-        <v>-70.36</v>
+        <v>-70.05</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -12260,10 +12260,10 @@
         <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>2893.75</v>
+        <v>2923.72</v>
       </c>
       <c r="I57" t="n">
-        <v>-71.06</v>
+        <v>-70.76000000000001</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -12300,10 +12300,10 @@
         <v>10000</v>
       </c>
       <c r="H58" t="n">
-        <v>2762.39</v>
+        <v>2800.07</v>
       </c>
       <c r="I58" t="n">
-        <v>-72.38</v>
+        <v>-72</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -12340,10 +12340,10 @@
         <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>2749.93</v>
+        <v>2778.41</v>
       </c>
       <c r="I59" t="n">
-        <v>-72.5</v>
+        <v>-72.22</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -12380,10 +12380,10 @@
         <v>10000</v>
       </c>
       <c r="H60" t="n">
-        <v>2749.93</v>
+        <v>2778.41</v>
       </c>
       <c r="I60" t="n">
-        <v>-72.5</v>
+        <v>-72.22</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -12420,10 +12420,10 @@
         <v>10000</v>
       </c>
       <c r="H61" t="n">
-        <v>2655.42</v>
+        <v>2691.63</v>
       </c>
       <c r="I61" t="n">
-        <v>-73.45</v>
+        <v>-73.08</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -12460,10 +12460,10 @@
         <v>10000</v>
       </c>
       <c r="H62" t="n">
-        <v>2608.93</v>
+        <v>2644.51</v>
       </c>
       <c r="I62" t="n">
-        <v>-73.91</v>
+        <v>-73.55</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -12500,10 +12500,10 @@
         <v>10000</v>
       </c>
       <c r="H63" t="n">
-        <v>2533.1</v>
+        <v>2567.64</v>
       </c>
       <c r="I63" t="n">
-        <v>-74.67</v>
+        <v>-74.31999999999999</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -12540,10 +12540,10 @@
         <v>10000</v>
       </c>
       <c r="H64" t="n">
-        <v>2520.14</v>
+        <v>2554.51</v>
       </c>
       <c r="I64" t="n">
-        <v>-74.8</v>
+        <v>-74.45</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -12580,10 +12580,10 @@
         <v>10000</v>
       </c>
       <c r="H65" t="n">
-        <v>2504.91</v>
+        <v>2539.08</v>
       </c>
       <c r="I65" t="n">
-        <v>-74.95</v>
+        <v>-74.61</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -12620,10 +12620,10 @@
         <v>10000</v>
       </c>
       <c r="H66" t="n">
-        <v>2504.26</v>
+        <v>2538.42</v>
       </c>
       <c r="I66" t="n">
-        <v>-74.95999999999999</v>
+        <v>-74.62</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -12660,10 +12660,10 @@
         <v>10000</v>
       </c>
       <c r="H67" t="n">
-        <v>2464.99</v>
+        <v>2498.61</v>
       </c>
       <c r="I67" t="n">
-        <v>-75.34999999999999</v>
+        <v>-75.01000000000001</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -12700,10 +12700,10 @@
         <v>10000</v>
       </c>
       <c r="H68" t="n">
-        <v>2348.06</v>
+        <v>2380.08</v>
       </c>
       <c r="I68" t="n">
-        <v>-76.52</v>
+        <v>-76.2</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -12740,10 +12740,10 @@
         <v>10000</v>
       </c>
       <c r="H69" t="n">
-        <v>1782.16</v>
+        <v>1805.02</v>
       </c>
       <c r="I69" t="n">
-        <v>-82.18000000000001</v>
+        <v>-81.95</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -12780,10 +12780,10 @@
         <v>10000</v>
       </c>
       <c r="H70" t="n">
-        <v>893.53</v>
+        <v>904.98</v>
       </c>
       <c r="I70" t="n">
-        <v>-91.06</v>
+        <v>-90.95</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -12820,10 +12820,10 @@
         <v>10000</v>
       </c>
       <c r="H71" t="n">
-        <v>689.73</v>
+        <v>698.58</v>
       </c>
       <c r="I71" t="n">
-        <v>-93.09999999999999</v>
+        <v>-93.01000000000001</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -12860,10 +12860,10 @@
         <v>10000</v>
       </c>
       <c r="H72" t="n">
-        <v>594.34</v>
+        <v>601.96</v>
       </c>
       <c r="I72" t="n">
-        <v>-94.06</v>
+        <v>-93.98</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -12900,10 +12900,10 @@
         <v>10000</v>
       </c>
       <c r="H73" t="n">
-        <v>592.35</v>
+        <v>599.9400000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>-94.08</v>
+        <v>-94</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -12940,10 +12940,10 @@
         <v>10000</v>
       </c>
       <c r="H74" t="n">
-        <v>589.14</v>
+        <v>596.6900000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>-94.11</v>
+        <v>-94.03</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -12980,10 +12980,10 @@
         <v>10000</v>
       </c>
       <c r="H75" t="n">
-        <v>582.4</v>
+        <v>589.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-94.18000000000001</v>
+        <v>-94.09999999999999</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -13020,10 +13020,10 @@
         <v>10000</v>
       </c>
       <c r="H76" t="n">
-        <v>574.21</v>
+        <v>581.5700000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-94.26000000000001</v>
+        <v>-94.18000000000001</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -13060,10 +13060,10 @@
         <v>10000</v>
       </c>
       <c r="H77" t="n">
-        <v>572.11</v>
+        <v>579.45</v>
       </c>
       <c r="I77" t="n">
-        <v>-94.28</v>
+        <v>-94.20999999999999</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -13100,10 +13100,10 @@
         <v>10000</v>
       </c>
       <c r="H78" t="n">
-        <v>569.35</v>
+        <v>576.65</v>
       </c>
       <c r="I78" t="n">
-        <v>-94.31</v>
+        <v>-94.23</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -13140,10 +13140,10 @@
         <v>10000</v>
       </c>
       <c r="H79" t="n">
-        <v>543.72</v>
+        <v>550.6900000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-94.56</v>
+        <v>-94.48999999999999</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -13246,10 +13246,10 @@
         <v>10000</v>
       </c>
       <c r="H2" t="n">
-        <v>14865.16</v>
+        <v>14891.99</v>
       </c>
       <c r="I2" t="n">
-        <v>48.65</v>
+        <v>48.92</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -13286,10 +13286,10 @@
         <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>14526.19</v>
+        <v>14552.4</v>
       </c>
       <c r="I3" t="n">
-        <v>45.26</v>
+        <v>45.52</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -13326,10 +13326,10 @@
         <v>10000</v>
       </c>
       <c r="H4" t="n">
-        <v>12916.28</v>
+        <v>12915.02</v>
       </c>
       <c r="I4" t="n">
-        <v>29.16</v>
+        <v>29.15</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -13345,19 +13345,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NEAR/BNB</t>
+          <t>ZRO/NEAR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -13366,14 +13366,14 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>11329.94</v>
+        <v>11302.93</v>
       </c>
       <c r="I5" t="n">
-        <v>13.3</v>
+        <v>13.03</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14.840841 BNB + cash 0.00</t>
+          <t>9419.108519 ZRO + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -13385,19 +13385,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ZRO/NEAR</t>
+          <t>NEAR/BNB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -13406,14 +13406,14 @@
         <v>10000</v>
       </c>
       <c r="H6" t="n">
-        <v>11302.93</v>
+        <v>11283.94</v>
       </c>
       <c r="I6" t="n">
-        <v>13.03</v>
+        <v>12.84</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9419.108519 ZRO + cash 0.00</t>
+          <t>14.840841 BNB + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -13526,10 +13526,10 @@
         <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>10493.57</v>
+        <v>10530.39</v>
       </c>
       <c r="I9" t="n">
-        <v>4.94</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -13566,10 +13566,10 @@
         <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>10235.52</v>
+        <v>10271.44</v>
       </c>
       <c r="I10" t="n">
-        <v>2.36</v>
+        <v>2.71</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -13646,10 +13646,10 @@
         <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>9719.76</v>
+        <v>9721.690000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.8</v>
+        <v>-2.78</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -13686,10 +13686,10 @@
         <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>9441.870000000001</v>
+        <v>9475</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.58</v>
+        <v>-5.25</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -13726,10 +13726,10 @@
         <v>10000</v>
       </c>
       <c r="H14" t="n">
-        <v>9000.120000000001</v>
+        <v>8963.57</v>
       </c>
       <c r="I14" t="n">
-        <v>-10</v>
+        <v>-10.36</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -13806,10 +13806,10 @@
         <v>10000</v>
       </c>
       <c r="H16" t="n">
-        <v>8265.65</v>
+        <v>8300.59</v>
       </c>
       <c r="I16" t="n">
-        <v>-17.34</v>
+        <v>-16.99</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -13846,10 +13846,10 @@
         <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>8196.91</v>
+        <v>8274.129999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-18.03</v>
+        <v>-17.26</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ICP/BTC</t>
+          <t>AAVE/ATOM</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -13874,10 +13874,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>288</v>
+        <v>104</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -13886,14 +13886,14 @@
         <v>10000</v>
       </c>
       <c r="H18" t="n">
-        <v>8183.74</v>
+        <v>8238.059999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-18.16</v>
+        <v>-17.62</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2871.486789 ICP + cash 0.00</t>
+          <t>4757.212175 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -13905,7 +13905,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AAVE/ATOM</t>
+          <t>ICP/BTC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -13914,10 +13914,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>104</v>
+        <v>288</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -13926,14 +13926,14 @@
         <v>10000</v>
       </c>
       <c r="H19" t="n">
-        <v>8127.22</v>
+        <v>8212.450000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-18.73</v>
+        <v>-17.88</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4757.212175 ATOM + cash 0.00</t>
+          <t>2871.486789 ICP + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -13966,10 +13966,10 @@
         <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>8074.47</v>
+        <v>8076.07</v>
       </c>
       <c r="I20" t="n">
-        <v>-19.26</v>
+        <v>-19.24</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BTC/TRX</t>
+          <t>AAVE/NEAR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -13994,10 +13994,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>249</v>
+        <v>198</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -14006,14 +14006,14 @@
         <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>7748.49</v>
+        <v>7808.88</v>
       </c>
       <c r="I21" t="n">
-        <v>-22.52</v>
+        <v>-21.91</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.095556 BTC + cash 0.00</t>
+          <t>54.435343 AAVE + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AAVE/NEAR</t>
+          <t>BTC/TRX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -14034,10 +14034,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>198</v>
+        <v>249</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -14046,14 +14046,14 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>7547.87</v>
+        <v>7750.03</v>
       </c>
       <c r="I22" t="n">
-        <v>-24.52</v>
+        <v>-22.5</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>54.435343 AAVE + cash 0.00</t>
+          <t>0.095556 BTC + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -14086,10 +14086,10 @@
         <v>10000</v>
       </c>
       <c r="H23" t="n">
-        <v>7508.78</v>
+        <v>7535.13</v>
       </c>
       <c r="I23" t="n">
-        <v>-24.91</v>
+        <v>-24.65</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -14126,10 +14126,10 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>7124.9</v>
+        <v>7222.07</v>
       </c>
       <c r="I24" t="n">
-        <v>-28.75</v>
+        <v>-27.78</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -14166,10 +14166,10 @@
         <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>6996.76</v>
+        <v>7092.19</v>
       </c>
       <c r="I25" t="n">
-        <v>-30.03</v>
+        <v>-29.08</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -14206,10 +14206,10 @@
         <v>10000</v>
       </c>
       <c r="H26" t="n">
-        <v>6852.39</v>
+        <v>6864.76</v>
       </c>
       <c r="I26" t="n">
-        <v>-31.48</v>
+        <v>-31.35</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -14246,10 +14246,10 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>6672.1</v>
+        <v>6700.31</v>
       </c>
       <c r="I27" t="n">
-        <v>-33.28</v>
+        <v>-33</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -14286,10 +14286,10 @@
         <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>5983.86</v>
+        <v>6040.22</v>
       </c>
       <c r="I28" t="n">
-        <v>-40.16</v>
+        <v>-39.6</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ETH/BNB</t>
+          <t>LINK/AAVE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -14314,10 +14314,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>364</v>
+        <v>133</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -14326,14 +14326,14 @@
         <v>10000</v>
       </c>
       <c r="H29" t="n">
-        <v>5844.9</v>
+        <v>5995.21</v>
       </c>
       <c r="I29" t="n">
-        <v>-41.55</v>
+        <v>-40.05</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2.234872 ETH + cash 0.00</t>
+          <t>41.792327 AAVE + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -14345,7 +14345,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ETH/BTC</t>
+          <t>ATOM/NEAR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -14354,10 +14354,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>352</v>
+        <v>157</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -14366,14 +14366,14 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>5844.9</v>
+        <v>5861.4</v>
       </c>
       <c r="I30" t="n">
-        <v>-41.55</v>
+        <v>-41.39</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2.234872 ETH + cash 0.00</t>
+          <t>3384.768149 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -14385,7 +14385,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LINK/AAVE</t>
+          <t>ETH/BTC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -14394,10 +14394,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>133</v>
+        <v>352</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -14406,14 +14406,14 @@
         <v>10000</v>
       </c>
       <c r="H31" t="n">
-        <v>5794.82</v>
+        <v>5855.45</v>
       </c>
       <c r="I31" t="n">
-        <v>-42.05</v>
+        <v>-41.45</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>41.792327 AAVE + cash 0.00</t>
+          <t>2.234872 ETH + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -14425,7 +14425,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ATOM/NEAR</t>
+          <t>ETH/BNB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -14434,10 +14434,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>157</v>
+        <v>364</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -14446,14 +14446,14 @@
         <v>10000</v>
       </c>
       <c r="H32" t="n">
-        <v>5782.54</v>
+        <v>5855.45</v>
       </c>
       <c r="I32" t="n">
-        <v>-42.17</v>
+        <v>-41.45</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>3384.768149 ATOM + cash 0.00</t>
+          <t>2.234872 ETH + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -14486,10 +14486,10 @@
         <v>10000</v>
       </c>
       <c r="H33" t="n">
-        <v>5498.45</v>
+        <v>5573.45</v>
       </c>
       <c r="I33" t="n">
-        <v>-45.02</v>
+        <v>-44.27</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -14526,10 +14526,10 @@
         <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>5457.96</v>
+        <v>5509.37</v>
       </c>
       <c r="I34" t="n">
-        <v>-45.42</v>
+        <v>-44.91</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -14545,19 +14545,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ZRO/HBAR</t>
+          <t>ICP/AAVE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -14566,14 +14566,14 @@
         <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>5254.44</v>
+        <v>5430.36</v>
       </c>
       <c r="I35" t="n">
-        <v>-47.46</v>
+        <v>-45.7</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>66111.832284 HBAR + cash 0.00</t>
+          <t>37.854819 AAVE + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -14585,19 +14585,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ICP/AAVE</t>
+          <t>ZRO/HBAR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -14606,14 +14606,14 @@
         <v>10000</v>
       </c>
       <c r="H36" t="n">
-        <v>5248.86</v>
+        <v>5276.65</v>
       </c>
       <c r="I36" t="n">
-        <v>-47.51</v>
+        <v>-47.23</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>37.854819 AAVE + cash 0.00</t>
+          <t>66111.832284 HBAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -14646,10 +14646,10 @@
         <v>10000</v>
       </c>
       <c r="H37" t="n">
-        <v>5203.65</v>
+        <v>5252.66</v>
       </c>
       <c r="I37" t="n">
-        <v>-47.96</v>
+        <v>-47.47</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -14686,10 +14686,10 @@
         <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>5203.65</v>
+        <v>5252.66</v>
       </c>
       <c r="I38" t="n">
-        <v>-47.96</v>
+        <v>-47.47</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -14726,10 +14726,10 @@
         <v>10000</v>
       </c>
       <c r="H39" t="n">
-        <v>5203.65</v>
+        <v>5252.66</v>
       </c>
       <c r="I39" t="n">
-        <v>-47.96</v>
+        <v>-47.47</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -14766,10 +14766,10 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>5203.65</v>
+        <v>5252.66</v>
       </c>
       <c r="I40" t="n">
-        <v>-47.96</v>
+        <v>-47.47</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -14806,10 +14806,10 @@
         <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>4869.78</v>
+        <v>5038.18</v>
       </c>
       <c r="I41" t="n">
-        <v>-51.3</v>
+        <v>-49.62</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -14846,10 +14846,10 @@
         <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>4846.29</v>
+        <v>5013.88</v>
       </c>
       <c r="I42" t="n">
-        <v>-51.54</v>
+        <v>-49.86</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ATOM/HBAR</t>
+          <t>AAVE/BTC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -14874,10 +14874,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>41</v>
+        <v>363</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -14886,14 +14886,14 @@
         <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>4645.13</v>
+        <v>4755.3</v>
       </c>
       <c r="I43" t="n">
-        <v>-53.55</v>
+        <v>-52.45</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>58445.433893 HBAR + cash 0.00</t>
+          <t>33.148992 AAVE + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AAVE/BNB</t>
+          <t>AAVE/TRX</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -14917,7 +14917,7 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -14926,10 +14926,10 @@
         <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>4596.36</v>
+        <v>4755.3</v>
       </c>
       <c r="I44" t="n">
-        <v>-54.04</v>
+        <v>-52.45</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -14945,7 +14945,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AAVE/TRX</t>
+          <t>AAVE/BNB</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -14957,7 +14957,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -14966,10 +14966,10 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>4596.36</v>
+        <v>4755.3</v>
       </c>
       <c r="I45" t="n">
-        <v>-54.04</v>
+        <v>-52.45</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AAVE/BTC</t>
+          <t>ATOM/HBAR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -14994,10 +14994,10 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>363</v>
+        <v>41</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -15006,14 +15006,14 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>4596.36</v>
+        <v>4664.76</v>
       </c>
       <c r="I46" t="n">
-        <v>-54.04</v>
+        <v>-53.35</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>33.148992 AAVE + cash 0.00</t>
+          <t>58445.433893 HBAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15046,10 +15046,10 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>4332.15</v>
+        <v>4350.46</v>
       </c>
       <c r="I47" t="n">
-        <v>-56.68</v>
+        <v>-56.5</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -15086,10 +15086,10 @@
         <v>10000</v>
       </c>
       <c r="H48" t="n">
-        <v>4017.96</v>
+        <v>4072.76</v>
       </c>
       <c r="I48" t="n">
-        <v>-59.82</v>
+        <v>-59.27</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -15126,10 +15126,10 @@
         <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>3980.91</v>
+        <v>4035.21</v>
       </c>
       <c r="I49" t="n">
-        <v>-60.19</v>
+        <v>-59.65</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -15166,10 +15166,10 @@
         <v>10000</v>
       </c>
       <c r="H50" t="n">
-        <v>3962.4</v>
+        <v>4013.21</v>
       </c>
       <c r="I50" t="n">
-        <v>-60.38</v>
+        <v>-59.87</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -15206,10 +15206,10 @@
         <v>10000</v>
       </c>
       <c r="H51" t="n">
-        <v>3757.78</v>
+        <v>3809.03</v>
       </c>
       <c r="I51" t="n">
-        <v>-62.42</v>
+        <v>-61.91</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -15246,10 +15246,10 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>3757.78</v>
+        <v>3809.03</v>
       </c>
       <c r="I52" t="n">
-        <v>-62.42</v>
+        <v>-61.91</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -15286,10 +15286,10 @@
         <v>10000</v>
       </c>
       <c r="H53" t="n">
-        <v>3611.75</v>
+        <v>3627.02</v>
       </c>
       <c r="I53" t="n">
-        <v>-63.88</v>
+        <v>-63.73</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ETH/HBAR</t>
+          <t>DOT/ATOM</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -15314,10 +15314,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>278</v>
+        <v>222</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -15326,14 +15326,14 @@
         <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>3554.44</v>
+        <v>3578.93</v>
       </c>
       <c r="I54" t="n">
-        <v>-64.45999999999999</v>
+        <v>-64.20999999999999</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>44722.308707 HBAR + cash 0.00</t>
+          <t>3135.560550 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DOT/ATOM</t>
+          <t>ETH/HBAR</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -15354,10 +15354,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>222</v>
+        <v>278</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -15366,14 +15366,14 @@
         <v>10000</v>
       </c>
       <c r="H55" t="n">
-        <v>3542.24</v>
+        <v>3569.47</v>
       </c>
       <c r="I55" t="n">
-        <v>-64.58</v>
+        <v>-64.31</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>3135.560550 DOT + cash 0.00</t>
+          <t>44722.308707 HBAR + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15406,10 +15406,10 @@
         <v>10000</v>
       </c>
       <c r="H56" t="n">
-        <v>3517.4</v>
+        <v>3532.27</v>
       </c>
       <c r="I56" t="n">
-        <v>-64.83</v>
+        <v>-64.68000000000001</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -15446,10 +15446,10 @@
         <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>3500.43</v>
+        <v>3515.23</v>
       </c>
       <c r="I57" t="n">
-        <v>-65</v>
+        <v>-64.84999999999999</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -15486,10 +15486,10 @@
         <v>10000</v>
       </c>
       <c r="H58" t="n">
-        <v>3334.45</v>
+        <v>3348.55</v>
       </c>
       <c r="I58" t="n">
-        <v>-66.66</v>
+        <v>-66.51000000000001</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -15526,10 +15526,10 @@
         <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>3208.21</v>
+        <v>3249.35</v>
       </c>
       <c r="I59" t="n">
-        <v>-67.92</v>
+        <v>-67.51000000000001</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -15566,10 +15566,10 @@
         <v>10000</v>
       </c>
       <c r="H60" t="n">
-        <v>3140.86</v>
+        <v>3173.39</v>
       </c>
       <c r="I60" t="n">
-        <v>-68.59</v>
+        <v>-68.27</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DOT/LINK</t>
+          <t>ADA/NEAR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -15597,7 +15597,7 @@
         <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -15606,14 +15606,14 @@
         <v>10000</v>
       </c>
       <c r="H61" t="n">
-        <v>2968.94</v>
+        <v>3012.94</v>
       </c>
       <c r="I61" t="n">
-        <v>-70.31</v>
+        <v>-69.87</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2628.077450 DOT + cash 0.00</t>
+          <t>13047.794641 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15625,7 +15625,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ADA/NEAR</t>
+          <t>DOT/LINK</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -15637,7 +15637,7 @@
         <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -15646,14 +15646,14 @@
         <v>10000</v>
       </c>
       <c r="H62" t="n">
-        <v>2950.37</v>
+        <v>2999.69</v>
       </c>
       <c r="I62" t="n">
-        <v>-70.5</v>
+        <v>-70</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>13047.794641 ADA + cash 0.00</t>
+          <t>2628.077450 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15686,10 +15686,10 @@
         <v>10000</v>
       </c>
       <c r="H63" t="n">
-        <v>2941.42</v>
+        <v>2971.88</v>
       </c>
       <c r="I63" t="n">
-        <v>-70.59</v>
+        <v>-70.28</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AAVE/XCH</t>
+          <t>ADA/ATOM</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -15714,10 +15714,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>210</v>
+        <v>266</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -15726,14 +15726,14 @@
         <v>10000</v>
       </c>
       <c r="H64" t="n">
-        <v>2905.01</v>
+        <v>2966.01</v>
       </c>
       <c r="I64" t="n">
-        <v>-70.95</v>
+        <v>-70.34</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>1929.983353 XCH + cash 0.00</t>
+          <t>12844.538258 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15745,7 +15745,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ADA/ATOM</t>
+          <t>AAVE/XCH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -15754,10 +15754,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>266</v>
+        <v>210</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -15766,14 +15766,14 @@
         <v>10000</v>
       </c>
       <c r="H65" t="n">
-        <v>2904.41</v>
+        <v>2942.26</v>
       </c>
       <c r="I65" t="n">
-        <v>-70.95999999999999</v>
+        <v>-70.58</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>12844.538258 ADA + cash 0.00</t>
+          <t>1929.983353 XCH + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DOT/NEAR</t>
+          <t>ADA/ICP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -15797,7 +15797,7 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>277</v>
+        <v>331</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -15806,14 +15806,14 @@
         <v>10000</v>
       </c>
       <c r="H66" t="n">
-        <v>2812.23</v>
+        <v>2870.84</v>
       </c>
       <c r="I66" t="n">
-        <v>-71.88</v>
+        <v>-71.29000000000001</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2489.356202 DOT + cash 0.00</t>
+          <t>12432.415237 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15825,7 +15825,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ADA/ICP</t>
+          <t>DOT/NEAR</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -15837,7 +15837,7 @@
         <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>331</v>
+        <v>277</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -15846,14 +15846,14 @@
         <v>10000</v>
       </c>
       <c r="H67" t="n">
-        <v>2811.22</v>
+        <v>2841.35</v>
       </c>
       <c r="I67" t="n">
-        <v>-71.89</v>
+        <v>-71.59</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>12432.415237 ADA + cash 0.00</t>
+          <t>2489.356202 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -15886,10 +15886,10 @@
         <v>10000</v>
       </c>
       <c r="H68" t="n">
-        <v>2808.84</v>
+        <v>2837.93</v>
       </c>
       <c r="I68" t="n">
-        <v>-71.91</v>
+        <v>-71.62</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -15926,10 +15926,10 @@
         <v>10000</v>
       </c>
       <c r="H69" t="n">
-        <v>2772.77</v>
+        <v>2801.49</v>
       </c>
       <c r="I69" t="n">
-        <v>-72.27</v>
+        <v>-71.98999999999999</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -15966,10 +15966,10 @@
         <v>10000</v>
       </c>
       <c r="H70" t="n">
-        <v>2699.24</v>
+        <v>2727.2</v>
       </c>
       <c r="I70" t="n">
-        <v>-73.01000000000001</v>
+        <v>-72.73</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DOT/BTC</t>
+          <t>ADA/ETH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -15997,7 +15997,7 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -16006,14 +16006,14 @@
         <v>10000</v>
       </c>
       <c r="H71" t="n">
-        <v>2543.4</v>
+        <v>2574.58</v>
       </c>
       <c r="I71" t="n">
-        <v>-74.56999999999999</v>
+        <v>-74.25</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2251.390233 DOT + cash 0.00</t>
+          <t>11149.403117 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -16025,19 +16025,19 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DOT/ZRO</t>
+          <t>ADA/LINK</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="D72" t="n">
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>363</v>
+        <v>318</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -16046,14 +16046,14 @@
         <v>10000</v>
       </c>
       <c r="H72" t="n">
-        <v>2543.4</v>
+        <v>2574.58</v>
       </c>
       <c r="I72" t="n">
-        <v>-74.56999999999999</v>
+        <v>-74.25</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2251.390233 DOT + cash 0.00</t>
+          <t>11149.403117 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -16065,7 +16065,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DOT/TRX</t>
+          <t>ADA/BTC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -16077,7 +16077,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -16086,14 +16086,14 @@
         <v>10000</v>
       </c>
       <c r="H73" t="n">
-        <v>2543.4</v>
+        <v>2574.58</v>
       </c>
       <c r="I73" t="n">
-        <v>-74.56999999999999</v>
+        <v>-74.25</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2251.390233 DOT + cash 0.00</t>
+          <t>11149.403117 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -16105,7 +16105,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DOT/BNB</t>
+          <t>ADA/AAVE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>364</v>
+        <v>311</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -16126,14 +16126,14 @@
         <v>10000</v>
       </c>
       <c r="H74" t="n">
-        <v>2543.4</v>
+        <v>2574.58</v>
       </c>
       <c r="I74" t="n">
-        <v>-74.56999999999999</v>
+        <v>-74.25</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2251.390233 DOT + cash 0.00</t>
+          <t>11149.403117 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -16145,19 +16145,19 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ADA/ETH</t>
+          <t>ADA/ZRO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="D75" t="n">
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -16166,10 +16166,10 @@
         <v>10000</v>
       </c>
       <c r="H75" t="n">
-        <v>2521.1</v>
+        <v>2574.58</v>
       </c>
       <c r="I75" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.25</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -16206,10 +16206,10 @@
         <v>10000</v>
       </c>
       <c r="H76" t="n">
-        <v>2521.1</v>
+        <v>2574.58</v>
       </c>
       <c r="I76" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.25</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ADA/BTC</t>
+          <t>ADA/HBAR</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -16237,7 +16237,7 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>363</v>
+        <v>327</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -16246,10 +16246,10 @@
         <v>10000</v>
       </c>
       <c r="H77" t="n">
-        <v>2521.1</v>
+        <v>2574.58</v>
       </c>
       <c r="I77" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.25</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -16286,10 +16286,10 @@
         <v>10000</v>
       </c>
       <c r="H78" t="n">
-        <v>2521.1</v>
+        <v>2574.58</v>
       </c>
       <c r="I78" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.25</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ADA/HBAR</t>
+          <t>DOT/BTC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -16317,7 +16317,7 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>327</v>
+        <v>363</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -16326,14 +16326,14 @@
         <v>10000</v>
       </c>
       <c r="H79" t="n">
-        <v>2521.1</v>
+        <v>2569.74</v>
       </c>
       <c r="I79" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.3</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>11149.403117 ADA + cash 0.00</t>
+          <t>2251.390233 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -16345,19 +16345,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ADA/LINK</t>
+          <t>DOT/ZRO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="D80" t="n">
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>318</v>
+        <v>363</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -16366,14 +16366,14 @@
         <v>10000</v>
       </c>
       <c r="H80" t="n">
-        <v>2521.1</v>
+        <v>2569.74</v>
       </c>
       <c r="I80" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.3</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>11149.403117 ADA + cash 0.00</t>
+          <t>2251.390233 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -16385,19 +16385,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ADA/ZRO</t>
+          <t>DOT/TRX</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -16406,14 +16406,14 @@
         <v>10000</v>
       </c>
       <c r="H81" t="n">
-        <v>2521.1</v>
+        <v>2569.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.3</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>11149.403117 ADA + cash 0.00</t>
+          <t>2251.390233 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -16425,7 +16425,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ADA/AAVE</t>
+          <t>DOT/BNB</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -16437,7 +16437,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -16446,14 +16446,14 @@
         <v>10000</v>
       </c>
       <c r="H82" t="n">
-        <v>2521.1</v>
+        <v>2569.74</v>
       </c>
       <c r="I82" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.3</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>11149.403117 ADA + cash 0.00</t>
+          <t>2251.390233 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -16486,10 +16486,10 @@
         <v>10000</v>
       </c>
       <c r="H83" t="n">
-        <v>2418.97</v>
+        <v>2449.98</v>
       </c>
       <c r="I83" t="n">
-        <v>-75.81</v>
+        <v>-75.5</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -16526,10 +16526,10 @@
         <v>10000</v>
       </c>
       <c r="H84" t="n">
-        <v>2281.67</v>
+        <v>2310.92</v>
       </c>
       <c r="I84" t="n">
-        <v>-77.18000000000001</v>
+        <v>-76.89</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -16566,10 +16566,10 @@
         <v>10000</v>
       </c>
       <c r="H85" t="n">
-        <v>2124.54</v>
+        <v>2151.79</v>
       </c>
       <c r="I85" t="n">
-        <v>-78.75</v>
+        <v>-78.48</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -16606,10 +16606,10 @@
         <v>10000</v>
       </c>
       <c r="H86" t="n">
-        <v>2073.51</v>
+        <v>2100.1</v>
       </c>
       <c r="I86" t="n">
-        <v>-79.26000000000001</v>
+        <v>-79</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -16646,10 +16646,10 @@
         <v>10000</v>
       </c>
       <c r="H87" t="n">
-        <v>2049.67</v>
+        <v>2075.95</v>
       </c>
       <c r="I87" t="n">
-        <v>-79.5</v>
+        <v>-79.23999999999999</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -16686,10 +16686,10 @@
         <v>10000</v>
       </c>
       <c r="H88" t="n">
-        <v>1988.48</v>
+        <v>2013.97</v>
       </c>
       <c r="I88" t="n">
-        <v>-80.12</v>
+        <v>-79.86</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -16726,10 +16726,10 @@
         <v>10000</v>
       </c>
       <c r="H89" t="n">
-        <v>1821.34</v>
+        <v>1844.7</v>
       </c>
       <c r="I89" t="n">
-        <v>-81.79000000000001</v>
+        <v>-81.55</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -16766,10 +16766,10 @@
         <v>10000</v>
       </c>
       <c r="H90" t="n">
-        <v>1649.26</v>
+        <v>1670.4</v>
       </c>
       <c r="I90" t="n">
-        <v>-83.51000000000001</v>
+        <v>-83.3</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -16806,10 +16806,10 @@
         <v>10000</v>
       </c>
       <c r="H91" t="n">
-        <v>1645.39</v>
+        <v>1666.48</v>
       </c>
       <c r="I91" t="n">
-        <v>-83.55</v>
+        <v>-83.34</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -16846,10 +16846,10 @@
         <v>10000</v>
       </c>
       <c r="H92" t="n">
-        <v>1572.22</v>
+        <v>1592.38</v>
       </c>
       <c r="I92" t="n">
-        <v>-84.28</v>
+        <v>-84.08</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -16992,10 +16992,10 @@
         <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>14138.37</v>
+        <v>14187.98</v>
       </c>
       <c r="I3" t="n">
-        <v>41.38</v>
+        <v>41.88</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -17072,10 +17072,10 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>12843.27</v>
+        <v>12791.12</v>
       </c>
       <c r="I5" t="n">
-        <v>28.43</v>
+        <v>27.91</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -17112,10 +17112,10 @@
         <v>10000</v>
       </c>
       <c r="H6" t="n">
-        <v>12762.91</v>
+        <v>12765.44</v>
       </c>
       <c r="I6" t="n">
-        <v>27.63</v>
+        <v>27.65</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -17152,10 +17152,10 @@
         <v>10000</v>
       </c>
       <c r="H7" t="n">
-        <v>11645.68</v>
+        <v>11694.91</v>
       </c>
       <c r="I7" t="n">
-        <v>16.46</v>
+        <v>16.95</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEAR/BNB</t>
+          <t>NEAR/XCH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -17183,7 +17183,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>330</v>
+        <v>273</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -17192,14 +17192,14 @@
         <v>10000</v>
       </c>
       <c r="H8" t="n">
-        <v>11627.59</v>
+        <v>11651.3</v>
       </c>
       <c r="I8" t="n">
-        <v>16.28</v>
+        <v>16.51</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15.230722 BNB + cash 0.00</t>
+          <t>7642.704492 XCH + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -17232,10 +17232,10 @@
         <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>11606.82</v>
+        <v>11609.12</v>
       </c>
       <c r="I9" t="n">
-        <v>16.07</v>
+        <v>16.09</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NEAR/XCH</t>
+          <t>NEAR/BNB</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -17263,7 +17263,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>273</v>
+        <v>330</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -17272,14 +17272,14 @@
         <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>11503.8</v>
+        <v>11580.37</v>
       </c>
       <c r="I10" t="n">
-        <v>15.04</v>
+        <v>15.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>7642.704492 XCH + cash 0.00</t>
+          <t>15.230722 BNB + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -17312,10 +17312,10 @@
         <v>10000</v>
       </c>
       <c r="H11" t="n">
-        <v>11502.47</v>
+        <v>11501.35</v>
       </c>
       <c r="I11" t="n">
-        <v>15.02</v>
+        <v>15.01</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -17352,10 +17352,10 @@
         <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>10855.56</v>
+        <v>10893.65</v>
       </c>
       <c r="I12" t="n">
-        <v>8.56</v>
+        <v>8.94</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -17392,10 +17392,10 @@
         <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>10767</v>
+        <v>10769.13</v>
       </c>
       <c r="I13" t="n">
-        <v>7.67</v>
+        <v>7.69</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -17472,10 +17472,10 @@
         <v>10000</v>
       </c>
       <c r="H15" t="n">
-        <v>9462.01</v>
+        <v>9479.09</v>
       </c>
       <c r="I15" t="n">
-        <v>-5.38</v>
+        <v>-5.21</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -17512,10 +17512,10 @@
         <v>10000</v>
       </c>
       <c r="H16" t="n">
-        <v>9441.870000000001</v>
+        <v>9475</v>
       </c>
       <c r="I16" t="n">
-        <v>-5.58</v>
+        <v>-5.25</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -17552,10 +17552,10 @@
         <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>9302.6</v>
+        <v>9390.23</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.97</v>
+        <v>-6.1</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -17592,10 +17592,10 @@
         <v>10000</v>
       </c>
       <c r="H18" t="n">
-        <v>9201.030000000001</v>
+        <v>9163.66</v>
       </c>
       <c r="I18" t="n">
-        <v>-7.99</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -17632,10 +17632,10 @@
         <v>10000</v>
       </c>
       <c r="H19" t="n">
-        <v>8993.309999999999</v>
+        <v>8995.09</v>
       </c>
       <c r="I19" t="n">
-        <v>-10.07</v>
+        <v>-10.05</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -17672,10 +17672,10 @@
         <v>10000</v>
       </c>
       <c r="H20" t="n">
-        <v>8535.74</v>
+        <v>8551.139999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-14.64</v>
+        <v>-14.49</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -17712,10 +17712,10 @@
         <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>7946.33</v>
+        <v>8221.120000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-20.54</v>
+        <v>-17.79</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ETH/XCH</t>
+          <t>ICP/ATOM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -17740,10 +17740,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>315</v>
+        <v>28</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -17752,14 +17752,14 @@
         <v>10000</v>
       </c>
       <c r="H22" t="n">
-        <v>7645.11</v>
+        <v>7693.66</v>
       </c>
       <c r="I22" t="n">
-        <v>-23.55</v>
+        <v>-23.06</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.923201 ETH + cash 0.00</t>
+          <t>4442.834505 ATOM + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -17771,7 +17771,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ICP/ATOM</t>
+          <t>ETH/XCH</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -17780,10 +17780,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>28</v>
+        <v>315</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -17792,14 +17792,14 @@
         <v>10000</v>
       </c>
       <c r="H23" t="n">
-        <v>7590.14</v>
+        <v>7658.9</v>
       </c>
       <c r="I23" t="n">
-        <v>-24.1</v>
+        <v>-23.41</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4442.834505 ATOM + cash 0.00</t>
+          <t>2.923201 ETH + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -17832,10 +17832,10 @@
         <v>10000</v>
       </c>
       <c r="H24" t="n">
-        <v>6996.83</v>
+        <v>6998.21</v>
       </c>
       <c r="I24" t="n">
-        <v>-30.03</v>
+        <v>-30.02</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -17872,10 +17872,10 @@
         <v>10000</v>
       </c>
       <c r="H25" t="n">
-        <v>5844.9</v>
+        <v>5855.45</v>
       </c>
       <c r="I25" t="n">
-        <v>-41.55</v>
+        <v>-41.45</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -17912,10 +17912,10 @@
         <v>10000</v>
       </c>
       <c r="H26" t="n">
-        <v>5844.9</v>
+        <v>5855.45</v>
       </c>
       <c r="I26" t="n">
-        <v>-41.55</v>
+        <v>-41.45</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -17952,10 +17952,10 @@
         <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>5844.9</v>
+        <v>5855.45</v>
       </c>
       <c r="I27" t="n">
-        <v>-41.55</v>
+        <v>-41.45</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -17992,10 +17992,10 @@
         <v>10000</v>
       </c>
       <c r="H28" t="n">
-        <v>5844.9</v>
+        <v>5855.45</v>
       </c>
       <c r="I28" t="n">
-        <v>-41.55</v>
+        <v>-41.45</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -18032,10 +18032,10 @@
         <v>10000</v>
       </c>
       <c r="H29" t="n">
-        <v>5541.36</v>
+        <v>5732.98</v>
       </c>
       <c r="I29" t="n">
-        <v>-44.59</v>
+        <v>-42.67</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -18072,10 +18072,10 @@
         <v>10000</v>
       </c>
       <c r="H30" t="n">
-        <v>5457.96</v>
+        <v>5509.37</v>
       </c>
       <c r="I30" t="n">
-        <v>-45.42</v>
+        <v>-44.91</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -18112,10 +18112,10 @@
         <v>10000</v>
       </c>
       <c r="H31" t="n">
-        <v>5261.43</v>
+        <v>5283.68</v>
       </c>
       <c r="I31" t="n">
-        <v>-47.39</v>
+        <v>-47.16</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -18152,10 +18152,10 @@
         <v>10000</v>
       </c>
       <c r="H32" t="n">
-        <v>5203.65</v>
+        <v>5252.66</v>
       </c>
       <c r="I32" t="n">
-        <v>-47.96</v>
+        <v>-47.47</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>10000</v>
       </c>
       <c r="H33" t="n">
-        <v>5203.65</v>
+        <v>5252.66</v>
       </c>
       <c r="I33" t="n">
-        <v>-47.96</v>
+        <v>-47.47</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -18232,10 +18232,10 @@
         <v>10000</v>
       </c>
       <c r="H34" t="n">
-        <v>5203.65</v>
+        <v>5252.66</v>
       </c>
       <c r="I34" t="n">
-        <v>-47.96</v>
+        <v>-47.47</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -18272,10 +18272,10 @@
         <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>5203.65</v>
+        <v>5252.66</v>
       </c>
       <c r="I35" t="n">
-        <v>-47.96</v>
+        <v>-47.47</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -18312,10 +18312,10 @@
         <v>10000</v>
       </c>
       <c r="H36" t="n">
-        <v>5203.65</v>
+        <v>5252.66</v>
       </c>
       <c r="I36" t="n">
-        <v>-47.96</v>
+        <v>-47.47</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -18352,10 +18352,10 @@
         <v>10000</v>
       </c>
       <c r="H37" t="n">
-        <v>5203.65</v>
+        <v>5252.66</v>
       </c>
       <c r="I37" t="n">
-        <v>-47.96</v>
+        <v>-47.47</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -18392,10 +18392,10 @@
         <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>5203.65</v>
+        <v>5252.66</v>
       </c>
       <c r="I38" t="n">
-        <v>-47.96</v>
+        <v>-47.47</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -18432,10 +18432,10 @@
         <v>10000</v>
       </c>
       <c r="H39" t="n">
-        <v>5203.65</v>
+        <v>5252.66</v>
       </c>
       <c r="I39" t="n">
-        <v>-47.96</v>
+        <v>-47.47</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>5203.65</v>
+        <v>5252.66</v>
       </c>
       <c r="I40" t="n">
-        <v>-47.96</v>
+        <v>-47.47</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -18512,10 +18512,10 @@
         <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>4969.69</v>
+        <v>5021.16</v>
       </c>
       <c r="I41" t="n">
-        <v>-50.3</v>
+        <v>-49.79</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -18552,10 +18552,10 @@
         <v>10000</v>
       </c>
       <c r="H42" t="n">
-        <v>4818.65</v>
+        <v>4985.28</v>
       </c>
       <c r="I42" t="n">
-        <v>-51.81</v>
+        <v>-50.15</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -18592,10 +18592,10 @@
         <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>4596.36</v>
+        <v>4755.3</v>
       </c>
       <c r="I43" t="n">
-        <v>-54.04</v>
+        <v>-52.45</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -18632,10 +18632,10 @@
         <v>10000</v>
       </c>
       <c r="H44" t="n">
-        <v>4596.36</v>
+        <v>4755.3</v>
       </c>
       <c r="I44" t="n">
-        <v>-54.04</v>
+        <v>-52.45</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>4596.36</v>
+        <v>4755.3</v>
       </c>
       <c r="I45" t="n">
-        <v>-54.04</v>
+        <v>-52.45</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -18712,10 +18712,10 @@
         <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>4596.36</v>
+        <v>4755.3</v>
       </c>
       <c r="I46" t="n">
-        <v>-54.04</v>
+        <v>-52.45</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -18752,10 +18752,10 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>4596.36</v>
+        <v>4755.3</v>
       </c>
       <c r="I47" t="n">
-        <v>-54.04</v>
+        <v>-52.45</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -18792,10 +18792,10 @@
         <v>10000</v>
       </c>
       <c r="H48" t="n">
-        <v>4596.36</v>
+        <v>4755.3</v>
       </c>
       <c r="I48" t="n">
-        <v>-54.04</v>
+        <v>-52.45</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -18832,10 +18832,10 @@
         <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>4596.36</v>
+        <v>4755.3</v>
       </c>
       <c r="I49" t="n">
-        <v>-54.04</v>
+        <v>-52.45</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -18872,10 +18872,10 @@
         <v>10000</v>
       </c>
       <c r="H50" t="n">
-        <v>4547.68</v>
+        <v>4609.7</v>
       </c>
       <c r="I50" t="n">
-        <v>-54.52</v>
+        <v>-53.9</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -18912,10 +18912,10 @@
         <v>10000</v>
       </c>
       <c r="H51" t="n">
-        <v>4108.41</v>
+        <v>4164.44</v>
       </c>
       <c r="I51" t="n">
-        <v>-58.92</v>
+        <v>-58.36</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -18952,10 +18952,10 @@
         <v>10000</v>
       </c>
       <c r="H52" t="n">
-        <v>4004.26</v>
+        <v>4058.87</v>
       </c>
       <c r="I52" t="n">
-        <v>-59.96</v>
+        <v>-59.41</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -18992,10 +18992,10 @@
         <v>10000</v>
       </c>
       <c r="H53" t="n">
-        <v>3941.88</v>
+        <v>3958.54</v>
       </c>
       <c r="I53" t="n">
-        <v>-60.58</v>
+        <v>-60.41</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -19032,10 +19032,10 @@
         <v>10000</v>
       </c>
       <c r="H54" t="n">
-        <v>3757.78</v>
+        <v>3809.03</v>
       </c>
       <c r="I54" t="n">
-        <v>-62.42</v>
+        <v>-61.91</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -19072,10 +19072,10 @@
         <v>10000</v>
       </c>
       <c r="H55" t="n">
-        <v>3757.78</v>
+        <v>3809.03</v>
       </c>
       <c r="I55" t="n">
-        <v>-62.42</v>
+        <v>-61.91</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -19112,10 +19112,10 @@
         <v>10000</v>
       </c>
       <c r="H56" t="n">
-        <v>3757.78</v>
+        <v>3809.03</v>
       </c>
       <c r="I56" t="n">
-        <v>-62.42</v>
+        <v>-61.91</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -19152,10 +19152,10 @@
         <v>10000</v>
       </c>
       <c r="H57" t="n">
-        <v>3757.78</v>
+        <v>3809.03</v>
       </c>
       <c r="I57" t="n">
-        <v>-62.42</v>
+        <v>-61.91</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -19192,10 +19192,10 @@
         <v>10000</v>
       </c>
       <c r="H58" t="n">
-        <v>3757.78</v>
+        <v>3809.03</v>
       </c>
       <c r="I58" t="n">
-        <v>-62.42</v>
+        <v>-61.91</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -19232,10 +19232,10 @@
         <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>3611.75</v>
+        <v>3627.02</v>
       </c>
       <c r="I59" t="n">
-        <v>-63.88</v>
+        <v>-63.73</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -19272,10 +19272,10 @@
         <v>10000</v>
       </c>
       <c r="H60" t="n">
-        <v>3603.5</v>
+        <v>3618.73</v>
       </c>
       <c r="I60" t="n">
-        <v>-63.97</v>
+        <v>-63.81</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -19312,10 +19312,10 @@
         <v>10000</v>
       </c>
       <c r="H61" t="n">
-        <v>3554.44</v>
+        <v>3569.47</v>
       </c>
       <c r="I61" t="n">
-        <v>-64.45999999999999</v>
+        <v>-64.31</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -19352,10 +19352,10 @@
         <v>10000</v>
       </c>
       <c r="H62" t="n">
-        <v>3334.45</v>
+        <v>3348.55</v>
       </c>
       <c r="I62" t="n">
-        <v>-66.66</v>
+        <v>-66.51000000000001</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -19392,10 +19392,10 @@
         <v>10000</v>
       </c>
       <c r="H63" t="n">
-        <v>2772.4</v>
+        <v>2807.95</v>
       </c>
       <c r="I63" t="n">
-        <v>-72.28</v>
+        <v>-71.92</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -19432,10 +19432,10 @@
         <v>10000</v>
       </c>
       <c r="H64" t="n">
-        <v>2685.98</v>
+        <v>2713.8</v>
       </c>
       <c r="I64" t="n">
-        <v>-73.14</v>
+        <v>-72.86</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DOT/BTC</t>
+          <t>ADA/ATOM</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -19463,7 +19463,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>363</v>
+        <v>299</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -19472,14 +19472,14 @@
         <v>10000</v>
       </c>
       <c r="H65" t="n">
-        <v>2543.4</v>
+        <v>2574.58</v>
       </c>
       <c r="I65" t="n">
-        <v>-74.56999999999999</v>
+        <v>-74.25</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2251.390233 DOT + cash 0.00</t>
+          <t>11149.403117 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DOT/TRX</t>
+          <t>ADA/TRX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -19503,7 +19503,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -19512,14 +19512,14 @@
         <v>10000</v>
       </c>
       <c r="H66" t="n">
-        <v>2543.4</v>
+        <v>2574.58</v>
       </c>
       <c r="I66" t="n">
-        <v>-74.56999999999999</v>
+        <v>-74.25</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2251.390233 DOT + cash 0.00</t>
+          <t>11149.403117 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -19531,7 +19531,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DOT/BNB</t>
+          <t>ADA/AAVE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -19543,7 +19543,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>364</v>
+        <v>311</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -19552,14 +19552,14 @@
         <v>10000</v>
       </c>
       <c r="H67" t="n">
-        <v>2543.4</v>
+        <v>2574.58</v>
       </c>
       <c r="I67" t="n">
-        <v>-74.56999999999999</v>
+        <v>-74.25</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2251.390233 DOT + cash 0.00</t>
+          <t>11149.403117 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -19571,7 +19571,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DOT/AAVE</t>
+          <t>ADA/BTC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -19583,7 +19583,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>299</v>
+        <v>363</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -19592,14 +19592,14 @@
         <v>10000</v>
       </c>
       <c r="H68" t="n">
-        <v>2543.4</v>
+        <v>2574.58</v>
       </c>
       <c r="I68" t="n">
-        <v>-74.56999999999999</v>
+        <v>-74.25</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2251.390233 DOT + cash 0.00</t>
+          <t>11149.403117 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -19611,19 +19611,19 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DOT/ZRO</t>
+          <t>ADA/LINK</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>363</v>
+        <v>318</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -19632,14 +19632,14 @@
         <v>10000</v>
       </c>
       <c r="H69" t="n">
-        <v>2543.4</v>
+        <v>2574.58</v>
       </c>
       <c r="I69" t="n">
-        <v>-74.56999999999999</v>
+        <v>-74.25</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2251.390233 DOT + cash 0.00</t>
+          <t>11149.403117 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -19651,19 +19651,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DOT/LINK</t>
+          <t>ADA/ZRO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -19672,14 +19672,14 @@
         <v>10000</v>
       </c>
       <c r="H70" t="n">
-        <v>2543.4</v>
+        <v>2574.58</v>
       </c>
       <c r="I70" t="n">
-        <v>-74.56999999999999</v>
+        <v>-74.25</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2251.390233 DOT + cash 0.00</t>
+          <t>11149.403117 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -19691,7 +19691,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DOT/HBAR</t>
+          <t>ADA/XCH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -19703,7 +19703,7 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -19712,14 +19712,14 @@
         <v>10000</v>
       </c>
       <c r="H71" t="n">
-        <v>2543.4</v>
+        <v>2574.58</v>
       </c>
       <c r="I71" t="n">
-        <v>-74.56999999999999</v>
+        <v>-74.25</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2251.390233 DOT + cash 0.00</t>
+          <t>11149.403117 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -19731,7 +19731,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DOT/XCH</t>
+          <t>ADA/BNB</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -19743,7 +19743,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>289</v>
+        <v>364</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -19752,14 +19752,14 @@
         <v>10000</v>
       </c>
       <c r="H72" t="n">
-        <v>2543.4</v>
+        <v>2574.58</v>
       </c>
       <c r="I72" t="n">
-        <v>-74.56999999999999</v>
+        <v>-74.25</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2251.390233 DOT + cash 0.00</t>
+          <t>11149.403117 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -19771,7 +19771,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DOT/NEAR</t>
+          <t>ADA/NEAR</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -19783,7 +19783,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -19792,14 +19792,14 @@
         <v>10000</v>
       </c>
       <c r="H73" t="n">
-        <v>2543.4</v>
+        <v>2574.58</v>
       </c>
       <c r="I73" t="n">
-        <v>-74.56999999999999</v>
+        <v>-74.25</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2251.390233 DOT + cash 0.00</t>
+          <t>11149.403117 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -19811,7 +19811,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DOT/ATOM</t>
+          <t>ADA/ICP</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -19823,7 +19823,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>281</v>
+        <v>342</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -19832,14 +19832,14 @@
         <v>10000</v>
       </c>
       <c r="H74" t="n">
-        <v>2543.4</v>
+        <v>2574.58</v>
       </c>
       <c r="I74" t="n">
-        <v>-74.56999999999999</v>
+        <v>-74.25</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2251.390233 DOT + cash 0.00</t>
+          <t>11149.403117 ADA + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -19851,7 +19851,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ADA/NEAR</t>
+          <t>ADA/ETH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -19863,7 +19863,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>319</v>
+        <v>351</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -19872,10 +19872,10 @@
         <v>10000</v>
       </c>
       <c r="H75" t="n">
-        <v>2521.1</v>
+        <v>2574.58</v>
       </c>
       <c r="I75" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.25</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ADA/BNB</t>
+          <t>ADA/DOT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -19903,7 +19903,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>364</v>
+        <v>186</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -19912,10 +19912,10 @@
         <v>10000</v>
       </c>
       <c r="H76" t="n">
-        <v>2521.1</v>
+        <v>2574.58</v>
       </c>
       <c r="I76" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.25</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -19952,10 +19952,10 @@
         <v>10000</v>
       </c>
       <c r="H77" t="n">
-        <v>2521.1</v>
+        <v>2574.58</v>
       </c>
       <c r="I77" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.25</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ADA/TRX</t>
+          <t>DOT/TRX</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -19983,7 +19983,7 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -19992,14 +19992,14 @@
         <v>10000</v>
       </c>
       <c r="H78" t="n">
-        <v>2521.1</v>
+        <v>2569.74</v>
       </c>
       <c r="I78" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.3</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>11149.403117 ADA + cash 0.00</t>
+          <t>2251.390233 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -20011,7 +20011,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ADA/AAVE</t>
+          <t>DOT/BNB</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -20023,7 +20023,7 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -20032,14 +20032,14 @@
         <v>10000</v>
       </c>
       <c r="H79" t="n">
-        <v>2521.1</v>
+        <v>2569.74</v>
       </c>
       <c r="I79" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.3</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>11149.403117 ADA + cash 0.00</t>
+          <t>2251.390233 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ADA/BTC</t>
+          <t>DOT/AAVE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -20063,7 +20063,7 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>363</v>
+        <v>299</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -20072,14 +20072,14 @@
         <v>10000</v>
       </c>
       <c r="H80" t="n">
-        <v>2521.1</v>
+        <v>2569.74</v>
       </c>
       <c r="I80" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.3</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>11149.403117 ADA + cash 0.00</t>
+          <t>2251.390233 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ADA/ATOM</t>
+          <t>DOT/BTC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -20103,7 +20103,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>299</v>
+        <v>363</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -20112,14 +20112,14 @@
         <v>10000</v>
       </c>
       <c r="H81" t="n">
-        <v>2521.1</v>
+        <v>2569.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.3</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>11149.403117 ADA + cash 0.00</t>
+          <t>2251.390233 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -20131,7 +20131,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ADA/ICP</t>
+          <t>DOT/ATOM</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -20143,7 +20143,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>342</v>
+        <v>281</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -20152,14 +20152,14 @@
         <v>10000</v>
       </c>
       <c r="H82" t="n">
-        <v>2521.1</v>
+        <v>2569.74</v>
       </c>
       <c r="I82" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.3</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>11149.403117 ADA + cash 0.00</t>
+          <t>2251.390233 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -20171,7 +20171,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ADA/ETH</t>
+          <t>DOT/NEAR</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -20183,7 +20183,7 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>351</v>
+        <v>324</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -20192,14 +20192,14 @@
         <v>10000</v>
       </c>
       <c r="H83" t="n">
-        <v>2521.1</v>
+        <v>2569.74</v>
       </c>
       <c r="I83" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.3</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>11149.403117 ADA + cash 0.00</t>
+          <t>2251.390233 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -20211,7 +20211,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ADA/DOT</t>
+          <t>DOT/XCH</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -20223,7 +20223,7 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>186</v>
+        <v>289</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -20232,14 +20232,14 @@
         <v>10000</v>
       </c>
       <c r="H84" t="n">
-        <v>2521.1</v>
+        <v>2569.74</v>
       </c>
       <c r="I84" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.3</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>11149.403117 ADA + cash 0.00</t>
+          <t>2251.390233 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -20251,19 +20251,19 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ADA/LINK</t>
+          <t>DOT/ZRO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="D85" t="n">
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>318</v>
+        <v>363</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -20272,14 +20272,14 @@
         <v>10000</v>
       </c>
       <c r="H85" t="n">
-        <v>2521.1</v>
+        <v>2569.74</v>
       </c>
       <c r="I85" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.3</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>11149.403117 ADA + cash 0.00</t>
+          <t>2251.390233 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -20291,19 +20291,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ADA/ZRO</t>
+          <t>DOT/LINK</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="D86" t="n">
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>362</v>
+        <v>336</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -20312,14 +20312,14 @@
         <v>10000</v>
       </c>
       <c r="H86" t="n">
-        <v>2521.1</v>
+        <v>2569.74</v>
       </c>
       <c r="I86" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.3</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>11149.403117 ADA + cash 0.00</t>
+          <t>2251.390233 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ADA/XCH</t>
+          <t>DOT/HBAR</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -20343,7 +20343,7 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -20352,14 +20352,14 @@
         <v>10000</v>
       </c>
       <c r="H87" t="n">
-        <v>2521.1</v>
+        <v>2569.74</v>
       </c>
       <c r="I87" t="n">
-        <v>-74.79000000000001</v>
+        <v>-74.3</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>11149.403117 ADA + cash 0.00</t>
+          <t>2251.390233 DOT + cash 0.00</t>
         </is>
       </c>
     </row>
@@ -20392,10 +20392,10 @@
         <v>10000</v>
       </c>
       <c r="H88" t="n">
-        <v>1822.62</v>
+        <v>1845.99</v>
       </c>
       <c r="I88" t="n">
-        <v>-81.77</v>
+        <v>-81.54000000000001</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -20432,10 +20432,10 @@
         <v>10000</v>
       </c>
       <c r="H89" t="n">
-        <v>1753.55</v>
+        <v>1776.04</v>
       </c>
       <c r="I89" t="n">
-        <v>-82.45999999999999</v>
+        <v>-82.23999999999999</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -20472,10 +20472,10 @@
         <v>10000</v>
       </c>
       <c r="H90" t="n">
-        <v>1572.22</v>
+        <v>1592.38</v>
       </c>
       <c r="I90" t="n">
-        <v>-84.28</v>
+        <v>-84.08</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -20512,10 +20512,10 @@
         <v>10000</v>
       </c>
       <c r="H91" t="n">
-        <v>1572.22</v>
+        <v>1592.38</v>
       </c>
       <c r="I91" t="n">
-        <v>-84.28</v>
+        <v>-84.08</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -20552,10 +20552,10 @@
         <v>10000</v>
       </c>
       <c r="H92" t="n">
-        <v>1572.22</v>
+        <v>1592.38</v>
       </c>
       <c r="I92" t="n">
-        <v>-84.28</v>
+        <v>-84.08</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
